--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC50E48B-509F-4D81-87A3-3C133C6ACDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E4953B-304D-4FC6-881F-5AE69FAEA427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,21 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>I feel energetic after attending the spiritual class.</t>
+  </si>
+  <si>
+    <t>I was feeling tired due to a lack of sleep, but I started feeling better after hanging out with friends.</t>
+  </si>
+  <si>
+    <t>No any feeling for today.</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1042,7 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I18" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1015</v>
       </c>
       <c r="J6" s="10">
@@ -1077,7 +1092,7 @@
         <v>1110</v>
       </c>
       <c r="J7" s="10">
-        <f t="shared" si="1"/>
+        <f>IF(I7="","",1440-I7)</f>
         <v>330</v>
       </c>
       <c r="K7" s="11" t="s">
@@ -1119,7 +1134,7 @@
         <v>420</v>
       </c>
       <c r="I8" s="10">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
         <v>1115</v>
       </c>
       <c r="J8" s="10">
@@ -1143,69 +1158,142 @@
       <c r="A9" s="8">
         <v>46255</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10" t="str">
+      <c r="B9" s="9">
+        <v>210</v>
+      </c>
+      <c r="C9" s="9">
+        <v>95</v>
+      </c>
+      <c r="D9" s="9">
+        <v>135</v>
+      </c>
+      <c r="E9" s="9">
+        <v>72</v>
+      </c>
+      <c r="F9" s="9">
+        <v>250</v>
+      </c>
+      <c r="G9" s="9">
+        <v>5</v>
+      </c>
+      <c r="H9" s="9">
+        <v>270</v>
+      </c>
+      <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+        <v>1032</v>
+      </c>
+      <c r="J9" s="10">
+        <f>IF(I9="","",1440-I9)</f>
+        <v>408</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B10" s="9">
+        <v>75</v>
+      </c>
+      <c r="C10" s="9">
+        <v>125</v>
+      </c>
+      <c r="D10" s="9">
+        <v>210</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>584</v>
+      </c>
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>994</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+        <v>446</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B11" s="9">
+        <v>320</v>
+      </c>
+      <c r="C11" s="9">
+        <v>30</v>
+      </c>
+      <c r="D11" s="9">
+        <v>75</v>
+      </c>
+      <c r="E11" s="9">
+        <v>93</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>345</v>
+      </c>
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>863</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>577</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
+      <c r="A12" s="8"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -1368,7 +1456,7 @@
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
       <c r="I19" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
         <v/>
       </c>
       <c r="J19" s="15" t="str">
@@ -1390,7 +1478,7 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
       <c r="I20" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
         <v/>
       </c>
       <c r="J20" s="15" t="str">
@@ -1412,7 +1500,7 @@
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
       <c r="I21" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
         <v/>
       </c>
       <c r="J21" s="15" t="str">
@@ -1434,7 +1522,7 @@
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
       <c r="I22" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
         <v/>
       </c>
       <c r="J22" s="15" t="str">
@@ -1456,7 +1544,7 @@
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
       <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
         <v/>
       </c>
       <c r="J23" s="15" t="str">
@@ -1478,7 +1566,7 @@
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
       <c r="I24" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
         <v/>
       </c>
       <c r="J24" s="15" t="str">
@@ -1500,7 +1588,7 @@
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
         <v/>
       </c>
       <c r="J25" s="15" t="str">
@@ -1522,7 +1610,7 @@
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
       <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
         <v/>
       </c>
       <c r="J26" s="15" t="str">
@@ -1544,7 +1632,7 @@
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="I27" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
         <v/>
       </c>
       <c r="J27" s="15" t="str">
@@ -1566,7 +1654,7 @@
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
       <c r="I28" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
         <v/>
       </c>
       <c r="J28" s="15" t="str">
@@ -1588,7 +1676,7 @@
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
         <v/>
       </c>
       <c r="J29" s="15" t="str">
@@ -1610,7 +1698,7 @@
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="I30" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
         <v/>
       </c>
       <c r="J30" s="15" t="str">
@@ -1632,7 +1720,7 @@
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
         <v/>
       </c>
       <c r="J31" s="15" t="str">
@@ -1654,7 +1742,7 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
         <v/>
       </c>
       <c r="J32" s="15" t="str">
@@ -1676,7 +1764,7 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
         <v/>
       </c>
       <c r="J33" s="15" t="str">
@@ -1698,7 +1786,7 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
       <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
         <v/>
       </c>
       <c r="J34" s="15" t="str">
@@ -1720,7 +1808,7 @@
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
       <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
         <v/>
       </c>
       <c r="J35" s="15" t="str">
@@ -1742,7 +1830,7 @@
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
       <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
         <v/>
       </c>
       <c r="J36" s="15" t="str">
@@ -1764,7 +1852,7 @@
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
       <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
         <v/>
       </c>
       <c r="J37" s="15" t="str">
@@ -1786,7 +1874,7 @@
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
       <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
         <v/>
       </c>
       <c r="J38" s="15" t="str">
@@ -1808,7 +1896,7 @@
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
         <v/>
       </c>
       <c r="J39" s="15" t="str">
@@ -1830,7 +1918,7 @@
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
       <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
         <v/>
       </c>
       <c r="J40" s="15" t="str">
@@ -1852,7 +1940,7 @@
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
         <v/>
       </c>
       <c r="J41" s="15" t="str">
@@ -1874,7 +1962,7 @@
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
         <v/>
       </c>
       <c r="J42" s="15" t="str">
@@ -1896,7 +1984,7 @@
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
         <v/>
       </c>
       <c r="J43" s="15" t="str">
@@ -1918,7 +2006,7 @@
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
       <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
         <v/>
       </c>
       <c r="J44" s="15" t="str">
@@ -1940,7 +2028,7 @@
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
       <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
         <v/>
       </c>
       <c r="J45" s="15" t="str">
@@ -1962,7 +2050,7 @@
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
       <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
         <v/>
       </c>
       <c r="J46" s="15" t="str">
@@ -1984,7 +2072,7 @@
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
       <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
         <v/>
       </c>
       <c r="J47" s="15" t="str">
@@ -2006,7 +2094,7 @@
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
       <c r="I48" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B48:F48,H48)=0,"",SUM(B48:F48,H48))</f>
         <v/>
       </c>
       <c r="J48" s="15" t="str">
@@ -2028,7 +2116,7 @@
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
         <v/>
       </c>
       <c r="J49" s="15" t="str">
@@ -2050,7 +2138,7 @@
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
       <c r="I50" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B50:F50,H50)=0,"",SUM(B50:F50,H50))</f>
         <v/>
       </c>
       <c r="J50" s="15" t="str">
@@ -2072,7 +2160,7 @@
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
       <c r="I51" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B51:F51,H51)=0,"",SUM(B51:F51,H51))</f>
         <v/>
       </c>
       <c r="J51" s="15" t="str">
@@ -2094,7 +2182,7 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B52:F52,H52)=0,"",SUM(B52:F52,H52))</f>
         <v/>
       </c>
       <c r="J52" s="15" t="str">
@@ -2116,7 +2204,7 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B53:F53,H53)=0,"",SUM(B53:F53,H53))</f>
         <v/>
       </c>
       <c r="J53" s="15" t="str">
@@ -2138,7 +2226,7 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B54:F54,H54)=0,"",SUM(B54:F54,H54))</f>
         <v/>
       </c>
       <c r="J54" s="15" t="str">
@@ -2160,7 +2248,7 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
       <c r="I55" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B55:F55,H55)=0,"",SUM(B55:F55,H55))</f>
         <v/>
       </c>
       <c r="J55" s="15" t="str">
@@ -2182,7 +2270,7 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
       <c r="I56" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B56:F56,H56)=0,"",SUM(B56:F56,H56))</f>
         <v/>
       </c>
       <c r="J56" s="15" t="str">
@@ -2204,7 +2292,7 @@
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B57:F57,H57)=0,"",SUM(B57:F57,H57))</f>
         <v/>
       </c>
       <c r="J57" s="15" t="str">
@@ -2226,7 +2314,7 @@
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
       <c r="I58" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B58:F58,H58)=0,"",SUM(B58:F58,H58))</f>
         <v/>
       </c>
       <c r="J58" s="15" t="str">
@@ -2248,7 +2336,7 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
       <c r="I59" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B59:F59,H59)=0,"",SUM(B59:F59,H59))</f>
         <v/>
       </c>
       <c r="J59" s="15" t="str">
@@ -2270,7 +2358,7 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B60:F60,H60)=0,"",SUM(B60:F60,H60))</f>
         <v/>
       </c>
       <c r="J60" s="15" t="str">
@@ -2292,7 +2380,7 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B61:F61,H61)=0,"",SUM(B61:F61,H61))</f>
         <v/>
       </c>
       <c r="J61" s="15" t="str">
@@ -2314,7 +2402,7 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B62:F62,H62)=0,"",SUM(B62:F62,H62))</f>
         <v/>
       </c>
       <c r="J62" s="15" t="str">
@@ -2336,7 +2424,7 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B63:F63,H63)=0,"",SUM(B63:F63,H63))</f>
         <v/>
       </c>
       <c r="J63" s="15" t="str">
@@ -2358,7 +2446,7 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B64:F64,H64)=0,"",SUM(B64:F64,H64))</f>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
@@ -2380,7 +2468,7 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B65:F65,H65)=0,"",SUM(B65:F65,H65))</f>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
@@ -2402,7 +2490,7 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B66:F66,H66)=0,"",SUM(B66:F66,H66))</f>
         <v/>
       </c>
       <c r="J66" s="15" t="str">
@@ -2424,7 +2512,7 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B67:F67,H67)=0,"",SUM(B67:F67,H67))</f>
         <v/>
       </c>
       <c r="J67" s="15" t="str">
@@ -2446,7 +2534,7 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B68:F68,H68)=0,"",SUM(B68:F68,H68))</f>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
@@ -2468,7 +2556,7 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
@@ -2490,11 +2578,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f>IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="2">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2512,11 +2600,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
+        <f>IF(SUM(B71:F71,H71)=0,"",SUM(B71:F71,H71))</f>
+        <v/>
+      </c>
+      <c r="J71" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2534,11 +2622,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
+        <f>IF(SUM(B72:F72,H72)=0,"",SUM(B72:F72,H72))</f>
+        <v/>
+      </c>
+      <c r="J72" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2556,11 +2644,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
+        <f>IF(SUM(B73:F73,H73)=0,"",SUM(B73:F73,H73))</f>
+        <v/>
+      </c>
+      <c r="J73" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2578,11 +2666,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
+        <f>IF(SUM(B74:F74,H74)=0,"",SUM(B74:F74,H74))</f>
+        <v/>
+      </c>
+      <c r="J74" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2600,11 +2688,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
+        <f>IF(SUM(B75:F75,H75)=0,"",SUM(B75:F75,H75))</f>
+        <v/>
+      </c>
+      <c r="J75" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2622,11 +2710,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
+        <f>IF(SUM(B76:F76,H76)=0,"",SUM(B76:F76,H76))</f>
+        <v/>
+      </c>
+      <c r="J76" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2644,11 +2732,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
+        <f>IF(SUM(B77:F77,H77)=0,"",SUM(B77:F77,H77))</f>
+        <v/>
+      </c>
+      <c r="J77" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2666,11 +2754,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
+        <f>IF(SUM(B78:F78,H78)=0,"",SUM(B78:F78,H78))</f>
+        <v/>
+      </c>
+      <c r="J78" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2688,11 +2776,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
+        <f>IF(SUM(B79:F79,H79)=0,"",SUM(B79:F79,H79))</f>
+        <v/>
+      </c>
+      <c r="J79" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2710,11 +2798,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
+        <f>IF(SUM(B80:F80,H80)=0,"",SUM(B80:F80,H80))</f>
+        <v/>
+      </c>
+      <c r="J80" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2732,11 +2820,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
+        <f>IF(SUM(B81:F81,H81)=0,"",SUM(B81:F81,H81))</f>
+        <v/>
+      </c>
+      <c r="J81" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2754,11 +2842,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
+        <f>IF(SUM(B82:F82,H82)=0,"",SUM(B82:F82,H82))</f>
+        <v/>
+      </c>
+      <c r="J82" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2776,11 +2864,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
+        <f>IF(SUM(B83:F83,H83)=0,"",SUM(B83:F83,H83))</f>
+        <v/>
+      </c>
+      <c r="J83" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2798,11 +2886,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
+        <f>IF(SUM(B84:F84,H84)=0,"",SUM(B84:F84,H84))</f>
+        <v/>
+      </c>
+      <c r="J84" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2820,11 +2908,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
+        <f>IF(SUM(B85:F85,H85)=0,"",SUM(B85:F85,H85))</f>
+        <v/>
+      </c>
+      <c r="J85" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -2842,11 +2930,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
+        <f>IF(SUM(B86:F86,H86)=0,"",SUM(B86:F86,H86))</f>
+        <v/>
+      </c>
+      <c r="J86" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -2864,11 +2952,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
+        <f>IF(SUM(B87:F87,H87)=0,"",SUM(B87:F87,H87))</f>
+        <v/>
+      </c>
+      <c r="J87" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -2886,11 +2974,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
+        <f>IF(SUM(B88:F88,H88)=0,"",SUM(B88:F88,H88))</f>
+        <v/>
+      </c>
+      <c r="J88" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -2908,11 +2996,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
+        <f>IF(SUM(B89:F89,H89)=0,"",SUM(B89:F89,H89))</f>
+        <v/>
+      </c>
+      <c r="J89" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -2930,11 +3018,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
+        <f>IF(SUM(B90:F90,H90)=0,"",SUM(B90:F90,H90))</f>
+        <v/>
+      </c>
+      <c r="J90" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -2952,11 +3040,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
+        <f>IF(SUM(B91:F91,H91)=0,"",SUM(B91:F91,H91))</f>
+        <v/>
+      </c>
+      <c r="J91" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -2974,11 +3062,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
+        <f>IF(SUM(B92:F92,H92)=0,"",SUM(B92:F92,H92))</f>
+        <v/>
+      </c>
+      <c r="J92" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -2996,11 +3084,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
+        <f>IF(SUM(B93:F93,H93)=0,"",SUM(B93:F93,H93))</f>
+        <v/>
+      </c>
+      <c r="J93" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3018,11 +3106,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
+        <f>IF(SUM(B94:F94,H94)=0,"",SUM(B94:F94,H94))</f>
+        <v/>
+      </c>
+      <c r="J94" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3040,11 +3128,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
+        <f>IF(SUM(B95:F95,H95)=0,"",SUM(B95:F95,H95))</f>
+        <v/>
+      </c>
+      <c r="J95" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3062,11 +3150,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
+        <f>IF(SUM(B96:F96,H96)=0,"",SUM(B96:F96,H96))</f>
+        <v/>
+      </c>
+      <c r="J96" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3084,11 +3172,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
+        <f>IF(SUM(B97:F97,H97)=0,"",SUM(B97:F97,H97))</f>
+        <v/>
+      </c>
+      <c r="J97" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3106,11 +3194,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
+        <f>IF(SUM(B98:F98,H98)=0,"",SUM(B98:F98,H98))</f>
+        <v/>
+      </c>
+      <c r="J98" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3128,11 +3216,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
+        <f>IF(SUM(B99:F99,H99)=0,"",SUM(B99:F99,H99))</f>
+        <v/>
+      </c>
+      <c r="J99" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3150,11 +3238,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
+        <f>IF(SUM(B100:F100,H100)=0,"",SUM(B100:F100,H100))</f>
+        <v/>
+      </c>
+      <c r="J100" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3172,11 +3260,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
+        <f>IF(SUM(B101:F101,H101)=0,"",SUM(B101:F101,H101))</f>
+        <v/>
+      </c>
+      <c r="J101" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3194,11 +3282,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
+        <f>IF(SUM(B102:F102,H102)=0,"",SUM(B102:F102,H102))</f>
+        <v/>
+      </c>
+      <c r="J102" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3216,11 +3304,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
+        <f>IF(SUM(B103:F103,H103)=0,"",SUM(B103:F103,H103))</f>
+        <v/>
+      </c>
+      <c r="J103" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3238,11 +3326,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
+        <f>IF(SUM(B104:F104,H104)=0,"",SUM(B104:F104,H104))</f>
+        <v/>
+      </c>
+      <c r="J104" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3260,11 +3348,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
+        <f>IF(SUM(B105:F105,H105)=0,"",SUM(B105:F105,H105))</f>
+        <v/>
+      </c>
+      <c r="J105" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3282,11 +3370,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
+        <f>IF(SUM(B106:F106,H106)=0,"",SUM(B106:F106,H106))</f>
+        <v/>
+      </c>
+      <c r="J106" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3304,11 +3392,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
+        <f>IF(SUM(B107:F107,H107)=0,"",SUM(B107:F107,H107))</f>
+        <v/>
+      </c>
+      <c r="J107" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3326,11 +3414,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
+        <f>IF(SUM(B108:F108,H108)=0,"",SUM(B108:F108,H108))</f>
+        <v/>
+      </c>
+      <c r="J108" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3348,11 +3436,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
+        <f>IF(SUM(B109:F109,H109)=0,"",SUM(B109:F109,H109))</f>
+        <v/>
+      </c>
+      <c r="J109" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3370,11 +3458,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
+        <f>IF(SUM(B110:F110,H110)=0,"",SUM(B110:F110,H110))</f>
+        <v/>
+      </c>
+      <c r="J110" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3392,11 +3480,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
+        <f>IF(SUM(B111:F111,H111)=0,"",SUM(B111:F111,H111))</f>
+        <v/>
+      </c>
+      <c r="J111" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3414,11 +3502,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
+        <f>IF(SUM(B112:F112,H112)=0,"",SUM(B112:F112,H112))</f>
+        <v/>
+      </c>
+      <c r="J112" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3436,11 +3524,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
+        <f>IF(SUM(B113:F113,H113)=0,"",SUM(B113:F113,H113))</f>
+        <v/>
+      </c>
+      <c r="J113" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3458,11 +3546,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
+        <f>IF(SUM(B114:F114,H114)=0,"",SUM(B114:F114,H114))</f>
+        <v/>
+      </c>
+      <c r="J114" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3480,11 +3568,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
+        <f>IF(SUM(B115:F115,H115)=0,"",SUM(B115:F115,H115))</f>
+        <v/>
+      </c>
+      <c r="J115" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3502,11 +3590,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
+        <f>IF(SUM(B116:F116,H116)=0,"",SUM(B116:F116,H116))</f>
+        <v/>
+      </c>
+      <c r="J116" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3524,11 +3612,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
+        <f>IF(SUM(B117:F117,H117)=0,"",SUM(B117:F117,H117))</f>
+        <v/>
+      </c>
+      <c r="J117" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3546,11 +3634,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
+        <f>IF(SUM(B118:F118,H118)=0,"",SUM(B118:F118,H118))</f>
+        <v/>
+      </c>
+      <c r="J118" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3568,11 +3656,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
+        <f>IF(SUM(B119:F119,H119)=0,"",SUM(B119:F119,H119))</f>
+        <v/>
+      </c>
+      <c r="J119" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3590,11 +3678,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
+        <f>IF(SUM(B120:F120,H120)=0,"",SUM(B120:F120,H120))</f>
+        <v/>
+      </c>
+      <c r="J120" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3612,11 +3700,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
+        <f>IF(SUM(B121:F121,H121)=0,"",SUM(B121:F121,H121))</f>
+        <v/>
+      </c>
+      <c r="J121" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3634,11 +3722,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
+        <f>IF(SUM(B122:F122,H122)=0,"",SUM(B122:F122,H122))</f>
+        <v/>
+      </c>
+      <c r="J122" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3656,11 +3744,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
+        <f>IF(SUM(B123:F123,H123)=0,"",SUM(B123:F123,H123))</f>
+        <v/>
+      </c>
+      <c r="J123" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3678,11 +3766,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
+        <f>IF(SUM(B124:F124,H124)=0,"",SUM(B124:F124,H124))</f>
+        <v/>
+      </c>
+      <c r="J124" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3700,11 +3788,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
+        <f>IF(SUM(B125:F125,H125)=0,"",SUM(B125:F125,H125))</f>
+        <v/>
+      </c>
+      <c r="J125" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3722,11 +3810,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
+        <f>IF(SUM(B126:F126,H126)=0,"",SUM(B126:F126,H126))</f>
+        <v/>
+      </c>
+      <c r="J126" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3744,11 +3832,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
+        <f>IF(SUM(B127:F127,H127)=0,"",SUM(B127:F127,H127))</f>
+        <v/>
+      </c>
+      <c r="J127" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3766,11 +3854,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
+        <f>IF(SUM(B128:F128,H128)=0,"",SUM(B128:F128,H128))</f>
+        <v/>
+      </c>
+      <c r="J128" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3788,11 +3876,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
+        <f>IF(SUM(B129:F129,H129)=0,"",SUM(B129:F129,H129))</f>
+        <v/>
+      </c>
+      <c r="J129" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3810,11 +3898,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
+        <f>IF(SUM(B130:F130,H130)=0,"",SUM(B130:F130,H130))</f>
+        <v/>
+      </c>
+      <c r="J130" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3832,11 +3920,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
+        <f>IF(SUM(B131:F131,H131)=0,"",SUM(B131:F131,H131))</f>
+        <v/>
+      </c>
+      <c r="J131" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -3854,11 +3942,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
+        <f>IF(SUM(B132:F132,H132)=0,"",SUM(B132:F132,H132))</f>
+        <v/>
+      </c>
+      <c r="J132" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -3876,11 +3964,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
+        <f>IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
+        <v/>
+      </c>
+      <c r="J133" s="15" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -3898,11 +3986,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f>IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="3">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -3920,11 +4008,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B135:F135,H135)=0,"",SUM(B135:F135,H135))</f>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -3942,11 +4030,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B136:F136,H136)=0,"",SUM(B136:F136,H136))</f>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -3964,11 +4052,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B137:F137,H137)=0,"",SUM(B137:F137,H137))</f>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -3986,11 +4074,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B138:F138,H138)=0,"",SUM(B138:F138,H138))</f>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4008,11 +4096,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B139:F139,H139)=0,"",SUM(B139:F139,H139))</f>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4030,11 +4118,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B140:F140,H140)=0,"",SUM(B140:F140,H140))</f>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4052,11 +4140,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B141:F141,H141)=0,"",SUM(B141:F141,H141))</f>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4074,11 +4162,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B142:F142,H142)=0,"",SUM(B142:F142,H142))</f>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4096,11 +4184,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B143:F143,H143)=0,"",SUM(B143:F143,H143))</f>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4118,11 +4206,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B144:F144,H144)=0,"",SUM(B144:F144,H144))</f>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4140,11 +4228,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B145:F145,H145)=0,"",SUM(B145:F145,H145))</f>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4162,11 +4250,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B146:F146,H146)=0,"",SUM(B146:F146,H146))</f>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4184,11 +4272,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B147:F147,H147)=0,"",SUM(B147:F147,H147))</f>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4206,11 +4294,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B148:F148,H148)=0,"",SUM(B148:F148,H148))</f>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4228,11 +4316,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B149:F149,H149)=0,"",SUM(B149:F149,H149))</f>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4250,11 +4338,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B150:F150,H150)=0,"",SUM(B150:F150,H150))</f>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4272,11 +4360,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B151:F151,H151)=0,"",SUM(B151:F151,H151))</f>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4294,11 +4382,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B152:F152,H152)=0,"",SUM(B152:F152,H152))</f>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4316,11 +4404,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B153:F153,H153)=0,"",SUM(B153:F153,H153))</f>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4338,11 +4426,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B154:F154,H154)=0,"",SUM(B154:F154,H154))</f>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4360,11 +4448,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B155:F155,H155)=0,"",SUM(B155:F155,H155))</f>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4382,11 +4470,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B156:F156,H156)=0,"",SUM(B156:F156,H156))</f>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4404,11 +4492,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B157:F157,H157)=0,"",SUM(B157:F157,H157))</f>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4426,11 +4514,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B158:F158,H158)=0,"",SUM(B158:F158,H158))</f>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4448,11 +4536,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B159:F159,H159)=0,"",SUM(B159:F159,H159))</f>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4470,11 +4558,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B160:F160,H160)=0,"",SUM(B160:F160,H160))</f>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4492,11 +4580,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B161:F161,H161)=0,"",SUM(B161:F161,H161))</f>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4514,11 +4602,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B162:F162,H162)=0,"",SUM(B162:F162,H162))</f>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4536,11 +4624,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B163:F163,H163)=0,"",SUM(B163:F163,H163))</f>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4558,11 +4646,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B164:F164,H164)=0,"",SUM(B164:F164,H164))</f>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4580,11 +4668,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B165:F165,H165)=0,"",SUM(B165:F165,H165))</f>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4602,11 +4690,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B166:F166,H166)=0,"",SUM(B166:F166,H166))</f>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4624,11 +4712,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B167:F167,H167)=0,"",SUM(B167:F167,H167))</f>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4646,11 +4734,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B168:F168,H168)=0,"",SUM(B168:F168,H168))</f>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4668,11 +4756,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B169:F169,H169)=0,"",SUM(B169:F169,H169))</f>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4690,11 +4778,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B170:F170,H170)=0,"",SUM(B170:F170,H170))</f>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4712,11 +4800,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B171:F171,H171)=0,"",SUM(B171:F171,H171))</f>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4734,11 +4822,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B172:F172,H172)=0,"",SUM(B172:F172,H172))</f>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4756,11 +4844,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B173:F173,H173)=0,"",SUM(B173:F173,H173))</f>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4778,11 +4866,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B174:F174,H174)=0,"",SUM(B174:F174,H174))</f>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4800,11 +4888,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B175:F175,H175)=0,"",SUM(B175:F175,H175))</f>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4822,11 +4910,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B176:F176,H176)=0,"",SUM(B176:F176,H176))</f>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -4844,11 +4932,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B177:F177,H177)=0,"",SUM(B177:F177,H177))</f>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -4866,11 +4954,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B178:F178,H178)=0,"",SUM(B178:F178,H178))</f>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -4888,11 +4976,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B179:F179,H179)=0,"",SUM(B179:F179,H179))</f>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -4910,11 +4998,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B180:F180,H180)=0,"",SUM(B180:F180,H180))</f>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -4932,11 +5020,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B181:F181,H181)=0,"",SUM(B181:F181,H181))</f>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -4954,11 +5042,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B182:F182,H182)=0,"",SUM(B182:F182,H182))</f>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -4976,11 +5064,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B183:F183,H183)=0,"",SUM(B183:F183,H183))</f>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -4998,11 +5086,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B184:F184,H184)=0,"",SUM(B184:F184,H184))</f>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5020,11 +5108,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B185:F185,H185)=0,"",SUM(B185:F185,H185))</f>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5042,11 +5130,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B186:F186,H186)=0,"",SUM(B186:F186,H186))</f>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5064,11 +5152,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B187:F187,H187)=0,"",SUM(B187:F187,H187))</f>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5086,11 +5174,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B188:F188,H188)=0,"",SUM(B188:F188,H188))</f>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5108,11 +5196,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B189:F189,H189)=0,"",SUM(B189:F189,H189))</f>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5130,11 +5218,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B190:F190,H190)=0,"",SUM(B190:F190,H190))</f>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5152,11 +5240,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B191:F191,H191)=0,"",SUM(B191:F191,H191))</f>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5174,11 +5262,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B192:F192,H192)=0,"",SUM(B192:F192,H192))</f>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5196,11 +5284,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B193:F193,H193)=0,"",SUM(B193:F193,H193))</f>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5218,11 +5306,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B194:F194,H194)=0,"",SUM(B194:F194,H194))</f>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5240,11 +5328,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B195:F195,H195)=0,"",SUM(B195:F195,H195))</f>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5262,11 +5350,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B196:F196,H196)=0,"",SUM(B196:F196,H196))</f>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5284,11 +5372,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5306,11 +5394,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f>IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="4">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5328,11 +5416,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B199:F199,H199)=0,"",SUM(B199:F199,H199))</f>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5350,11 +5438,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B200:F200,H200)=0,"",SUM(B200:F200,H200))</f>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5372,11 +5460,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B201:F201,H201)=0,"",SUM(B201:F201,H201))</f>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5394,11 +5482,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B202:F202,H202)=0,"",SUM(B202:F202,H202))</f>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5416,11 +5504,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B203:F203,H203)=0,"",SUM(B203:F203,H203))</f>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5438,11 +5526,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B204:F204,H204)=0,"",SUM(B204:F204,H204))</f>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5460,11 +5548,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B205:F205,H205)=0,"",SUM(B205:F205,H205))</f>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5482,11 +5570,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B206:F206,H206)=0,"",SUM(B206:F206,H206))</f>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5504,11 +5592,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B207:F207,H207)=0,"",SUM(B207:F207,H207))</f>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5526,11 +5614,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B208:F208,H208)=0,"",SUM(B208:F208,H208))</f>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5548,11 +5636,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B209:F209,H209)=0,"",SUM(B209:F209,H209))</f>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5570,11 +5658,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B210:F210,H210)=0,"",SUM(B210:F210,H210))</f>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5592,11 +5680,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B211:F211,H211)=0,"",SUM(B211:F211,H211))</f>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5614,11 +5702,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B212:F212,H212)=0,"",SUM(B212:F212,H212))</f>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5636,11 +5724,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B213:F213,H213)=0,"",SUM(B213:F213,H213))</f>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5658,11 +5746,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B214:F214,H214)=0,"",SUM(B214:F214,H214))</f>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5680,11 +5768,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B215:F215,H215)=0,"",SUM(B215:F215,H215))</f>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5702,11 +5790,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B216:F216,H216)=0,"",SUM(B216:F216,H216))</f>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5724,11 +5812,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B217:F217,H217)=0,"",SUM(B217:F217,H217))</f>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5746,11 +5834,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B218:F218,H218)=0,"",SUM(B218:F218,H218))</f>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5768,11 +5856,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B219:F219,H219)=0,"",SUM(B219:F219,H219))</f>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5790,11 +5878,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B220:F220,H220)=0,"",SUM(B220:F220,H220))</f>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5812,11 +5900,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B221:F221,H221)=0,"",SUM(B221:F221,H221))</f>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -5834,11 +5922,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B222:F222,H222)=0,"",SUM(B222:F222,H222))</f>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -5856,11 +5944,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B223:F223,H223)=0,"",SUM(B223:F223,H223))</f>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -5878,11 +5966,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B224:F224,H224)=0,"",SUM(B224:F224,H224))</f>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -5900,11 +5988,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B225:F225,H225)=0,"",SUM(B225:F225,H225))</f>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -5922,11 +6010,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B226:F226,H226)=0,"",SUM(B226:F226,H226))</f>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -5944,11 +6032,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B227:F227,H227)=0,"",SUM(B227:F227,H227))</f>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -5966,11 +6054,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B228:F228,H228)=0,"",SUM(B228:F228,H228))</f>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -5988,11 +6076,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B229:F229,H229)=0,"",SUM(B229:F229,H229))</f>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6010,11 +6098,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B230:F230,H230)=0,"",SUM(B230:F230,H230))</f>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6032,11 +6120,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B231:F231,H231)=0,"",SUM(B231:F231,H231))</f>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6054,11 +6142,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B232:F232,H232)=0,"",SUM(B232:F232,H232))</f>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6076,11 +6164,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B233:F233,H233)=0,"",SUM(B233:F233,H233))</f>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6098,11 +6186,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B234:F234,H234)=0,"",SUM(B234:F234,H234))</f>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6120,11 +6208,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B235:F235,H235)=0,"",SUM(B235:F235,H235))</f>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6142,11 +6230,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B236:F236,H236)=0,"",SUM(B236:F236,H236))</f>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6164,11 +6252,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B237:F237,H237)=0,"",SUM(B237:F237,H237))</f>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6186,11 +6274,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B238:F238,H238)=0,"",SUM(B238:F238,H238))</f>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6208,11 +6296,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B239:F239,H239)=0,"",SUM(B239:F239,H239))</f>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6230,11 +6318,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B240:F240,H240)=0,"",SUM(B240:F240,H240))</f>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6252,11 +6340,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B241:F241,H241)=0,"",SUM(B241:F241,H241))</f>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6274,11 +6362,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B242:F242,H242)=0,"",SUM(B242:F242,H242))</f>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6296,11 +6384,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B243:F243,H243)=0,"",SUM(B243:F243,H243))</f>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6318,11 +6406,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B244:F244,H244)=0,"",SUM(B244:F244,H244))</f>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6340,11 +6428,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B245:F245,H245)=0,"",SUM(B245:F245,H245))</f>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6362,11 +6450,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B246:F246,H246)=0,"",SUM(B246:F246,H246))</f>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6384,11 +6472,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B247:F247,H247)=0,"",SUM(B247:F247,H247))</f>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6406,11 +6494,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B248:F248,H248)=0,"",SUM(B248:F248,H248))</f>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6428,11 +6516,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B249:F249,H249)=0,"",SUM(B249:F249,H249))</f>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6450,11 +6538,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B250:F250,H250)=0,"",SUM(B250:F250,H250))</f>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6472,11 +6560,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B251:F251,H251)=0,"",SUM(B251:F251,H251))</f>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6494,11 +6582,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B252:F252,H252)=0,"",SUM(B252:F252,H252))</f>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6516,11 +6604,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B253:F253,H253)=0,"",SUM(B253:F253,H253))</f>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6538,11 +6626,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B254:F254,H254)=0,"",SUM(B254:F254,H254))</f>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6560,11 +6648,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B255:F255,H255)=0,"",SUM(B255:F255,H255))</f>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6582,11 +6670,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B256:F256,H256)=0,"",SUM(B256:F256,H256))</f>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6604,11 +6692,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B257:F257,H257)=0,"",SUM(B257:F257,H257))</f>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6626,11 +6714,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B258:F258,H258)=0,"",SUM(B258:F258,H258))</f>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6648,11 +6736,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B259:F259,H259)=0,"",SUM(B259:F259,H259))</f>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6670,11 +6758,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B260:F260,H260)=0,"",SUM(B260:F260,H260))</f>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6692,11 +6780,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6714,11 +6802,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f>IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="5">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6736,11 +6824,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B263:F263,H263)=0,"",SUM(B263:F263,H263))</f>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6758,11 +6846,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B264:F264,H264)=0,"",SUM(B264:F264,H264))</f>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6780,11 +6868,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B265:F265,H265)=0,"",SUM(B265:F265,H265))</f>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6802,11 +6890,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B266:F266,H266)=0,"",SUM(B266:F266,H266))</f>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6824,11 +6912,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B267:F267,H267)=0,"",SUM(B267:F267,H267))</f>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -6846,11 +6934,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B268:F268,H268)=0,"",SUM(B268:F268,H268))</f>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -6868,11 +6956,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B269:F269,H269)=0,"",SUM(B269:F269,H269))</f>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -6890,11 +6978,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B270:F270,H270)=0,"",SUM(B270:F270,H270))</f>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -6912,11 +7000,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B271:F271,H271)=0,"",SUM(B271:F271,H271))</f>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -6934,11 +7022,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B272:F272,H272)=0,"",SUM(B272:F272,H272))</f>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -6956,11 +7044,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B273:F273,H273)=0,"",SUM(B273:F273,H273))</f>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -6978,11 +7066,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B274:F274,H274)=0,"",SUM(B274:F274,H274))</f>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7000,11 +7088,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B275:F275,H275)=0,"",SUM(B275:F275,H275))</f>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7022,11 +7110,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B276:F276,H276)=0,"",SUM(B276:F276,H276))</f>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7044,11 +7132,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B277:F277,H277)=0,"",SUM(B277:F277,H277))</f>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7066,11 +7154,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B278:F278,H278)=0,"",SUM(B278:F278,H278))</f>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7088,11 +7176,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B279:F279,H279)=0,"",SUM(B279:F279,H279))</f>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7110,11 +7198,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B280:F280,H280)=0,"",SUM(B280:F280,H280))</f>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7132,11 +7220,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B281:F281,H281)=0,"",SUM(B281:F281,H281))</f>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7154,11 +7242,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B282:F282,H282)=0,"",SUM(B282:F282,H282))</f>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7176,11 +7264,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B283:F283,H283)=0,"",SUM(B283:F283,H283))</f>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7198,11 +7286,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B284:F284,H284)=0,"",SUM(B284:F284,H284))</f>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7220,11 +7308,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B285:F285,H285)=0,"",SUM(B285:F285,H285))</f>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7242,11 +7330,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B286:F286,H286)=0,"",SUM(B286:F286,H286))</f>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7264,11 +7352,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B287:F287,H287)=0,"",SUM(B287:F287,H287))</f>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7286,11 +7374,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B288:F288,H288)=0,"",SUM(B288:F288,H288))</f>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7308,11 +7396,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B289:F289,H289)=0,"",SUM(B289:F289,H289))</f>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7330,11 +7418,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B290:F290,H290)=0,"",SUM(B290:F290,H290))</f>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7352,11 +7440,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B291:F291,H291)=0,"",SUM(B291:F291,H291))</f>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7374,11 +7462,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B292:F292,H292)=0,"",SUM(B292:F292,H292))</f>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7396,11 +7484,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B293:F293,H293)=0,"",SUM(B293:F293,H293))</f>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7418,11 +7506,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B294:F294,H294)=0,"",SUM(B294:F294,H294))</f>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7440,11 +7528,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B295:F295,H295)=0,"",SUM(B295:F295,H295))</f>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7462,11 +7550,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B296:F296,H296)=0,"",SUM(B296:F296,H296))</f>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7484,11 +7572,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B297:F297,H297)=0,"",SUM(B297:F297,H297))</f>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7506,11 +7594,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B298:F298,H298)=0,"",SUM(B298:F298,H298))</f>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7528,11 +7616,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B299:F299,H299)=0,"",SUM(B299:F299,H299))</f>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7550,11 +7638,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B300:F300,H300)=0,"",SUM(B300:F300,H300))</f>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7572,11 +7660,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B301:F301,H301)=0,"",SUM(B301:F301,H301))</f>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7594,11 +7682,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B302:F302,H302)=0,"",SUM(B302:F302,H302))</f>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7616,11 +7704,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B303:F303,H303)=0,"",SUM(B303:F303,H303))</f>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7638,11 +7726,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B304:F304,H304)=0,"",SUM(B304:F304,H304))</f>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7660,11 +7748,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B305:F305,H305)=0,"",SUM(B305:F305,H305))</f>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7682,11 +7770,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B306:F306,H306)=0,"",SUM(B306:F306,H306))</f>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7704,11 +7792,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B307:F307,H307)=0,"",SUM(B307:F307,H307))</f>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7726,11 +7814,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B308:F308,H308)=0,"",SUM(B308:F308,H308))</f>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7748,11 +7836,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B309:F309,H309)=0,"",SUM(B309:F309,H309))</f>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7770,11 +7858,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B310:F310,H310)=0,"",SUM(B310:F310,H310))</f>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7792,11 +7880,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B311:F311,H311)=0,"",SUM(B311:F311,H311))</f>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7814,11 +7902,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B312:F312,H312)=0,"",SUM(B312:F312,H312))</f>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -7836,11 +7924,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B313:F313,H313)=0,"",SUM(B313:F313,H313))</f>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -7858,11 +7946,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B314:F314,H314)=0,"",SUM(B314:F314,H314))</f>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -7880,11 +7968,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B315:F315,H315)=0,"",SUM(B315:F315,H315))</f>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -7902,11 +7990,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B316:F316,H316)=0,"",SUM(B316:F316,H316))</f>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -7924,11 +8012,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B317:F317,H317)=0,"",SUM(B317:F317,H317))</f>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -7946,11 +8034,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B318:F318,H318)=0,"",SUM(B318:F318,H318))</f>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -7968,11 +8056,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B319:F319,H319)=0,"",SUM(B319:F319,H319))</f>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -7990,11 +8078,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B320:F320,H320)=0,"",SUM(B320:F320,H320))</f>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8012,11 +8100,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B321:F321,H321)=0,"",SUM(B321:F321,H321))</f>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8034,11 +8122,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B322:F322,H322)=0,"",SUM(B322:F322,H322))</f>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8056,11 +8144,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B323:F323,H323)=0,"",SUM(B323:F323,H323))</f>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8078,11 +8166,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B324:F324,H324)=0,"",SUM(B324:F324,H324))</f>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8100,11 +8188,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8122,11 +8210,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f>IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="6">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8144,11 +8232,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B327:F327,H327)=0,"",SUM(B327:F327,H327))</f>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8166,11 +8254,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B328:F328,H328)=0,"",SUM(B328:F328,H328))</f>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8188,11 +8276,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B329:F329,H329)=0,"",SUM(B329:F329,H329))</f>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8210,11 +8298,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B330:F330,H330)=0,"",SUM(B330:F330,H330))</f>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8232,11 +8320,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B331:F331,H331)=0,"",SUM(B331:F331,H331))</f>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8254,11 +8342,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B332:F332,H332)=0,"",SUM(B332:F332,H332))</f>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8276,11 +8364,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B333:F333,H333)=0,"",SUM(B333:F333,H333))</f>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8298,11 +8386,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B334:F334,H334)=0,"",SUM(B334:F334,H334))</f>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8320,11 +8408,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B335:F335,H335)=0,"",SUM(B335:F335,H335))</f>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8342,11 +8430,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B336:F336,H336)=0,"",SUM(B336:F336,H336))</f>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8364,11 +8452,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B337:F337,H337)=0,"",SUM(B337:F337,H337))</f>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8386,11 +8474,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B338:F338,H338)=0,"",SUM(B338:F338,H338))</f>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8408,11 +8496,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B339:F339,H339)=0,"",SUM(B339:F339,H339))</f>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8430,11 +8518,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B340:F340,H340)=0,"",SUM(B340:F340,H340))</f>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8452,11 +8540,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B341:F341,H341)=0,"",SUM(B341:F341,H341))</f>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8474,11 +8562,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B342:F342,H342)=0,"",SUM(B342:F342,H342))</f>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8496,11 +8584,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B343:F343,H343)=0,"",SUM(B343:F343,H343))</f>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8518,11 +8606,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B344:F344,H344)=0,"",SUM(B344:F344,H344))</f>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8540,11 +8628,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B345:F345,H345)=0,"",SUM(B345:F345,H345))</f>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8562,11 +8650,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B346:F346,H346)=0,"",SUM(B346:F346,H346))</f>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8584,11 +8672,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B347:F347,H347)=0,"",SUM(B347:F347,H347))</f>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8606,11 +8694,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B348:F348,H348)=0,"",SUM(B348:F348,H348))</f>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8628,11 +8716,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B349:F349,H349)=0,"",SUM(B349:F349,H349))</f>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8650,11 +8738,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B350:F350,H350)=0,"",SUM(B350:F350,H350))</f>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8672,11 +8760,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B351:F351,H351)=0,"",SUM(B351:F351,H351))</f>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8694,11 +8782,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B352:F352,H352)=0,"",SUM(B352:F352,H352))</f>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8716,11 +8804,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B353:F353,H353)=0,"",SUM(B353:F353,H353))</f>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8738,11 +8826,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B354:F354,H354)=0,"",SUM(B354:F354,H354))</f>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8760,11 +8848,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B355:F355,H355)=0,"",SUM(B355:F355,H355))</f>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8782,11 +8870,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B356:F356,H356)=0,"",SUM(B356:F356,H356))</f>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8804,11 +8892,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B357:F357,H357)=0,"",SUM(B357:F357,H357))</f>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8826,11 +8914,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B358:F358,H358)=0,"",SUM(B358:F358,H358))</f>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -8848,11 +8936,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B359:F359,H359)=0,"",SUM(B359:F359,H359))</f>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -8870,11 +8958,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B360:F360,H360)=0,"",SUM(B360:F360,H360))</f>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -8892,11 +8980,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B361:F361,H361)=0,"",SUM(B361:F361,H361))</f>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -8914,11 +9002,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B362:F362,H362)=0,"",SUM(B362:F362,H362))</f>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -8936,11 +9024,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B363:F363,H363)=0,"",SUM(B363:F363,H363))</f>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -8958,11 +9046,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B364:F364,H364)=0,"",SUM(B364:F364,H364))</f>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -8980,11 +9068,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B365:F365,H365)=0,"",SUM(B365:F365,H365))</f>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9002,11 +9090,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B366:F366,H366)=0,"",SUM(B366:F366,H366))</f>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9024,11 +9112,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B367:F367,H367)=0,"",SUM(B367:F367,H367))</f>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9046,11 +9134,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B368:F368,H368)=0,"",SUM(B368:F368,H368))</f>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9068,11 +9156,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B369:F369,H369)=0,"",SUM(B369:F369,H369))</f>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9090,11 +9178,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B370:F370,H370)=0,"",SUM(B370:F370,H370))</f>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9112,11 +9200,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B371:F371,H371)=0,"",SUM(B371:F371,H371))</f>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9134,11 +9222,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B372:F372,H372)=0,"",SUM(B372:F372,H372))</f>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9156,11 +9244,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B373:F373,H373)=0,"",SUM(B373:F373,H373))</f>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9178,11 +9266,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B374:F374,H374)=0,"",SUM(B374:F374,H374))</f>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9200,11 +9288,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B375:F375,H375)=0,"",SUM(B375:F375,H375))</f>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9222,11 +9310,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B376:F376,H376)=0,"",SUM(B376:F376,H376))</f>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9244,11 +9332,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B377:F377,H377)=0,"",SUM(B377:F377,H377))</f>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9266,11 +9354,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B378:F378,H378)=0,"",SUM(B378:F378,H378))</f>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9288,11 +9376,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B379:F379,H379)=0,"",SUM(B379:F379,H379))</f>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9310,11 +9398,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B380:F380,H380)=0,"",SUM(B380:F380,H380))</f>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9332,11 +9420,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B381:F381,H381)=0,"",SUM(B381:F381,H381))</f>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9354,11 +9442,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B382:F382,H382)=0,"",SUM(B382:F382,H382))</f>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9376,11 +9464,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B383:F383,H383)=0,"",SUM(B383:F383,H383))</f>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9398,11 +9486,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B384:F384,H384)=0,"",SUM(B384:F384,H384))</f>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9420,11 +9508,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B385:F385,H385)=0,"",SUM(B385:F385,H385))</f>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9442,11 +9530,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B386:F386,H386)=0,"",SUM(B386:F386,H386))</f>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9464,11 +9552,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B387:F387,H387)=0,"",SUM(B387:F387,H387))</f>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9486,11 +9574,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B388:F388,H388)=0,"",SUM(B388:F388,H388))</f>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9508,11 +9596,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9530,11 +9618,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f>IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="7">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9552,11 +9640,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B391:F391,H391)=0,"",SUM(B391:F391,H391))</f>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9574,11 +9662,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B392:F392,H392)=0,"",SUM(B392:F392,H392))</f>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9596,11 +9684,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B393:F393,H393)=0,"",SUM(B393:F393,H393))</f>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9618,11 +9706,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B394:F394,H394)=0,"",SUM(B394:F394,H394))</f>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9640,11 +9728,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B395:F395,H395)=0,"",SUM(B395:F395,H395))</f>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9662,11 +9750,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B396:F396,H396)=0,"",SUM(B396:F396,H396))</f>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9684,11 +9772,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B397:F397,H397)=0,"",SUM(B397:F397,H397))</f>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9706,11 +9794,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B398:F398,H398)=0,"",SUM(B398:F398,H398))</f>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9728,11 +9816,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B399:F399,H399)=0,"",SUM(B399:F399,H399))</f>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9750,11 +9838,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B400:F400,H400)=0,"",SUM(B400:F400,H400))</f>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9772,11 +9860,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f>IF(SUM(B401:F401,H401)=0,"",SUM(B401:F401,H401))</f>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E4953B-304D-4FC6-881F-5AE69FAEA427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7949AC-5C81-4742-A091-DE22FF9CF158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>No any feeling for today.</t>
+  </si>
+  <si>
+    <t>A normal Day.</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1203,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>46256</v>
       </c>
@@ -1293,26 +1296,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="9">
+        <v>280</v>
+      </c>
+      <c r="C12" s="9">
+        <v>48</v>
+      </c>
+      <c r="D12" s="9">
+        <v>150</v>
+      </c>
+      <c r="E12" s="9">
+        <v>60</v>
+      </c>
+      <c r="F12" s="9">
+        <v>250</v>
+      </c>
+      <c r="G12" s="9">
+        <v>5</v>
+      </c>
+      <c r="H12" s="9">
+        <v>100</v>
+      </c>
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>888</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>552</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
@@ -1456,7 +1483,7 @@
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
       <c r="I19" s="15" t="str">
-        <f>IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
+        <f t="shared" ref="I19:I82" si="2">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
         <v/>
       </c>
       <c r="J19" s="15" t="str">
@@ -1478,7 +1505,7 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
       <c r="I20" s="15" t="str">
-        <f>IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J20" s="15" t="str">
@@ -1500,7 +1527,7 @@
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
       <c r="I21" s="15" t="str">
-        <f>IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J21" s="15" t="str">
@@ -1522,7 +1549,7 @@
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
       <c r="I22" s="15" t="str">
-        <f>IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J22" s="15" t="str">
@@ -1544,7 +1571,7 @@
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
       <c r="I23" s="15" t="str">
-        <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J23" s="15" t="str">
@@ -1566,7 +1593,7 @@
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
       <c r="I24" s="15" t="str">
-        <f>IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J24" s="15" t="str">
@@ -1588,7 +1615,7 @@
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="I25" s="15" t="str">
-        <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J25" s="15" t="str">
@@ -1610,7 +1637,7 @@
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
       <c r="I26" s="15" t="str">
-        <f>IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J26" s="15" t="str">
@@ -1632,7 +1659,7 @@
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="I27" s="15" t="str">
-        <f>IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J27" s="15" t="str">
@@ -1654,7 +1681,7 @@
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
       <c r="I28" s="15" t="str">
-        <f>IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J28" s="15" t="str">
@@ -1676,7 +1703,7 @@
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="I29" s="15" t="str">
-        <f>IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J29" s="15" t="str">
@@ -1698,7 +1725,7 @@
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="I30" s="15" t="str">
-        <f>IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J30" s="15" t="str">
@@ -1720,7 +1747,7 @@
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="I31" s="15" t="str">
-        <f>IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J31" s="15" t="str">
@@ -1742,7 +1769,7 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="I32" s="15" t="str">
-        <f>IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J32" s="15" t="str">
@@ -1764,7 +1791,7 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="15" t="str">
-        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J33" s="15" t="str">
@@ -1786,7 +1813,7 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
       <c r="I34" s="15" t="str">
-        <f>IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J34" s="15" t="str">
@@ -1808,7 +1835,7 @@
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
       <c r="I35" s="15" t="str">
-        <f>IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J35" s="15" t="str">
@@ -1830,7 +1857,7 @@
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
       <c r="I36" s="15" t="str">
-        <f>IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J36" s="15" t="str">
@@ -1852,7 +1879,7 @@
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
       <c r="I37" s="15" t="str">
-        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J37" s="15" t="str">
@@ -1874,7 +1901,7 @@
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
       <c r="I38" s="15" t="str">
-        <f>IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J38" s="15" t="str">
@@ -1896,7 +1923,7 @@
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="15" t="str">
-        <f>IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J39" s="15" t="str">
@@ -1918,7 +1945,7 @@
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
       <c r="I40" s="15" t="str">
-        <f>IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J40" s="15" t="str">
@@ -1940,7 +1967,7 @@
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="15" t="str">
-        <f>IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J41" s="15" t="str">
@@ -1962,7 +1989,7 @@
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="15" t="str">
-        <f>IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J42" s="15" t="str">
@@ -1984,7 +2011,7 @@
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="15" t="str">
-        <f>IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J43" s="15" t="str">
@@ -2006,7 +2033,7 @@
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
       <c r="I44" s="15" t="str">
-        <f>IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J44" s="15" t="str">
@@ -2028,7 +2055,7 @@
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
       <c r="I45" s="15" t="str">
-        <f>IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J45" s="15" t="str">
@@ -2050,7 +2077,7 @@
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
       <c r="I46" s="15" t="str">
-        <f>IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J46" s="15" t="str">
@@ -2072,7 +2099,7 @@
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
       <c r="I47" s="15" t="str">
-        <f>IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J47" s="15" t="str">
@@ -2094,7 +2121,7 @@
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
       <c r="I48" s="15" t="str">
-        <f>IF(SUM(B48:F48,H48)=0,"",SUM(B48:F48,H48))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J48" s="15" t="str">
@@ -2116,7 +2143,7 @@
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="15" t="str">
-        <f>IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J49" s="15" t="str">
@@ -2138,7 +2165,7 @@
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
       <c r="I50" s="15" t="str">
-        <f>IF(SUM(B50:F50,H50)=0,"",SUM(B50:F50,H50))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J50" s="15" t="str">
@@ -2160,7 +2187,7 @@
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
       <c r="I51" s="15" t="str">
-        <f>IF(SUM(B51:F51,H51)=0,"",SUM(B51:F51,H51))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J51" s="15" t="str">
@@ -2182,7 +2209,7 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="15" t="str">
-        <f>IF(SUM(B52:F52,H52)=0,"",SUM(B52:F52,H52))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J52" s="15" t="str">
@@ -2204,7 +2231,7 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="15" t="str">
-        <f>IF(SUM(B53:F53,H53)=0,"",SUM(B53:F53,H53))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J53" s="15" t="str">
@@ -2226,7 +2253,7 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="15" t="str">
-        <f>IF(SUM(B54:F54,H54)=0,"",SUM(B54:F54,H54))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J54" s="15" t="str">
@@ -2248,7 +2275,7 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
       <c r="I55" s="15" t="str">
-        <f>IF(SUM(B55:F55,H55)=0,"",SUM(B55:F55,H55))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J55" s="15" t="str">
@@ -2270,7 +2297,7 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
       <c r="I56" s="15" t="str">
-        <f>IF(SUM(B56:F56,H56)=0,"",SUM(B56:F56,H56))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J56" s="15" t="str">
@@ -2292,7 +2319,7 @@
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="15" t="str">
-        <f>IF(SUM(B57:F57,H57)=0,"",SUM(B57:F57,H57))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J57" s="15" t="str">
@@ -2314,7 +2341,7 @@
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
       <c r="I58" s="15" t="str">
-        <f>IF(SUM(B58:F58,H58)=0,"",SUM(B58:F58,H58))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J58" s="15" t="str">
@@ -2336,7 +2363,7 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
       <c r="I59" s="15" t="str">
-        <f>IF(SUM(B59:F59,H59)=0,"",SUM(B59:F59,H59))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J59" s="15" t="str">
@@ -2358,7 +2385,7 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
-        <f>IF(SUM(B60:F60,H60)=0,"",SUM(B60:F60,H60))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J60" s="15" t="str">
@@ -2380,7 +2407,7 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
-        <f>IF(SUM(B61:F61,H61)=0,"",SUM(B61:F61,H61))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J61" s="15" t="str">
@@ -2402,7 +2429,7 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
-        <f>IF(SUM(B62:F62,H62)=0,"",SUM(B62:F62,H62))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J62" s="15" t="str">
@@ -2424,7 +2451,7 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
-        <f>IF(SUM(B63:F63,H63)=0,"",SUM(B63:F63,H63))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J63" s="15" t="str">
@@ -2446,7 +2473,7 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f>IF(SUM(B64:F64,H64)=0,"",SUM(B64:F64,H64))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
@@ -2468,7 +2495,7 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f>IF(SUM(B65:F65,H65)=0,"",SUM(B65:F65,H65))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
@@ -2490,7 +2517,7 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
-        <f>IF(SUM(B66:F66,H66)=0,"",SUM(B66:F66,H66))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J66" s="15" t="str">
@@ -2512,7 +2539,7 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
-        <f>IF(SUM(B67:F67,H67)=0,"",SUM(B67:F67,H67))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J67" s="15" t="str">
@@ -2534,7 +2561,7 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f>IF(SUM(B68:F68,H68)=0,"",SUM(B68:F68,H68))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
@@ -2556,7 +2583,7 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f>IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
@@ -2578,11 +2605,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f>IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="2">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2600,11 +2627,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f>IF(SUM(B71:F71,H71)=0,"",SUM(B71:F71,H71))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2622,11 +2649,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f>IF(SUM(B72:F72,H72)=0,"",SUM(B72:F72,H72))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2644,11 +2671,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f>IF(SUM(B73:F73,H73)=0,"",SUM(B73:F73,H73))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2666,11 +2693,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f>IF(SUM(B74:F74,H74)=0,"",SUM(B74:F74,H74))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2688,11 +2715,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f>IF(SUM(B75:F75,H75)=0,"",SUM(B75:F75,H75))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2710,11 +2737,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f>IF(SUM(B76:F76,H76)=0,"",SUM(B76:F76,H76))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2732,11 +2759,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f>IF(SUM(B77:F77,H77)=0,"",SUM(B77:F77,H77))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2754,11 +2781,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f>IF(SUM(B78:F78,H78)=0,"",SUM(B78:F78,H78))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2776,11 +2803,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f>IF(SUM(B79:F79,H79)=0,"",SUM(B79:F79,H79))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2798,11 +2825,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f>IF(SUM(B80:F80,H80)=0,"",SUM(B80:F80,H80))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2820,11 +2847,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f>IF(SUM(B81:F81,H81)=0,"",SUM(B81:F81,H81))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2842,11 +2869,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f>IF(SUM(B82:F82,H82)=0,"",SUM(B82:F82,H82))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2864,11 +2891,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f>IF(SUM(B83:F83,H83)=0,"",SUM(B83:F83,H83))</f>
+        <f t="shared" ref="I83:I146" si="4">IF(SUM(B83:F83,H83)=0,"",SUM(B83:F83,H83))</f>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2886,11 +2913,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f>IF(SUM(B84:F84,H84)=0,"",SUM(B84:F84,H84))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2908,11 +2935,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f>IF(SUM(B85:F85,H85)=0,"",SUM(B85:F85,H85))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -2930,11 +2957,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f>IF(SUM(B86:F86,H86)=0,"",SUM(B86:F86,H86))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -2952,11 +2979,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f>IF(SUM(B87:F87,H87)=0,"",SUM(B87:F87,H87))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -2974,11 +3001,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f>IF(SUM(B88:F88,H88)=0,"",SUM(B88:F88,H88))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -2996,11 +3023,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f>IF(SUM(B89:F89,H89)=0,"",SUM(B89:F89,H89))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3018,11 +3045,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f>IF(SUM(B90:F90,H90)=0,"",SUM(B90:F90,H90))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3040,11 +3067,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f>IF(SUM(B91:F91,H91)=0,"",SUM(B91:F91,H91))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3062,11 +3089,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f>IF(SUM(B92:F92,H92)=0,"",SUM(B92:F92,H92))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3084,11 +3111,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f>IF(SUM(B93:F93,H93)=0,"",SUM(B93:F93,H93))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3106,11 +3133,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f>IF(SUM(B94:F94,H94)=0,"",SUM(B94:F94,H94))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3128,11 +3155,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f>IF(SUM(B95:F95,H95)=0,"",SUM(B95:F95,H95))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3150,11 +3177,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f>IF(SUM(B96:F96,H96)=0,"",SUM(B96:F96,H96))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3172,11 +3199,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f>IF(SUM(B97:F97,H97)=0,"",SUM(B97:F97,H97))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3194,11 +3221,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f>IF(SUM(B98:F98,H98)=0,"",SUM(B98:F98,H98))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3216,11 +3243,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f>IF(SUM(B99:F99,H99)=0,"",SUM(B99:F99,H99))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3238,11 +3265,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f>IF(SUM(B100:F100,H100)=0,"",SUM(B100:F100,H100))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3260,11 +3287,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f>IF(SUM(B101:F101,H101)=0,"",SUM(B101:F101,H101))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3282,11 +3309,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f>IF(SUM(B102:F102,H102)=0,"",SUM(B102:F102,H102))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3304,11 +3331,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f>IF(SUM(B103:F103,H103)=0,"",SUM(B103:F103,H103))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3326,11 +3353,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f>IF(SUM(B104:F104,H104)=0,"",SUM(B104:F104,H104))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3348,11 +3375,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f>IF(SUM(B105:F105,H105)=0,"",SUM(B105:F105,H105))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3370,11 +3397,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f>IF(SUM(B106:F106,H106)=0,"",SUM(B106:F106,H106))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3392,11 +3419,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f>IF(SUM(B107:F107,H107)=0,"",SUM(B107:F107,H107))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3414,11 +3441,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f>IF(SUM(B108:F108,H108)=0,"",SUM(B108:F108,H108))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3436,11 +3463,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f>IF(SUM(B109:F109,H109)=0,"",SUM(B109:F109,H109))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3458,11 +3485,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f>IF(SUM(B110:F110,H110)=0,"",SUM(B110:F110,H110))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3480,11 +3507,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f>IF(SUM(B111:F111,H111)=0,"",SUM(B111:F111,H111))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3502,11 +3529,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f>IF(SUM(B112:F112,H112)=0,"",SUM(B112:F112,H112))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3524,11 +3551,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f>IF(SUM(B113:F113,H113)=0,"",SUM(B113:F113,H113))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3546,11 +3573,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f>IF(SUM(B114:F114,H114)=0,"",SUM(B114:F114,H114))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3568,11 +3595,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f>IF(SUM(B115:F115,H115)=0,"",SUM(B115:F115,H115))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3590,11 +3617,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f>IF(SUM(B116:F116,H116)=0,"",SUM(B116:F116,H116))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3612,11 +3639,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f>IF(SUM(B117:F117,H117)=0,"",SUM(B117:F117,H117))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3634,11 +3661,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f>IF(SUM(B118:F118,H118)=0,"",SUM(B118:F118,H118))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3656,11 +3683,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f>IF(SUM(B119:F119,H119)=0,"",SUM(B119:F119,H119))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3678,11 +3705,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f>IF(SUM(B120:F120,H120)=0,"",SUM(B120:F120,H120))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3700,11 +3727,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f>IF(SUM(B121:F121,H121)=0,"",SUM(B121:F121,H121))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3722,11 +3749,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f>IF(SUM(B122:F122,H122)=0,"",SUM(B122:F122,H122))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3744,11 +3771,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f>IF(SUM(B123:F123,H123)=0,"",SUM(B123:F123,H123))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3766,11 +3793,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f>IF(SUM(B124:F124,H124)=0,"",SUM(B124:F124,H124))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3788,11 +3815,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f>IF(SUM(B125:F125,H125)=0,"",SUM(B125:F125,H125))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3810,11 +3837,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f>IF(SUM(B126:F126,H126)=0,"",SUM(B126:F126,H126))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3832,11 +3859,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f>IF(SUM(B127:F127,H127)=0,"",SUM(B127:F127,H127))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3854,11 +3881,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f>IF(SUM(B128:F128,H128)=0,"",SUM(B128:F128,H128))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3876,11 +3903,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f>IF(SUM(B129:F129,H129)=0,"",SUM(B129:F129,H129))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3898,11 +3925,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f>IF(SUM(B130:F130,H130)=0,"",SUM(B130:F130,H130))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3920,11 +3947,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f>IF(SUM(B131:F131,H131)=0,"",SUM(B131:F131,H131))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -3942,11 +3969,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f>IF(SUM(B132:F132,H132)=0,"",SUM(B132:F132,H132))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -3964,11 +3991,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f>IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -3986,11 +4013,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f>IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="3">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4008,11 +4035,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f>IF(SUM(B135:F135,H135)=0,"",SUM(B135:F135,H135))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4030,11 +4057,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f>IF(SUM(B136:F136,H136)=0,"",SUM(B136:F136,H136))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4052,11 +4079,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f>IF(SUM(B137:F137,H137)=0,"",SUM(B137:F137,H137))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4074,11 +4101,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f>IF(SUM(B138:F138,H138)=0,"",SUM(B138:F138,H138))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4096,11 +4123,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f>IF(SUM(B139:F139,H139)=0,"",SUM(B139:F139,H139))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4118,11 +4145,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f>IF(SUM(B140:F140,H140)=0,"",SUM(B140:F140,H140))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4140,11 +4167,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f>IF(SUM(B141:F141,H141)=0,"",SUM(B141:F141,H141))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4162,11 +4189,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f>IF(SUM(B142:F142,H142)=0,"",SUM(B142:F142,H142))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4184,11 +4211,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f>IF(SUM(B143:F143,H143)=0,"",SUM(B143:F143,H143))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4206,11 +4233,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f>IF(SUM(B144:F144,H144)=0,"",SUM(B144:F144,H144))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4228,11 +4255,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f>IF(SUM(B145:F145,H145)=0,"",SUM(B145:F145,H145))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4250,11 +4277,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f>IF(SUM(B146:F146,H146)=0,"",SUM(B146:F146,H146))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4272,11 +4299,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f>IF(SUM(B147:F147,H147)=0,"",SUM(B147:F147,H147))</f>
+        <f t="shared" ref="I147:I210" si="6">IF(SUM(B147:F147,H147)=0,"",SUM(B147:F147,H147))</f>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4294,11 +4321,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f>IF(SUM(B148:F148,H148)=0,"",SUM(B148:F148,H148))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4316,11 +4343,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f>IF(SUM(B149:F149,H149)=0,"",SUM(B149:F149,H149))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4338,11 +4365,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f>IF(SUM(B150:F150,H150)=0,"",SUM(B150:F150,H150))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4360,11 +4387,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f>IF(SUM(B151:F151,H151)=0,"",SUM(B151:F151,H151))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4382,11 +4409,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f>IF(SUM(B152:F152,H152)=0,"",SUM(B152:F152,H152))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4404,11 +4431,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f>IF(SUM(B153:F153,H153)=0,"",SUM(B153:F153,H153))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4426,11 +4453,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f>IF(SUM(B154:F154,H154)=0,"",SUM(B154:F154,H154))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4448,11 +4475,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f>IF(SUM(B155:F155,H155)=0,"",SUM(B155:F155,H155))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4470,11 +4497,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f>IF(SUM(B156:F156,H156)=0,"",SUM(B156:F156,H156))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4492,11 +4519,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f>IF(SUM(B157:F157,H157)=0,"",SUM(B157:F157,H157))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4514,11 +4541,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f>IF(SUM(B158:F158,H158)=0,"",SUM(B158:F158,H158))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4536,11 +4563,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f>IF(SUM(B159:F159,H159)=0,"",SUM(B159:F159,H159))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4558,11 +4585,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f>IF(SUM(B160:F160,H160)=0,"",SUM(B160:F160,H160))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4580,11 +4607,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f>IF(SUM(B161:F161,H161)=0,"",SUM(B161:F161,H161))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4602,11 +4629,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f>IF(SUM(B162:F162,H162)=0,"",SUM(B162:F162,H162))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4624,11 +4651,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f>IF(SUM(B163:F163,H163)=0,"",SUM(B163:F163,H163))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4646,11 +4673,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f>IF(SUM(B164:F164,H164)=0,"",SUM(B164:F164,H164))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4668,11 +4695,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f>IF(SUM(B165:F165,H165)=0,"",SUM(B165:F165,H165))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4690,11 +4717,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f>IF(SUM(B166:F166,H166)=0,"",SUM(B166:F166,H166))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4712,11 +4739,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f>IF(SUM(B167:F167,H167)=0,"",SUM(B167:F167,H167))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4734,11 +4761,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f>IF(SUM(B168:F168,H168)=0,"",SUM(B168:F168,H168))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4756,11 +4783,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f>IF(SUM(B169:F169,H169)=0,"",SUM(B169:F169,H169))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4778,11 +4805,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f>IF(SUM(B170:F170,H170)=0,"",SUM(B170:F170,H170))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4800,11 +4827,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f>IF(SUM(B171:F171,H171)=0,"",SUM(B171:F171,H171))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4822,11 +4849,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f>IF(SUM(B172:F172,H172)=0,"",SUM(B172:F172,H172))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4844,11 +4871,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f>IF(SUM(B173:F173,H173)=0,"",SUM(B173:F173,H173))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4866,11 +4893,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f>IF(SUM(B174:F174,H174)=0,"",SUM(B174:F174,H174))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4888,11 +4915,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f>IF(SUM(B175:F175,H175)=0,"",SUM(B175:F175,H175))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4910,11 +4937,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f>IF(SUM(B176:F176,H176)=0,"",SUM(B176:F176,H176))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -4932,11 +4959,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f>IF(SUM(B177:F177,H177)=0,"",SUM(B177:F177,H177))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -4954,11 +4981,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f>IF(SUM(B178:F178,H178)=0,"",SUM(B178:F178,H178))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -4976,11 +5003,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f>IF(SUM(B179:F179,H179)=0,"",SUM(B179:F179,H179))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -4998,11 +5025,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f>IF(SUM(B180:F180,H180)=0,"",SUM(B180:F180,H180))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5020,11 +5047,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f>IF(SUM(B181:F181,H181)=0,"",SUM(B181:F181,H181))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5042,11 +5069,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f>IF(SUM(B182:F182,H182)=0,"",SUM(B182:F182,H182))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5064,11 +5091,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f>IF(SUM(B183:F183,H183)=0,"",SUM(B183:F183,H183))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5086,11 +5113,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f>IF(SUM(B184:F184,H184)=0,"",SUM(B184:F184,H184))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5108,11 +5135,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f>IF(SUM(B185:F185,H185)=0,"",SUM(B185:F185,H185))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5130,11 +5157,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f>IF(SUM(B186:F186,H186)=0,"",SUM(B186:F186,H186))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5152,11 +5179,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f>IF(SUM(B187:F187,H187)=0,"",SUM(B187:F187,H187))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5174,11 +5201,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f>IF(SUM(B188:F188,H188)=0,"",SUM(B188:F188,H188))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5196,11 +5223,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f>IF(SUM(B189:F189,H189)=0,"",SUM(B189:F189,H189))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5218,11 +5245,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f>IF(SUM(B190:F190,H190)=0,"",SUM(B190:F190,H190))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5240,11 +5267,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f>IF(SUM(B191:F191,H191)=0,"",SUM(B191:F191,H191))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5262,11 +5289,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f>IF(SUM(B192:F192,H192)=0,"",SUM(B192:F192,H192))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5284,11 +5311,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f>IF(SUM(B193:F193,H193)=0,"",SUM(B193:F193,H193))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5306,11 +5333,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f>IF(SUM(B194:F194,H194)=0,"",SUM(B194:F194,H194))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5328,11 +5355,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f>IF(SUM(B195:F195,H195)=0,"",SUM(B195:F195,H195))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5350,11 +5377,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f>IF(SUM(B196:F196,H196)=0,"",SUM(B196:F196,H196))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5372,11 +5399,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f>IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5394,11 +5421,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f>IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="4">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5416,11 +5443,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f>IF(SUM(B199:F199,H199)=0,"",SUM(B199:F199,H199))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5438,11 +5465,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f>IF(SUM(B200:F200,H200)=0,"",SUM(B200:F200,H200))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5460,11 +5487,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f>IF(SUM(B201:F201,H201)=0,"",SUM(B201:F201,H201))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5482,11 +5509,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f>IF(SUM(B202:F202,H202)=0,"",SUM(B202:F202,H202))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5504,11 +5531,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f>IF(SUM(B203:F203,H203)=0,"",SUM(B203:F203,H203))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5526,11 +5553,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f>IF(SUM(B204:F204,H204)=0,"",SUM(B204:F204,H204))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5548,11 +5575,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f>IF(SUM(B205:F205,H205)=0,"",SUM(B205:F205,H205))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5570,11 +5597,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f>IF(SUM(B206:F206,H206)=0,"",SUM(B206:F206,H206))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5592,11 +5619,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f>IF(SUM(B207:F207,H207)=0,"",SUM(B207:F207,H207))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5614,11 +5641,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f>IF(SUM(B208:F208,H208)=0,"",SUM(B208:F208,H208))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5636,11 +5663,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f>IF(SUM(B209:F209,H209)=0,"",SUM(B209:F209,H209))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5658,11 +5685,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f>IF(SUM(B210:F210,H210)=0,"",SUM(B210:F210,H210))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5680,11 +5707,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f>IF(SUM(B211:F211,H211)=0,"",SUM(B211:F211,H211))</f>
+        <f t="shared" ref="I211:I274" si="8">IF(SUM(B211:F211,H211)=0,"",SUM(B211:F211,H211))</f>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5702,11 +5729,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f>IF(SUM(B212:F212,H212)=0,"",SUM(B212:F212,H212))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5724,11 +5751,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f>IF(SUM(B213:F213,H213)=0,"",SUM(B213:F213,H213))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5746,11 +5773,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f>IF(SUM(B214:F214,H214)=0,"",SUM(B214:F214,H214))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5768,11 +5795,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f>IF(SUM(B215:F215,H215)=0,"",SUM(B215:F215,H215))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5790,11 +5817,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f>IF(SUM(B216:F216,H216)=0,"",SUM(B216:F216,H216))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5812,11 +5839,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f>IF(SUM(B217:F217,H217)=0,"",SUM(B217:F217,H217))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5834,11 +5861,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f>IF(SUM(B218:F218,H218)=0,"",SUM(B218:F218,H218))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5856,11 +5883,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f>IF(SUM(B219:F219,H219)=0,"",SUM(B219:F219,H219))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5878,11 +5905,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f>IF(SUM(B220:F220,H220)=0,"",SUM(B220:F220,H220))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5900,11 +5927,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f>IF(SUM(B221:F221,H221)=0,"",SUM(B221:F221,H221))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -5922,11 +5949,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f>IF(SUM(B222:F222,H222)=0,"",SUM(B222:F222,H222))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -5944,11 +5971,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f>IF(SUM(B223:F223,H223)=0,"",SUM(B223:F223,H223))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -5966,11 +5993,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f>IF(SUM(B224:F224,H224)=0,"",SUM(B224:F224,H224))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -5988,11 +6015,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f>IF(SUM(B225:F225,H225)=0,"",SUM(B225:F225,H225))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6010,11 +6037,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f>IF(SUM(B226:F226,H226)=0,"",SUM(B226:F226,H226))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6032,11 +6059,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f>IF(SUM(B227:F227,H227)=0,"",SUM(B227:F227,H227))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6054,11 +6081,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f>IF(SUM(B228:F228,H228)=0,"",SUM(B228:F228,H228))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6076,11 +6103,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f>IF(SUM(B229:F229,H229)=0,"",SUM(B229:F229,H229))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6098,11 +6125,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f>IF(SUM(B230:F230,H230)=0,"",SUM(B230:F230,H230))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6120,11 +6147,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f>IF(SUM(B231:F231,H231)=0,"",SUM(B231:F231,H231))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6142,11 +6169,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f>IF(SUM(B232:F232,H232)=0,"",SUM(B232:F232,H232))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6164,11 +6191,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f>IF(SUM(B233:F233,H233)=0,"",SUM(B233:F233,H233))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6186,11 +6213,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f>IF(SUM(B234:F234,H234)=0,"",SUM(B234:F234,H234))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6208,11 +6235,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f>IF(SUM(B235:F235,H235)=0,"",SUM(B235:F235,H235))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6230,11 +6257,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f>IF(SUM(B236:F236,H236)=0,"",SUM(B236:F236,H236))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6252,11 +6279,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f>IF(SUM(B237:F237,H237)=0,"",SUM(B237:F237,H237))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6274,11 +6301,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f>IF(SUM(B238:F238,H238)=0,"",SUM(B238:F238,H238))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6296,11 +6323,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f>IF(SUM(B239:F239,H239)=0,"",SUM(B239:F239,H239))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6318,11 +6345,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f>IF(SUM(B240:F240,H240)=0,"",SUM(B240:F240,H240))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6340,11 +6367,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f>IF(SUM(B241:F241,H241)=0,"",SUM(B241:F241,H241))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6362,11 +6389,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f>IF(SUM(B242:F242,H242)=0,"",SUM(B242:F242,H242))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6384,11 +6411,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f>IF(SUM(B243:F243,H243)=0,"",SUM(B243:F243,H243))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6406,11 +6433,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f>IF(SUM(B244:F244,H244)=0,"",SUM(B244:F244,H244))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6428,11 +6455,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f>IF(SUM(B245:F245,H245)=0,"",SUM(B245:F245,H245))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6450,11 +6477,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f>IF(SUM(B246:F246,H246)=0,"",SUM(B246:F246,H246))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6472,11 +6499,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f>IF(SUM(B247:F247,H247)=0,"",SUM(B247:F247,H247))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6494,11 +6521,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f>IF(SUM(B248:F248,H248)=0,"",SUM(B248:F248,H248))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6516,11 +6543,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f>IF(SUM(B249:F249,H249)=0,"",SUM(B249:F249,H249))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6538,11 +6565,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f>IF(SUM(B250:F250,H250)=0,"",SUM(B250:F250,H250))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6560,11 +6587,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f>IF(SUM(B251:F251,H251)=0,"",SUM(B251:F251,H251))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6582,11 +6609,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f>IF(SUM(B252:F252,H252)=0,"",SUM(B252:F252,H252))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6604,11 +6631,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f>IF(SUM(B253:F253,H253)=0,"",SUM(B253:F253,H253))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6626,11 +6653,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f>IF(SUM(B254:F254,H254)=0,"",SUM(B254:F254,H254))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6648,11 +6675,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f>IF(SUM(B255:F255,H255)=0,"",SUM(B255:F255,H255))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6670,11 +6697,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f>IF(SUM(B256:F256,H256)=0,"",SUM(B256:F256,H256))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6692,11 +6719,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f>IF(SUM(B257:F257,H257)=0,"",SUM(B257:F257,H257))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6714,11 +6741,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f>IF(SUM(B258:F258,H258)=0,"",SUM(B258:F258,H258))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6736,11 +6763,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f>IF(SUM(B259:F259,H259)=0,"",SUM(B259:F259,H259))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6758,11 +6785,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f>IF(SUM(B260:F260,H260)=0,"",SUM(B260:F260,H260))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6780,11 +6807,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f>IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6802,11 +6829,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f>IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="5">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6824,11 +6851,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f>IF(SUM(B263:F263,H263)=0,"",SUM(B263:F263,H263))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6846,11 +6873,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f>IF(SUM(B264:F264,H264)=0,"",SUM(B264:F264,H264))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6868,11 +6895,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f>IF(SUM(B265:F265,H265)=0,"",SUM(B265:F265,H265))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6890,11 +6917,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f>IF(SUM(B266:F266,H266)=0,"",SUM(B266:F266,H266))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6912,11 +6939,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f>IF(SUM(B267:F267,H267)=0,"",SUM(B267:F267,H267))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -6934,11 +6961,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f>IF(SUM(B268:F268,H268)=0,"",SUM(B268:F268,H268))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -6956,11 +6983,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f>IF(SUM(B269:F269,H269)=0,"",SUM(B269:F269,H269))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -6978,11 +7005,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f>IF(SUM(B270:F270,H270)=0,"",SUM(B270:F270,H270))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7000,11 +7027,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f>IF(SUM(B271:F271,H271)=0,"",SUM(B271:F271,H271))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7022,11 +7049,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f>IF(SUM(B272:F272,H272)=0,"",SUM(B272:F272,H272))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7044,11 +7071,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f>IF(SUM(B273:F273,H273)=0,"",SUM(B273:F273,H273))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7066,11 +7093,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f>IF(SUM(B274:F274,H274)=0,"",SUM(B274:F274,H274))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7088,11 +7115,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f>IF(SUM(B275:F275,H275)=0,"",SUM(B275:F275,H275))</f>
+        <f t="shared" ref="I275:I338" si="10">IF(SUM(B275:F275,H275)=0,"",SUM(B275:F275,H275))</f>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7110,11 +7137,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f>IF(SUM(B276:F276,H276)=0,"",SUM(B276:F276,H276))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7132,11 +7159,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f>IF(SUM(B277:F277,H277)=0,"",SUM(B277:F277,H277))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7154,11 +7181,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f>IF(SUM(B278:F278,H278)=0,"",SUM(B278:F278,H278))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7176,11 +7203,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f>IF(SUM(B279:F279,H279)=0,"",SUM(B279:F279,H279))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7198,11 +7225,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f>IF(SUM(B280:F280,H280)=0,"",SUM(B280:F280,H280))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7220,11 +7247,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f>IF(SUM(B281:F281,H281)=0,"",SUM(B281:F281,H281))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7242,11 +7269,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f>IF(SUM(B282:F282,H282)=0,"",SUM(B282:F282,H282))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7264,11 +7291,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f>IF(SUM(B283:F283,H283)=0,"",SUM(B283:F283,H283))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7286,11 +7313,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f>IF(SUM(B284:F284,H284)=0,"",SUM(B284:F284,H284))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7308,11 +7335,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f>IF(SUM(B285:F285,H285)=0,"",SUM(B285:F285,H285))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7330,11 +7357,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f>IF(SUM(B286:F286,H286)=0,"",SUM(B286:F286,H286))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7352,11 +7379,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f>IF(SUM(B287:F287,H287)=0,"",SUM(B287:F287,H287))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7374,11 +7401,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f>IF(SUM(B288:F288,H288)=0,"",SUM(B288:F288,H288))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7396,11 +7423,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f>IF(SUM(B289:F289,H289)=0,"",SUM(B289:F289,H289))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7418,11 +7445,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f>IF(SUM(B290:F290,H290)=0,"",SUM(B290:F290,H290))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7440,11 +7467,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f>IF(SUM(B291:F291,H291)=0,"",SUM(B291:F291,H291))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7462,11 +7489,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f>IF(SUM(B292:F292,H292)=0,"",SUM(B292:F292,H292))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7484,11 +7511,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f>IF(SUM(B293:F293,H293)=0,"",SUM(B293:F293,H293))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7506,11 +7533,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f>IF(SUM(B294:F294,H294)=0,"",SUM(B294:F294,H294))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7528,11 +7555,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f>IF(SUM(B295:F295,H295)=0,"",SUM(B295:F295,H295))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7550,11 +7577,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f>IF(SUM(B296:F296,H296)=0,"",SUM(B296:F296,H296))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7572,11 +7599,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f>IF(SUM(B297:F297,H297)=0,"",SUM(B297:F297,H297))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7594,11 +7621,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f>IF(SUM(B298:F298,H298)=0,"",SUM(B298:F298,H298))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7616,11 +7643,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f>IF(SUM(B299:F299,H299)=0,"",SUM(B299:F299,H299))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7638,11 +7665,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f>IF(SUM(B300:F300,H300)=0,"",SUM(B300:F300,H300))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7660,11 +7687,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f>IF(SUM(B301:F301,H301)=0,"",SUM(B301:F301,H301))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7682,11 +7709,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f>IF(SUM(B302:F302,H302)=0,"",SUM(B302:F302,H302))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7704,11 +7731,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f>IF(SUM(B303:F303,H303)=0,"",SUM(B303:F303,H303))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7726,11 +7753,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f>IF(SUM(B304:F304,H304)=0,"",SUM(B304:F304,H304))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7748,11 +7775,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f>IF(SUM(B305:F305,H305)=0,"",SUM(B305:F305,H305))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7770,11 +7797,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f>IF(SUM(B306:F306,H306)=0,"",SUM(B306:F306,H306))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7792,11 +7819,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f>IF(SUM(B307:F307,H307)=0,"",SUM(B307:F307,H307))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7814,11 +7841,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f>IF(SUM(B308:F308,H308)=0,"",SUM(B308:F308,H308))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7836,11 +7863,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f>IF(SUM(B309:F309,H309)=0,"",SUM(B309:F309,H309))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7858,11 +7885,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f>IF(SUM(B310:F310,H310)=0,"",SUM(B310:F310,H310))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7880,11 +7907,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f>IF(SUM(B311:F311,H311)=0,"",SUM(B311:F311,H311))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7902,11 +7929,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f>IF(SUM(B312:F312,H312)=0,"",SUM(B312:F312,H312))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -7924,11 +7951,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f>IF(SUM(B313:F313,H313)=0,"",SUM(B313:F313,H313))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -7946,11 +7973,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f>IF(SUM(B314:F314,H314)=0,"",SUM(B314:F314,H314))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -7968,11 +7995,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f>IF(SUM(B315:F315,H315)=0,"",SUM(B315:F315,H315))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -7990,11 +8017,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f>IF(SUM(B316:F316,H316)=0,"",SUM(B316:F316,H316))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8012,11 +8039,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f>IF(SUM(B317:F317,H317)=0,"",SUM(B317:F317,H317))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8034,11 +8061,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f>IF(SUM(B318:F318,H318)=0,"",SUM(B318:F318,H318))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8056,11 +8083,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f>IF(SUM(B319:F319,H319)=0,"",SUM(B319:F319,H319))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8078,11 +8105,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f>IF(SUM(B320:F320,H320)=0,"",SUM(B320:F320,H320))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8100,11 +8127,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f>IF(SUM(B321:F321,H321)=0,"",SUM(B321:F321,H321))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8122,11 +8149,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f>IF(SUM(B322:F322,H322)=0,"",SUM(B322:F322,H322))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8144,11 +8171,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f>IF(SUM(B323:F323,H323)=0,"",SUM(B323:F323,H323))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8166,11 +8193,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f>IF(SUM(B324:F324,H324)=0,"",SUM(B324:F324,H324))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8188,11 +8215,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f>IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8210,11 +8237,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f>IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="6">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8232,11 +8259,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f>IF(SUM(B327:F327,H327)=0,"",SUM(B327:F327,H327))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8254,11 +8281,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f>IF(SUM(B328:F328,H328)=0,"",SUM(B328:F328,H328))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8276,11 +8303,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f>IF(SUM(B329:F329,H329)=0,"",SUM(B329:F329,H329))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8298,11 +8325,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f>IF(SUM(B330:F330,H330)=0,"",SUM(B330:F330,H330))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8320,11 +8347,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f>IF(SUM(B331:F331,H331)=0,"",SUM(B331:F331,H331))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8342,11 +8369,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f>IF(SUM(B332:F332,H332)=0,"",SUM(B332:F332,H332))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8364,11 +8391,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f>IF(SUM(B333:F333,H333)=0,"",SUM(B333:F333,H333))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8386,11 +8413,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f>IF(SUM(B334:F334,H334)=0,"",SUM(B334:F334,H334))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8408,11 +8435,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f>IF(SUM(B335:F335,H335)=0,"",SUM(B335:F335,H335))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8430,11 +8457,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f>IF(SUM(B336:F336,H336)=0,"",SUM(B336:F336,H336))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8452,11 +8479,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f>IF(SUM(B337:F337,H337)=0,"",SUM(B337:F337,H337))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8474,11 +8501,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f>IF(SUM(B338:F338,H338)=0,"",SUM(B338:F338,H338))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8496,11 +8523,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f>IF(SUM(B339:F339,H339)=0,"",SUM(B339:F339,H339))</f>
+        <f t="shared" ref="I339:I402" si="12">IF(SUM(B339:F339,H339)=0,"",SUM(B339:F339,H339))</f>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8518,11 +8545,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f>IF(SUM(B340:F340,H340)=0,"",SUM(B340:F340,H340))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8540,11 +8567,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f>IF(SUM(B341:F341,H341)=0,"",SUM(B341:F341,H341))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8562,11 +8589,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f>IF(SUM(B342:F342,H342)=0,"",SUM(B342:F342,H342))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8584,11 +8611,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f>IF(SUM(B343:F343,H343)=0,"",SUM(B343:F343,H343))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8606,11 +8633,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f>IF(SUM(B344:F344,H344)=0,"",SUM(B344:F344,H344))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8628,11 +8655,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f>IF(SUM(B345:F345,H345)=0,"",SUM(B345:F345,H345))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8650,11 +8677,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f>IF(SUM(B346:F346,H346)=0,"",SUM(B346:F346,H346))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8672,11 +8699,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f>IF(SUM(B347:F347,H347)=0,"",SUM(B347:F347,H347))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8694,11 +8721,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f>IF(SUM(B348:F348,H348)=0,"",SUM(B348:F348,H348))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8716,11 +8743,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f>IF(SUM(B349:F349,H349)=0,"",SUM(B349:F349,H349))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8738,11 +8765,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f>IF(SUM(B350:F350,H350)=0,"",SUM(B350:F350,H350))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8760,11 +8787,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f>IF(SUM(B351:F351,H351)=0,"",SUM(B351:F351,H351))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8782,11 +8809,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f>IF(SUM(B352:F352,H352)=0,"",SUM(B352:F352,H352))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8804,11 +8831,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f>IF(SUM(B353:F353,H353)=0,"",SUM(B353:F353,H353))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8826,11 +8853,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f>IF(SUM(B354:F354,H354)=0,"",SUM(B354:F354,H354))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8848,11 +8875,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f>IF(SUM(B355:F355,H355)=0,"",SUM(B355:F355,H355))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8870,11 +8897,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f>IF(SUM(B356:F356,H356)=0,"",SUM(B356:F356,H356))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8892,11 +8919,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f>IF(SUM(B357:F357,H357)=0,"",SUM(B357:F357,H357))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8914,11 +8941,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f>IF(SUM(B358:F358,H358)=0,"",SUM(B358:F358,H358))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -8936,11 +8963,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f>IF(SUM(B359:F359,H359)=0,"",SUM(B359:F359,H359))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -8958,11 +8985,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f>IF(SUM(B360:F360,H360)=0,"",SUM(B360:F360,H360))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -8980,11 +9007,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f>IF(SUM(B361:F361,H361)=0,"",SUM(B361:F361,H361))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9002,11 +9029,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f>IF(SUM(B362:F362,H362)=0,"",SUM(B362:F362,H362))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9024,11 +9051,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f>IF(SUM(B363:F363,H363)=0,"",SUM(B363:F363,H363))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9046,11 +9073,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f>IF(SUM(B364:F364,H364)=0,"",SUM(B364:F364,H364))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9068,11 +9095,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f>IF(SUM(B365:F365,H365)=0,"",SUM(B365:F365,H365))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9090,11 +9117,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f>IF(SUM(B366:F366,H366)=0,"",SUM(B366:F366,H366))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9112,11 +9139,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f>IF(SUM(B367:F367,H367)=0,"",SUM(B367:F367,H367))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9134,11 +9161,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f>IF(SUM(B368:F368,H368)=0,"",SUM(B368:F368,H368))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9156,11 +9183,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f>IF(SUM(B369:F369,H369)=0,"",SUM(B369:F369,H369))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9178,11 +9205,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f>IF(SUM(B370:F370,H370)=0,"",SUM(B370:F370,H370))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9200,11 +9227,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f>IF(SUM(B371:F371,H371)=0,"",SUM(B371:F371,H371))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9222,11 +9249,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f>IF(SUM(B372:F372,H372)=0,"",SUM(B372:F372,H372))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9244,11 +9271,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f>IF(SUM(B373:F373,H373)=0,"",SUM(B373:F373,H373))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9266,11 +9293,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f>IF(SUM(B374:F374,H374)=0,"",SUM(B374:F374,H374))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9288,11 +9315,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f>IF(SUM(B375:F375,H375)=0,"",SUM(B375:F375,H375))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9310,11 +9337,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f>IF(SUM(B376:F376,H376)=0,"",SUM(B376:F376,H376))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9332,11 +9359,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f>IF(SUM(B377:F377,H377)=0,"",SUM(B377:F377,H377))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9354,11 +9381,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f>IF(SUM(B378:F378,H378)=0,"",SUM(B378:F378,H378))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9376,11 +9403,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f>IF(SUM(B379:F379,H379)=0,"",SUM(B379:F379,H379))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9398,11 +9425,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f>IF(SUM(B380:F380,H380)=0,"",SUM(B380:F380,H380))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9420,11 +9447,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f>IF(SUM(B381:F381,H381)=0,"",SUM(B381:F381,H381))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9442,11 +9469,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f>IF(SUM(B382:F382,H382)=0,"",SUM(B382:F382,H382))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9464,11 +9491,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f>IF(SUM(B383:F383,H383)=0,"",SUM(B383:F383,H383))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9486,11 +9513,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f>IF(SUM(B384:F384,H384)=0,"",SUM(B384:F384,H384))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9508,11 +9535,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f>IF(SUM(B385:F385,H385)=0,"",SUM(B385:F385,H385))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9530,11 +9557,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f>IF(SUM(B386:F386,H386)=0,"",SUM(B386:F386,H386))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9552,11 +9579,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f>IF(SUM(B387:F387,H387)=0,"",SUM(B387:F387,H387))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9574,11 +9601,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f>IF(SUM(B388:F388,H388)=0,"",SUM(B388:F388,H388))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9596,11 +9623,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f>IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9618,11 +9645,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f>IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="7">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9640,11 +9667,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f>IF(SUM(B391:F391,H391)=0,"",SUM(B391:F391,H391))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9662,11 +9689,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f>IF(SUM(B392:F392,H392)=0,"",SUM(B392:F392,H392))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9684,11 +9711,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f>IF(SUM(B393:F393,H393)=0,"",SUM(B393:F393,H393))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9706,11 +9733,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f>IF(SUM(B394:F394,H394)=0,"",SUM(B394:F394,H394))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9728,11 +9755,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f>IF(SUM(B395:F395,H395)=0,"",SUM(B395:F395,H395))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9750,11 +9777,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f>IF(SUM(B396:F396,H396)=0,"",SUM(B396:F396,H396))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9772,11 +9799,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f>IF(SUM(B397:F397,H397)=0,"",SUM(B397:F397,H397))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9794,11 +9821,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f>IF(SUM(B398:F398,H398)=0,"",SUM(B398:F398,H398))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9816,11 +9843,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f>IF(SUM(B399:F399,H399)=0,"",SUM(B399:F399,H399))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9838,11 +9865,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f>IF(SUM(B400:F400,H400)=0,"",SUM(B400:F400,H400))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9860,11 +9887,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f>IF(SUM(B401:F401,H401)=0,"",SUM(B401:F401,H401))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7949AC-5C81-4742-A091-DE22FF9CF158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E758492-1768-45B3-9150-CD20CEDD6A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>A normal Day.</t>
+  </si>
+  <si>
+    <t>Feel energetic because we have only 3 classes today.</t>
   </si>
 </sst>
 </file>
@@ -1341,27 +1344,51 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="9">
+        <v>270</v>
+      </c>
+      <c r="C13" s="9">
+        <v>65</v>
+      </c>
+      <c r="D13" s="9">
+        <v>150</v>
+      </c>
+      <c r="E13" s="9">
+        <v>100</v>
+      </c>
+      <c r="F13" s="9">
+        <v>150</v>
+      </c>
+      <c r="G13" s="9">
+        <v>3</v>
+      </c>
+      <c r="H13" s="9">
+        <v>200</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>935</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>505</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
@@ -8523,7 +8550,7 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" ref="I339:I402" si="12">IF(SUM(B339:F339,H339)=0,"",SUM(B339:F339,H339))</f>
+        <f t="shared" ref="I339:I401" si="12">IF(SUM(B339:F339,H339)=0,"",SUM(B339:F339,H339))</f>
         <v/>
       </c>
       <c r="J339" s="15" t="str">

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E758492-1768-45B3-9150-CD20CEDD6A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE58F938-D333-4454-BFD3-026E60038963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -243,6 +243,12 @@
   <si>
     <t>Feel energetic because we have only 3 classes today.</t>
   </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Feeling very tired due to heavy schedule.</t>
+  </si>
 </sst>
 </file>
 
@@ -251,7 +257,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +337,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -423,7 +436,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -892,7 +907,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N400"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1048,11 +1063,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I18" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I17" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1015</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
         <v>425</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1390,27 +1405,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="9">
+        <v>450</v>
+      </c>
+      <c r="C14" s="9">
+        <v>80</v>
+      </c>
+      <c r="D14" s="9">
+        <v>70</v>
+      </c>
+      <c r="E14" s="9">
+        <v>150</v>
+      </c>
+      <c r="F14" s="9">
+        <v>8</v>
+      </c>
+      <c r="G14" s="9">
+        <v>400</v>
+      </c>
+      <c r="H14" s="9">
+        <v>150</v>
+      </c>
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>908</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>532</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
@@ -1488,7 +1527,7 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
       <c r="I18" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I18:I81" si="2">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
         <v/>
       </c>
       <c r="J18" s="15" t="str">
@@ -1510,7 +1549,7 @@
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
       <c r="I19" s="15" t="str">
-        <f t="shared" ref="I19:I82" si="2">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J19" s="15" t="str">
@@ -2614,7 +2653,7 @@
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -2636,7 +2675,7 @@
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2896,7 +2935,7 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I82:I145" si="4">IF(SUM(B82:F82,H82)=0,"",SUM(B82:F82,H82))</f>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
@@ -2918,7 +2957,7 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" ref="I83:I146" si="4">IF(SUM(B83:F83,H83)=0,"",SUM(B83:F83,H83))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
@@ -4022,7 +4061,7 @@
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4044,7 +4083,7 @@
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4304,7 +4343,7 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I146:I209" si="6">IF(SUM(B146:F146,H146)=0,"",SUM(B146:F146,H146))</f>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
@@ -4326,7 +4365,7 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" ref="I147:I210" si="6">IF(SUM(B147:F147,H147)=0,"",SUM(B147:F147,H147))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
@@ -5430,7 +5469,7 @@
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5452,7 +5491,7 @@
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5712,7 +5751,7 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I210:I273" si="8">IF(SUM(B210:F210,H210)=0,"",SUM(B210:F210,H210))</f>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
@@ -5734,7 +5773,7 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" ref="I211:I274" si="8">IF(SUM(B211:F211,H211)=0,"",SUM(B211:F211,H211))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
@@ -6838,7 +6877,7 @@
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6860,7 +6899,7 @@
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7120,7 +7159,7 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I274:I337" si="10">IF(SUM(B274:F274,H274)=0,"",SUM(B274:F274,H274))</f>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
@@ -7142,7 +7181,7 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" ref="I275:I338" si="10">IF(SUM(B275:F275,H275)=0,"",SUM(B275:F275,H275))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
@@ -8246,7 +8285,7 @@
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8268,7 +8307,7 @@
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8528,7 +8567,7 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I338:I400" si="12">IF(SUM(B338:F338,H338)=0,"",SUM(B338:F338,H338))</f>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
@@ -8550,7 +8589,7 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" ref="I339:I401" si="12">IF(SUM(B339:F339,H339)=0,"",SUM(B339:F339,H339))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
@@ -9654,7 +9693,7 @@
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9676,7 +9715,7 @@
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9904,28 +9943,6 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -9935,26 +9952,26 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J400">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE58F938-D333-4454-BFD3-026E60038963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90183FAB-57D4-4B08-9935-3742DD78B6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,13 +241,34 @@
     <t>A normal Day.</t>
   </si>
   <si>
-    <t>Feel energetic because we have only 3 classes today.</t>
-  </si>
-  <si>
     <t>Unsatisfied</t>
   </si>
   <si>
     <t>Feeling very tired due to heavy schedule.</t>
+  </si>
+  <si>
+    <t>Feeling happy.</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Feel energetic because we had only 3 classes today.</t>
+  </si>
+  <si>
+    <t>Feeling low because I am away from home and today is Rakhi.</t>
+  </si>
+  <si>
+    <t>Not at All</t>
+  </si>
+  <si>
+    <t>Not At All</t>
+  </si>
+  <si>
+    <t>Very ttred due to room shift.</t>
+  </si>
+  <si>
+    <t>A hectic day</t>
   </si>
 </sst>
 </file>
@@ -1402,7 +1423,7 @@
         <v>54</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1442,193 +1463,359 @@
         <v>63</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>63</v>
       </c>
       <c r="N14" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="9">
+        <v>320</v>
+      </c>
+      <c r="C15" s="9">
+        <v>100</v>
+      </c>
+      <c r="D15" s="9">
+        <v>300</v>
+      </c>
+      <c r="E15" s="9">
+        <v>90</v>
+      </c>
+      <c r="F15" s="9">
+        <v>3</v>
+      </c>
+      <c r="G15" s="9">
+        <v>150</v>
+      </c>
+      <c r="H15" s="9">
+        <v>150</v>
+      </c>
+      <c r="I15" s="10">
+        <f t="shared" si="0"/>
+        <v>963</v>
+      </c>
+      <c r="J15" s="10">
+        <f t="shared" si="1"/>
+        <v>477</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="12" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    <row r="16" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B16" s="9">
+        <v>300</v>
+      </c>
+      <c r="C16" s="9">
+        <v>120</v>
+      </c>
+      <c r="D16" s="9">
+        <v>60</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>250</v>
+      </c>
+      <c r="G16" s="9">
+        <v>5</v>
+      </c>
+      <c r="H16" s="9">
+        <v>150</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+        <v>560</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="9">
+        <v>350</v>
+      </c>
+      <c r="C17" s="9">
+        <v>60</v>
+      </c>
+      <c r="D17" s="9">
+        <v>300</v>
+      </c>
+      <c r="E17" s="9">
+        <v>120</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>250</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B18" s="9">
+        <v>440</v>
+      </c>
+      <c r="C18" s="9">
+        <v>45</v>
+      </c>
+      <c r="D18" s="9">
+        <v>270</v>
+      </c>
+      <c r="E18" s="9">
+        <v>90</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>400</v>
+      </c>
+      <c r="I18" s="10">
+        <f t="shared" ref="I18:I81" si="2">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
+        <v>1245</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
-        <f t="shared" ref="I18:I81" si="2">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>195</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="9">
+        <v>230</v>
+      </c>
+      <c r="C19" s="9">
+        <v>90</v>
+      </c>
+      <c r="D19" s="9">
+        <v>90</v>
+      </c>
+      <c r="E19" s="9">
+        <v>120</v>
+      </c>
+      <c r="F19" s="9">
+        <v>300</v>
+      </c>
+      <c r="G19" s="9">
+        <v>6</v>
+      </c>
+      <c r="H19" s="9">
+        <v>270</v>
+      </c>
+      <c r="I19" s="10">
+        <f t="shared" si="2"/>
+        <v>1100</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J19" s="15" t="str">
+      <c r="J20" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="9">
+        <v>450</v>
+      </c>
+      <c r="C21" s="9">
+        <v>80</v>
+      </c>
+      <c r="D21" s="9">
+        <v>130</v>
+      </c>
+      <c r="E21" s="9">
+        <v>45</v>
+      </c>
+      <c r="F21" s="9">
+        <v>150</v>
+      </c>
+      <c r="G21" s="9">
+        <v>3</v>
+      </c>
+      <c r="H21" s="9">
+        <v>260</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1115</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+        <v>325</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="9">
+        <v>400</v>
+      </c>
+      <c r="C22" s="9">
+        <v>35</v>
+      </c>
+      <c r="D22" s="9">
+        <v>150</v>
+      </c>
+      <c r="E22" s="9">
+        <v>100</v>
+      </c>
+      <c r="F22" s="9">
+        <v>400</v>
+      </c>
+      <c r="G22" s="9">
+        <v>8</v>
+      </c>
+      <c r="H22" s="9">
+        <v>90</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>265</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
+      <c r="A23" s="8"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90183FAB-57D4-4B08-9935-3742DD78B6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C45A52-2BAB-4686-B35D-388779A043E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -270,6 +270,12 @@
   <si>
     <t>A hectic day</t>
   </si>
+  <si>
+    <t>Just a normal day.</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
 </sst>
 </file>
 
@@ -367,7 +373,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -386,8 +392,20 @@
         <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -410,11 +428,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -460,11 +530,101 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -928,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N400"/>
+  <dimension ref="A1:N404"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1088,7 +1248,7 @@
         <v>1015</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J72" si="1">IF(I6="","",1440-I6)</f>
         <v>425</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1636,7 +1796,7 @@
         <v>400</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" ref="I18:I81" si="2">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
+        <f t="shared" ref="I18:I85" si="2">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
         <v>1245</v>
       </c>
       <c r="J18" s="10">
@@ -1657,48 +1817,48 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+      <c r="A19" s="21">
         <v>46265</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="22">
         <v>230</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="22">
         <v>90</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="22">
         <v>90</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="22">
         <v>120</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="22">
         <v>300</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="22">
         <v>6</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="22">
         <v>270</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="23">
         <f t="shared" si="2"/>
         <v>1100</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="23">
         <f t="shared" si="1"/>
         <v>340</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="M19" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="N19" s="12" t="s">
+      <c r="N19" s="25" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1711,218 +1871,222 @@
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
       <c r="N20" s="12"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+    <row r="21" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="31"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" spans="1:14" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="34"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="40"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+    </row>
+    <row r="23" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="31"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="15" t="str">
+        <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="15" t="str">
+        <f>IF(I23="","",1440-I23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="12"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="26">
         <v>46266</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B25" s="27">
         <v>450</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C25" s="27">
         <v>80</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D25" s="27">
         <v>130</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E25" s="27">
         <v>45</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F25" s="27">
         <v>150</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G25" s="27">
         <v>3</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H25" s="27">
         <v>260</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I25" s="28">
         <f t="shared" si="2"/>
         <v>1115</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J25" s="28">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K25" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L25" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="M21" s="11" t="s">
+      <c r="M25" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="N21" s="12"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
+      <c r="N25" s="30"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
         <v>46267</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B26" s="9">
         <v>400</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C26" s="9">
         <v>35</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D26" s="9">
         <v>150</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E26" s="9">
         <v>100</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F26" s="9">
         <v>400</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G26" s="9">
         <v>8</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H26" s="9">
         <v>90</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I26" s="10">
         <f t="shared" si="2"/>
         <v>1175</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
         <v>265</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K26" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L26" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M22" s="11" t="s">
+      <c r="M26" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="N22" s="12" t="s">
+      <c r="N26" s="12" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B27" s="9">
+        <v>420</v>
+      </c>
+      <c r="C27" s="9">
+        <v>150</v>
+      </c>
+      <c r="D27" s="9">
+        <v>60</v>
+      </c>
+      <c r="E27" s="9">
+        <v>100</v>
+      </c>
+      <c r="F27" s="9">
+        <v>300</v>
+      </c>
+      <c r="G27" s="9">
+        <v>6</v>
+      </c>
+      <c r="H27" s="9">
+        <v>80</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
@@ -2840,7 +3004,7 @@
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -2862,7 +3026,7 @@
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2884,7 +3048,7 @@
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2906,7 +3070,7 @@
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2928,7 +3092,7 @@
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J73:J136" si="3">IF(I73="","",1440-I73)</f>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3122,7 +3286,7 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" ref="I82:I145" si="4">IF(SUM(B82:F82,H82)=0,"",SUM(B82:F82,H82))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
@@ -3144,7 +3308,7 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
@@ -3166,7 +3330,7 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
@@ -3188,7 +3352,7 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
@@ -3210,7 +3374,7 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I86:I149" si="4">IF(SUM(B86:F86,H86)=0,"",SUM(B86:F86,H86))</f>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
@@ -4248,7 +4412,7 @@
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4270,7 +4434,7 @@
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4292,7 +4456,7 @@
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4314,7 +4478,7 @@
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4336,7 +4500,7 @@
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J137:J200" si="5">IF(I137="","",1440-I137)</f>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4530,7 +4694,7 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" ref="I146:I209" si="6">IF(SUM(B146:F146,H146)=0,"",SUM(B146:F146,H146))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
@@ -4552,7 +4716,7 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
@@ -4574,7 +4738,7 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
@@ -4596,7 +4760,7 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
@@ -4618,7 +4782,7 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I150:I213" si="6">IF(SUM(B150:F150,H150)=0,"",SUM(B150:F150,H150))</f>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
@@ -5656,7 +5820,7 @@
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5678,7 +5842,7 @@
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5700,7 +5864,7 @@
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5722,7 +5886,7 @@
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5744,7 +5908,7 @@
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J201:J264" si="7">IF(I201="","",1440-I201)</f>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5938,7 +6102,7 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" ref="I210:I273" si="8">IF(SUM(B210:F210,H210)=0,"",SUM(B210:F210,H210))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
@@ -5960,7 +6124,7 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
@@ -5982,7 +6146,7 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
@@ -6004,7 +6168,7 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
@@ -6026,7 +6190,7 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I214:I277" si="8">IF(SUM(B214:F214,H214)=0,"",SUM(B214:F214,H214))</f>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
@@ -7064,7 +7228,7 @@
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7086,7 +7250,7 @@
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7108,7 +7272,7 @@
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7130,7 +7294,7 @@
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7152,7 +7316,7 @@
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J265:J328" si="9">IF(I265="","",1440-I265)</f>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7346,7 +7510,7 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" ref="I274:I337" si="10">IF(SUM(B274:F274,H274)=0,"",SUM(B274:F274,H274))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
@@ -7368,7 +7532,7 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
@@ -7390,7 +7554,7 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
@@ -7412,7 +7576,7 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
@@ -7434,7 +7598,7 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I278:I341" si="10">IF(SUM(B278:F278,H278)=0,"",SUM(B278:F278,H278))</f>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
@@ -8472,7 +8636,7 @@
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8494,7 +8658,7 @@
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8516,7 +8680,7 @@
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8538,7 +8702,7 @@
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8560,7 +8724,7 @@
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J329:J392" si="11">IF(I329="","",1440-I329)</f>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8754,7 +8918,7 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" ref="I338:I400" si="12">IF(SUM(B338:F338,H338)=0,"",SUM(B338:F338,H338))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
@@ -8776,7 +8940,7 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
@@ -8798,7 +8962,7 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
@@ -8820,7 +8984,7 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
@@ -8842,7 +9006,7 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I342:I404" si="12">IF(SUM(B342:F342,H342)=0,"",SUM(B342:F342,H342))</f>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
@@ -9880,7 +10044,7 @@
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9902,7 +10066,7 @@
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9924,7 +10088,7 @@
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9946,7 +10110,7 @@
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9968,7 +10132,7 @@
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J393:J404" si="13">IF(I393="","",1440-I393)</f>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10130,8 +10294,97 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
+    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A401" s="13"/>
+      <c r="B401" s="14"/>
+      <c r="C401" s="14"/>
+      <c r="D401" s="14"/>
+      <c r="E401" s="14"/>
+      <c r="F401" s="14"/>
+      <c r="G401" s="14"/>
+      <c r="H401" s="14"/>
+      <c r="I401" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J401" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K401" s="16"/>
+      <c r="L401" s="16"/>
+      <c r="M401" s="16"/>
+      <c r="N401" s="17"/>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A404" s="13"/>
+      <c r="B404" s="14"/>
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J404" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K404" s="16"/>
+      <c r="L404" s="16"/>
+      <c r="M404" s="16"/>
+      <c r="N404" s="17"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B2:D2"/>
@@ -10139,21 +10392,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J400">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J6:J20 J24:J404 I21:J23">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K404" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L404" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M404" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C45A52-2BAB-4686-B35D-388779A043E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9FFAAE-6A77-478D-8517-4C00A9603F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -276,6 +276,12 @@
   <si>
     <t>September</t>
   </si>
+  <si>
+    <t>Enjoy the holiday and prepaqre for Cas.</t>
+  </si>
+  <si>
+    <t>Enjoy.</t>
+  </si>
 </sst>
 </file>
 
@@ -484,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -525,11 +531,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -560,71 +561,39 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1105,74 +1074,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="39">
         <v>12616871</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="39"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1817,48 +1786,48 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="21">
+      <c r="A19" s="18">
         <v>46265</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="19">
         <v>230</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="19">
         <v>90</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="19">
         <v>90</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="19">
         <v>120</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="19">
         <v>300</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="19">
         <v>6</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="19">
         <v>270</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="20">
         <f t="shared" si="2"/>
         <v>1100</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="20">
         <f t="shared" si="1"/>
         <v>340</v>
       </c>
-      <c r="K19" s="24" t="s">
+      <c r="K19" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="L19" s="24" t="s">
+      <c r="L19" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="M19" s="24" t="s">
+      <c r="M19" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="N19" s="25" t="s">
+      <c r="N19" s="22" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1878,15 +1847,15 @@
       <c r="M20" s="11"/>
       <c r="N20" s="12"/>
     </row>
-    <row r="21" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="31"/>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="28"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
       <c r="K21" s="12"/>
@@ -1894,35 +1863,35 @@
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
     </row>
-    <row r="22" spans="1:14" s="38" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="34"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
+    <row r="22" spans="1:14" s="34" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="30"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
       <c r="E22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="39" t="s">
+      <c r="F22" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="G22" s="40"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-    </row>
-    <row r="23" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="31"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="28"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
       <c r="I23" s="15" t="str">
         <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
         <v/>
@@ -1953,48 +1922,48 @@
       <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="26">
+      <c r="A25" s="23">
         <v>46266</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="24">
         <v>450</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="24">
         <v>80</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="24">
         <v>130</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="24">
         <v>45</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="24">
         <v>150</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="24">
         <v>3</v>
       </c>
-      <c r="H25" s="27">
+      <c r="H25" s="24">
         <v>260</v>
       </c>
-      <c r="I25" s="28">
+      <c r="I25" s="25">
         <f t="shared" si="2"/>
         <v>1115</v>
       </c>
-      <c r="J25" s="28">
+      <c r="J25" s="25">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="K25" s="29" t="s">
+      <c r="K25" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L25" s="29" t="s">
+      <c r="L25" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="M25" s="29" t="s">
+      <c r="M25" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="N25" s="30"/>
+      <c r="N25" s="27"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
@@ -2089,400 +2058,472 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B28" s="9">
+        <v>370</v>
+      </c>
+      <c r="C28" s="9">
+        <v>180</v>
+      </c>
+      <c r="D28" s="9">
+        <v>180</v>
+      </c>
+      <c r="E28" s="9">
+        <v>70</v>
+      </c>
+      <c r="F28" s="9">
+        <v>250</v>
+      </c>
+      <c r="G28" s="9">
+        <v>5</v>
+      </c>
+      <c r="H28" s="9">
+        <v>100</v>
+      </c>
+      <c r="I28" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B29" s="9">
+        <v>500</v>
+      </c>
+      <c r="C29" s="9">
+        <v>200</v>
+      </c>
+      <c r="D29" s="9">
+        <v>120</v>
+      </c>
+      <c r="E29" s="9">
+        <v>60</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>190</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+        <v>370</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B30" s="9">
+        <v>385</v>
+      </c>
+      <c r="C30" s="9">
+        <v>135</v>
+      </c>
+      <c r="D30" s="9">
+        <v>200</v>
+      </c>
+      <c r="E30" s="9">
+        <v>120</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>150</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J31" s="15" t="str">
+      <c r="J31" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J32" s="15" t="str">
+      <c r="J32" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="12"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J33" s="15" t="str">
+      <c r="J33" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="12"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J34" s="15" t="str">
+      <c r="J34" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="12"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J35" s="15" t="str">
+      <c r="J35" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="12"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J36" s="15" t="str">
+      <c r="J36" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J37" s="15" t="str">
+      <c r="J37" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="12"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J38" s="15" t="str">
+      <c r="J38" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="12"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="8"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J39" s="15" t="str">
+      <c r="J39" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="12"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J40" s="15" t="str">
+      <c r="J40" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="12"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J41" s="15" t="str">
+      <c r="J41" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="12"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J42" s="15" t="str">
+      <c r="J42" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="12"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="8"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J43" s="15" t="str">
+      <c r="J43" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="12"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J44" s="15" t="str">
+      <c r="J44" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="8"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J45" s="15" t="str">
+      <c r="J45" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="12"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
@@ -10392,8 +10433,8 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J20 J24:J404 I21:J23">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="J6:J20 I21:J23 J24:J404">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9FFAAE-6A77-478D-8517-4C00A9603F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7327F979-527B-4A49-901E-75FBB5167CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>Enjoy.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>To much word done by today evening.</t>
   </si>
 </sst>
 </file>
@@ -2196,48 +2202,94 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+      <c r="A31" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B31" s="9">
+        <v>400</v>
+      </c>
+      <c r="C31" s="9">
+        <v>180</v>
+      </c>
+      <c r="D31" s="9">
+        <v>150</v>
+      </c>
+      <c r="E31" s="9">
+        <v>100</v>
+      </c>
+      <c r="F31" s="9">
+        <v>300</v>
+      </c>
+      <c r="G31" s="9">
+        <v>6</v>
+      </c>
+      <c r="H31" s="9">
+        <v>215</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>1345</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
+        <v>95</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N31" s="12"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B32" s="9">
+        <v>480</v>
+      </c>
+      <c r="C32" s="9">
+        <v>120</v>
+      </c>
+      <c r="D32" s="9">
+        <v>60</v>
+      </c>
+      <c r="E32" s="9">
+        <v>20</v>
+      </c>
+      <c r="F32" s="9">
+        <v>150</v>
+      </c>
+      <c r="G32" s="9">
+        <v>3</v>
+      </c>
+      <c r="H32" s="9">
+        <v>240</v>
+      </c>
+      <c r="I32" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J32" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
+        <v>370</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7327F979-527B-4A49-901E-75FBB5167CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E01DDA-CE50-41AD-86DC-B7F577FEC9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,19 +274,19 @@
     <t>Just a normal day.</t>
   </si>
   <si>
-    <t>September</t>
-  </si>
-  <si>
-    <t>Enjoy the holiday and prepaqre for Cas.</t>
-  </si>
-  <si>
     <t>Enjoy.</t>
   </si>
   <si>
     <t>Stressed</t>
   </si>
   <si>
-    <t>To much word done by today evening.</t>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>To much work done by today evening.</t>
+  </si>
+  <si>
+    <t>Enjoy the holiday and prepaqre for Ca's.</t>
   </si>
 </sst>
 </file>
@@ -385,7 +385,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -404,20 +404,8 @@
         <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -466,37 +454,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB7B7B7"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFB7B7B7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB7B7B7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB7B7B7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -566,29 +528,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1063,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N404"/>
+  <dimension ref="A1:N399"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1080,74 +1019,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="39">
+      <c r="F2" s="30">
         <v>12616871</v>
       </c>
-      <c r="G2" s="39"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="39"/>
+      <c r="G3" s="30"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1223,7 +1162,7 @@
         <v>1015</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J72" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J67" si="1">IF(I6="","",1440-I6)</f>
         <v>425</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1771,7 +1710,7 @@
         <v>400</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" ref="I18:I85" si="2">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
+        <f t="shared" ref="I18:I80" si="2">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
         <v>1245</v>
       </c>
       <c r="J18" s="10">
@@ -1838,148 +1777,288 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-    </row>
-    <row r="22" spans="1:14" s="34" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="30"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" s="36"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="15" t="str">
-        <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f>IF(I23="","",1440-I23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="23">
+      <c r="A20" s="23">
         <v>46266</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B20" s="24">
         <v>450</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C20" s="24">
         <v>80</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D20" s="24">
         <v>130</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E20" s="24">
         <v>45</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F20" s="24">
         <v>150</v>
       </c>
-      <c r="G25" s="24">
+      <c r="G20" s="24">
         <v>3</v>
       </c>
-      <c r="H25" s="24">
+      <c r="H20" s="24">
         <v>260</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I20" s="25">
         <f t="shared" si="2"/>
         <v>1115</v>
       </c>
-      <c r="J25" s="25">
+      <c r="J20" s="25">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="K25" s="26" t="s">
+      <c r="K20" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L25" s="26" t="s">
+      <c r="L20" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="M25" s="26" t="s">
+      <c r="M20" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="N25" s="27"/>
+      <c r="N20" s="27"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="9">
+        <v>400</v>
+      </c>
+      <c r="C21" s="9">
+        <v>35</v>
+      </c>
+      <c r="D21" s="9">
+        <v>150</v>
+      </c>
+      <c r="E21" s="9">
+        <v>100</v>
+      </c>
+      <c r="F21" s="9">
+        <v>400</v>
+      </c>
+      <c r="G21" s="9">
+        <v>8</v>
+      </c>
+      <c r="H21" s="9">
+        <v>90</v>
+      </c>
+      <c r="I21" s="10">
+        <f t="shared" si="2"/>
+        <v>1175</v>
+      </c>
+      <c r="J21" s="10">
+        <f t="shared" si="1"/>
+        <v>265</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="9">
+        <v>420</v>
+      </c>
+      <c r="C22" s="9">
+        <v>150</v>
+      </c>
+      <c r="D22" s="9">
+        <v>60</v>
+      </c>
+      <c r="E22" s="9">
+        <v>100</v>
+      </c>
+      <c r="F22" s="9">
+        <v>300</v>
+      </c>
+      <c r="G22" s="9">
+        <v>6</v>
+      </c>
+      <c r="H22" s="9">
+        <v>80</v>
+      </c>
+      <c r="I22" s="10">
+        <f t="shared" si="2"/>
+        <v>1110</v>
+      </c>
+      <c r="J22" s="10">
+        <f t="shared" si="1"/>
+        <v>330</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B23" s="9">
+        <v>370</v>
+      </c>
+      <c r="C23" s="9">
+        <v>180</v>
+      </c>
+      <c r="D23" s="9">
+        <v>180</v>
+      </c>
+      <c r="E23" s="9">
+        <v>70</v>
+      </c>
+      <c r="F23" s="9">
+        <v>250</v>
+      </c>
+      <c r="G23" s="9">
+        <v>5</v>
+      </c>
+      <c r="H23" s="9">
+        <v>100</v>
+      </c>
+      <c r="I23" s="10">
+        <f t="shared" si="2"/>
+        <v>1150</v>
+      </c>
+      <c r="J23" s="10">
+        <f t="shared" si="1"/>
+        <v>290</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B24" s="9">
+        <v>500</v>
+      </c>
+      <c r="C24" s="9">
+        <v>200</v>
+      </c>
+      <c r="D24" s="9">
+        <v>120</v>
+      </c>
+      <c r="E24" s="9">
+        <v>60</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>190</v>
+      </c>
+      <c r="I24" s="10">
+        <f t="shared" si="2"/>
+        <v>1070</v>
+      </c>
+      <c r="J24" s="10">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B25" s="9">
+        <v>385</v>
+      </c>
+      <c r="C25" s="9">
+        <v>135</v>
+      </c>
+      <c r="D25" s="9">
+        <v>200</v>
+      </c>
+      <c r="E25" s="9">
+        <v>120</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>150</v>
+      </c>
+      <c r="I25" s="10">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="J25" s="10">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B26" s="9">
         <v>400</v>
       </c>
       <c r="C26" s="9">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="D26" s="9">
         <v>150</v>
@@ -1988,113 +2067,111 @@
         <v>100</v>
       </c>
       <c r="F26" s="9">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G26" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H26" s="9">
-        <v>90</v>
+        <v>215</v>
       </c>
       <c r="I26" s="10">
         <f t="shared" si="2"/>
-        <v>1175</v>
+        <v>1345</v>
       </c>
       <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>95</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="N26" s="12"/>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B27" s="9">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C27" s="9">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D27" s="9">
         <v>60</v>
       </c>
       <c r="E27" s="9">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F27" s="9">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G27" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H27" s="9">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="I27" s="10">
         <f t="shared" si="2"/>
-        <v>1110</v>
+        <v>1070</v>
       </c>
       <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B28" s="9">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="C28" s="9">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="D28" s="9">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E28" s="9">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="F28" s="9">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="G28" s="9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H28" s="9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I28" s="10">
         <f t="shared" si="2"/>
-        <v>1150</v>
+        <v>1230</v>
       </c>
       <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>49</v>
@@ -2106,190 +2183,98 @@
         <v>51</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
-        <v>46270</v>
-      </c>
-      <c r="B29" s="9">
-        <v>500</v>
-      </c>
-      <c r="C29" s="9">
-        <v>200</v>
-      </c>
-      <c r="D29" s="9">
-        <v>120</v>
-      </c>
-      <c r="E29" s="9">
-        <v>60</v>
-      </c>
-      <c r="F29" s="9">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9">
-        <v>0</v>
-      </c>
-      <c r="H29" s="9">
-        <v>190</v>
-      </c>
-      <c r="I29" s="10">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>1070</v>
-      </c>
-      <c r="J29" s="10">
+        <v/>
+      </c>
+      <c r="J29" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>370</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N29" s="12" t="s">
+        <v/>
+      </c>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="12"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J30" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="12"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
-        <v>46271</v>
-      </c>
-      <c r="B30" s="9">
-        <v>385</v>
-      </c>
-      <c r="C30" s="9">
-        <v>135</v>
-      </c>
-      <c r="D30" s="9">
-        <v>200</v>
-      </c>
-      <c r="E30" s="9">
-        <v>120</v>
-      </c>
-      <c r="F30" s="9">
-        <v>0</v>
-      </c>
-      <c r="G30" s="9">
-        <v>0</v>
-      </c>
-      <c r="H30" s="9">
-        <v>150</v>
-      </c>
-      <c r="I30" s="10">
+      <c r="H31" s="9"/>
+      <c r="I31" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>990</v>
-      </c>
-      <c r="J30" s="10">
+        <v/>
+      </c>
+      <c r="J31" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L30" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N30" s="12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
-        <v>46272</v>
-      </c>
-      <c r="B31" s="9">
-        <v>400</v>
-      </c>
-      <c r="C31" s="9">
-        <v>180</v>
-      </c>
-      <c r="D31" s="9">
-        <v>150</v>
-      </c>
-      <c r="E31" s="9">
-        <v>100</v>
-      </c>
-      <c r="F31" s="9">
-        <v>300</v>
-      </c>
-      <c r="G31" s="9">
-        <v>6</v>
-      </c>
-      <c r="H31" s="9">
-        <v>215</v>
-      </c>
-      <c r="I31" s="10">
+        <v/>
+      </c>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="12"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>1345</v>
-      </c>
-      <c r="J31" s="10">
+        <v/>
+      </c>
+      <c r="J32" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L31" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N31" s="12"/>
-    </row>
-    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
-        <v>46273</v>
-      </c>
-      <c r="B32" s="9">
-        <v>480</v>
-      </c>
-      <c r="C32" s="9">
-        <v>120</v>
-      </c>
-      <c r="D32" s="9">
-        <v>60</v>
-      </c>
-      <c r="E32" s="9">
-        <v>20</v>
-      </c>
-      <c r="F32" s="9">
-        <v>150</v>
-      </c>
-      <c r="G32" s="9">
-        <v>3</v>
-      </c>
-      <c r="H32" s="9">
-        <v>240</v>
-      </c>
-      <c r="I32" s="10">
-        <f t="shared" si="2"/>
-        <v>1070</v>
-      </c>
-      <c r="J32" s="10">
-        <f t="shared" si="1"/>
-        <v>370</v>
-      </c>
-      <c r="K32" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="L32" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="M32" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N32" s="12" t="s">
-        <v>83</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="12"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
@@ -2468,114 +2453,114 @@
       <c r="N40" s="12"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
+      <c r="A41" s="13"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J41" s="10" t="str">
+      <c r="J41" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
+      <c r="A42" s="13"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J42" s="10" t="str">
+      <c r="J42" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
+      <c r="A43" s="13"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J43" s="10" t="str">
+      <c r="J43" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
+      <c r="A44" s="13"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J44" s="10" t="str">
+      <c r="J44" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
+      <c r="A45" s="13"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J45" s="10" t="str">
+      <c r="J45" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
@@ -3075,7 +3060,7 @@
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J68:J131" si="3">IF(I68="","",1440-I68)</f>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -3097,7 +3082,7 @@
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3119,7 +3104,7 @@
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3141,7 +3126,7 @@
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3163,7 +3148,7 @@
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3185,7 +3170,7 @@
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" ref="J73:J136" si="3">IF(I73="","",1440-I73)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3357,7 +3342,7 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I81:I144" si="4">IF(SUM(B81:F81,H81)=0,"",SUM(B81:F81,H81))</f>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
@@ -3379,7 +3364,7 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
@@ -3401,7 +3386,7 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
@@ -3423,7 +3408,7 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
@@ -3445,7 +3430,7 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
@@ -3467,7 +3452,7 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" ref="I86:I149" si="4">IF(SUM(B86:F86,H86)=0,"",SUM(B86:F86,H86))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
@@ -4483,7 +4468,7 @@
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J132:J195" si="5">IF(I132="","",1440-I132)</f>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4505,7 +4490,7 @@
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4527,7 +4512,7 @@
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4549,7 +4534,7 @@
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4571,7 +4556,7 @@
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4593,7 +4578,7 @@
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" ref="J137:J200" si="5">IF(I137="","",1440-I137)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4765,7 +4750,7 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I145:I208" si="6">IF(SUM(B145:F145,H145)=0,"",SUM(B145:F145,H145))</f>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
@@ -4787,7 +4772,7 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
@@ -4809,7 +4794,7 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
@@ -4831,7 +4816,7 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
@@ -4853,7 +4838,7 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
@@ -4875,7 +4860,7 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" ref="I150:I213" si="6">IF(SUM(B150:F150,H150)=0,"",SUM(B150:F150,H150))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
@@ -5891,7 +5876,7 @@
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J196:J259" si="7">IF(I196="","",1440-I196)</f>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5913,7 +5898,7 @@
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5935,7 +5920,7 @@
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5957,7 +5942,7 @@
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5979,7 +5964,7 @@
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6001,7 +5986,7 @@
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" ref="J201:J264" si="7">IF(I201="","",1440-I201)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6173,7 +6158,7 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I209:I272" si="8">IF(SUM(B209:F209,H209)=0,"",SUM(B209:F209,H209))</f>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
@@ -6195,7 +6180,7 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
@@ -6217,7 +6202,7 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
@@ -6239,7 +6224,7 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
@@ -6261,7 +6246,7 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
@@ -6283,7 +6268,7 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" ref="I214:I277" si="8">IF(SUM(B214:F214,H214)=0,"",SUM(B214:F214,H214))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
@@ -7299,7 +7284,7 @@
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J260:J323" si="9">IF(I260="","",1440-I260)</f>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7321,7 +7306,7 @@
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7343,7 +7328,7 @@
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7365,7 +7350,7 @@
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7387,7 +7372,7 @@
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7409,7 +7394,7 @@
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" ref="J265:J328" si="9">IF(I265="","",1440-I265)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7581,7 +7566,7 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I273:I336" si="10">IF(SUM(B273:F273,H273)=0,"",SUM(B273:F273,H273))</f>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
@@ -7603,7 +7588,7 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
@@ -7625,7 +7610,7 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
@@ -7647,7 +7632,7 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
@@ -7669,7 +7654,7 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
@@ -7691,7 +7676,7 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" ref="I278:I341" si="10">IF(SUM(B278:F278,H278)=0,"",SUM(B278:F278,H278))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
@@ -8707,7 +8692,7 @@
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J324:J387" si="11">IF(I324="","",1440-I324)</f>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8729,7 +8714,7 @@
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8751,7 +8736,7 @@
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8773,7 +8758,7 @@
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8795,7 +8780,7 @@
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8817,7 +8802,7 @@
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" ref="J329:J392" si="11">IF(I329="","",1440-I329)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8989,7 +8974,7 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I337:I399" si="12">IF(SUM(B337:F337,H337)=0,"",SUM(B337:F337,H337))</f>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
@@ -9011,7 +8996,7 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
@@ -9033,7 +9018,7 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
@@ -9055,7 +9040,7 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
@@ -9077,7 +9062,7 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
@@ -9099,7 +9084,7 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" ref="I342:I404" si="12">IF(SUM(B342:F342,H342)=0,"",SUM(B342:F342,H342))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
@@ -10115,7 +10100,7 @@
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J388:J399" si="13">IF(I388="","",1440-I388)</f>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10137,7 +10122,7 @@
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10159,7 +10144,7 @@
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10181,7 +10166,7 @@
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10203,7 +10188,7 @@
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10225,7 +10210,7 @@
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" ref="J393:J404" si="13">IF(I393="","",1440-I393)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10365,119 +10350,8 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A400" s="13"/>
-      <c r="B400" s="14"/>
-      <c r="C400" s="14"/>
-      <c r="D400" s="14"/>
-      <c r="E400" s="14"/>
-      <c r="F400" s="14"/>
-      <c r="G400" s="14"/>
-      <c r="H400" s="14"/>
-      <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K400" s="16"/>
-      <c r="L400" s="16"/>
-      <c r="M400" s="16"/>
-      <c r="N400" s="17"/>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
-    </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A402" s="13"/>
-      <c r="B402" s="14"/>
-      <c r="C402" s="14"/>
-      <c r="D402" s="14"/>
-      <c r="E402" s="14"/>
-      <c r="F402" s="14"/>
-      <c r="G402" s="14"/>
-      <c r="H402" s="14"/>
-      <c r="I402" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J402" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K402" s="16"/>
-      <c r="L402" s="16"/>
-      <c r="M402" s="16"/>
-      <c r="N402" s="17"/>
-    </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A403" s="13"/>
-      <c r="B403" s="14"/>
-      <c r="C403" s="14"/>
-      <c r="D403" s="14"/>
-      <c r="E403" s="14"/>
-      <c r="F403" s="14"/>
-      <c r="G403" s="14"/>
-      <c r="H403" s="14"/>
-      <c r="I403" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J403" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K403" s="16"/>
-      <c r="L403" s="16"/>
-      <c r="M403" s="16"/>
-      <c r="N403" s="17"/>
-    </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A404" s="13"/>
-      <c r="B404" s="14"/>
-      <c r="C404" s="14"/>
-      <c r="D404" s="14"/>
-      <c r="E404" s="14"/>
-      <c r="F404" s="14"/>
-      <c r="G404" s="14"/>
-      <c r="H404" s="14"/>
-      <c r="I404" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J404" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K404" s="16"/>
-      <c r="L404" s="16"/>
-      <c r="M404" s="16"/>
-      <c r="N404" s="17"/>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F22:G22"/>
+  <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B2:D2"/>
@@ -10485,21 +10359,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J20 I21:J23 J24:J404">
+  <conditionalFormatting sqref="J6:J399">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K404" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K399" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L404" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L399" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M404" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M399" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E01DDA-CE50-41AD-86DC-B7F577FEC9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A38D32A-3BBD-4E73-8177-6E9B10E8EBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,13 +280,16 @@
     <t>Stressed</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
     <t>To much work done by today evening.</t>
   </si>
   <si>
     <t>Enjoy the holiday and prepaqre for Ca's.</t>
+  </si>
+  <si>
+    <t>Enjoy the Freshers' Party</t>
+  </si>
+  <si>
+    <t>The whole day was spent travelling.</t>
   </si>
 </sst>
 </file>
@@ -2047,7 +2050,7 @@
         <v>51</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2137,7 +2140,7 @@
         <v>63</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2187,72 +2190,142 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
+      <c r="A29" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="9">
+        <v>420</v>
+      </c>
+      <c r="C29" s="9">
+        <v>78</v>
+      </c>
+      <c r="D29" s="9">
+        <v>200</v>
+      </c>
+      <c r="E29" s="9">
+        <v>75</v>
+      </c>
+      <c r="F29" s="9">
+        <v>250</v>
+      </c>
+      <c r="G29" s="9">
+        <v>5</v>
+      </c>
+      <c r="H29" s="9">
+        <v>300</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
+        <v>1323</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
+        <v>117</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
+      <c r="A30" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="9">
+        <v>460</v>
+      </c>
+      <c r="C30" s="9">
+        <v>90</v>
+      </c>
+      <c r="D30" s="9">
+        <v>110</v>
+      </c>
+      <c r="E30" s="9">
+        <v>30</v>
+      </c>
+      <c r="F30" s="9">
+        <v>150</v>
+      </c>
+      <c r="G30" s="9">
+        <v>3</v>
+      </c>
+      <c r="H30" s="9">
+        <v>150</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
+        <v>990</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+        <v>450</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="9">
+        <v>300</v>
+      </c>
+      <c r="C31" s="9">
+        <v>30</v>
+      </c>
+      <c r="D31" s="9">
+        <v>60</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>120</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>510</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+        <v>930</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A38D32A-3BBD-4E73-8177-6E9B10E8EBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1CA0FC-DBD7-498E-88C9-1FD6B1BAD60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,18 @@
   </si>
   <si>
     <t>The whole day was spent travelling.</t>
+  </si>
+  <si>
+    <t>A heptic day as usual on every wednesday</t>
+  </si>
+  <si>
+    <t>Feeling blessed because participate in Ganpati Events.</t>
+  </si>
+  <si>
+    <t>Feeling happy because participate in Ganpati Events(Dandiya).</t>
+  </si>
+  <si>
+    <t>Visit a nearest mela.</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N399"/>
+  <dimension ref="A1:N404"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1135,1127 +1147,989 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="12"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="12"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>46249</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="12"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>46250</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="12"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="12"/>
+    </row>
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
         <v>46252</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B11" s="9">
         <v>480</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C11" s="9">
         <v>45</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D11" s="9">
         <v>120</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E11" s="9">
         <v>90</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F11" s="9">
         <v>250</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G11" s="9">
         <v>5</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H11" s="9">
         <v>30</v>
       </c>
-      <c r="I6" s="10">
-        <f t="shared" ref="I6:I17" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+      <c r="I11" s="10">
+        <f t="shared" ref="I11:I22" si="0">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
         <v>1015</v>
       </c>
-      <c r="J6" s="10">
-        <f t="shared" ref="J6:J67" si="1">IF(I6="","",1440-I6)</f>
+      <c r="J11" s="10">
+        <f t="shared" ref="J11:J72" si="1">IF(I11="","",1440-I11)</f>
         <v>425</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K11" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N11" s="12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
         <v>46253</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B12" s="9">
         <v>350</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C12" s="9">
         <v>80</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D12" s="9">
         <v>90</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E12" s="9">
         <v>30</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F12" s="9">
         <v>350</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G12" s="9">
         <v>7</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H12" s="9">
         <v>210</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="J7" s="10">
-        <f>IF(I7="","",1440-I7)</f>
+      <c r="J12" s="10">
+        <f>IF(I12="","",1440-I12)</f>
         <v>330</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K12" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L12" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="N12" s="12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
         <v>46254</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B13" s="9">
         <v>300</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C13" s="9">
         <v>50</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D13" s="9">
         <v>135</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E13" s="9">
         <v>60</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F13" s="9">
         <v>150</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G13" s="9">
         <v>3</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H13" s="9">
         <v>420</v>
       </c>
-      <c r="I8" s="10">
-        <f>IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+      <c r="I13" s="10">
+        <f>IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
         <v>1115</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K13" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L13" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M13" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="12" t="s">
+      <c r="N13" s="12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
         <v>46255</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B14" s="9">
         <v>210</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C14" s="9">
         <v>95</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D14" s="9">
         <v>135</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E14" s="9">
         <v>72</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F14" s="9">
         <v>250</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G14" s="9">
         <v>5</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H14" s="9">
         <v>270</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
         <v>1032</v>
       </c>
-      <c r="J9" s="10">
-        <f>IF(I9="","",1440-I9)</f>
+      <c r="J14" s="10">
+        <f>IF(I14="","",1440-I14)</f>
         <v>408</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K14" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L14" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M14" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="N9" s="12" t="s">
+      <c r="N14" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+    <row r="15" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
         <v>46256</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B15" s="9">
         <v>75</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C15" s="9">
         <v>125</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D15" s="9">
         <v>210</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E15" s="9">
         <v>0</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F15" s="9">
         <v>0</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G15" s="9">
         <v>0</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H15" s="9">
         <v>584</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
         <v>994</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
         <v>446</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K15" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L15" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M15" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="N15" s="12" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
         <v>46257</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B16" s="9">
         <v>320</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C16" s="9">
         <v>30</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D16" s="9">
         <v>75</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E16" s="9">
         <v>93</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F16" s="9">
         <v>0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G16" s="9">
         <v>0</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H16" s="9">
         <v>345</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
         <v>863</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
         <v>577</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K16" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L16" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M16" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N11" s="12" t="s">
+      <c r="N16" s="12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
         <v>46258</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B17" s="9">
         <v>280</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C17" s="9">
         <v>48</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D17" s="9">
         <v>150</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E17" s="9">
         <v>60</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F17" s="9">
         <v>250</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G17" s="9">
         <v>5</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H17" s="9">
         <v>100</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
         <v>888</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
         <v>552</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K17" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L17" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="12" t="s">
+      <c r="N17" s="12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
         <v>46259</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B18" s="9">
         <v>270</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C18" s="9">
         <v>65</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D18" s="9">
         <v>150</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E18" s="9">
         <v>100</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F18" s="9">
         <v>150</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G18" s="9">
         <v>3</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H18" s="9">
         <v>200</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
         <v>935</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
         <v>505</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K18" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L18" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M18" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N18" s="12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
         <v>46260</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B19" s="9">
         <v>450</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C19" s="9">
         <v>80</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D19" s="9">
         <v>70</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E19" s="9">
         <v>150</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F19" s="9">
         <v>8</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G19" s="9">
         <v>400</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H19" s="9">
         <v>150</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
         <v>908</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
         <v>532</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K19" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L19" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M19" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="N19" s="12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
         <v>46261</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B20" s="9">
         <v>320</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C20" s="9">
         <v>100</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D20" s="9">
         <v>300</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E20" s="9">
         <v>90</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F20" s="9">
         <v>3</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G20" s="9">
         <v>150</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H20" s="9">
         <v>150</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
         <v>963</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
         <v>477</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K20" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L20" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="M20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="12" t="s">
+      <c r="N20" s="12" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
         <v>46262</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B21" s="9">
         <v>300</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C21" s="9">
         <v>120</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D21" s="9">
         <v>60</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E21" s="9">
         <v>0</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F21" s="9">
         <v>250</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G21" s="9">
         <v>5</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H21" s="9">
         <v>150</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
         <v>880</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
         <v>560</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K21" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L21" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="12" t="s">
+      <c r="N21" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
         <v>46263</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B22" s="9">
         <v>350</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C22" s="9">
         <v>60</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D22" s="9">
         <v>300</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E22" s="9">
         <v>120</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F22" s="9">
         <v>0</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G22" s="9">
         <v>0</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H22" s="9">
         <v>250</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K22" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L22" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M22" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N17" s="12" t="s">
+      <c r="N22" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
         <v>46264</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B23" s="9">
         <v>440</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C23" s="9">
         <v>45</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D23" s="9">
         <v>270</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E23" s="9">
         <v>90</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F23" s="9">
         <v>0</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G23" s="9">
         <v>0</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H23" s="9">
         <v>400</v>
       </c>
-      <c r="I18" s="10">
-        <f t="shared" ref="I18:I80" si="2">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
+      <c r="I23" s="10">
+        <f t="shared" ref="I23:I85" si="2">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
         <v>1245</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K23" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L23" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="M23" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="N18" s="12" t="s">
+      <c r="N23" s="12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="18">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="18">
         <v>46265</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B24" s="19">
         <v>230</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C24" s="19">
         <v>90</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D24" s="19">
         <v>90</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E24" s="19">
         <v>120</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F24" s="19">
         <v>300</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G24" s="19">
         <v>6</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H24" s="19">
         <v>270</v>
       </c>
-      <c r="I19" s="20">
+      <c r="I24" s="20">
         <f t="shared" si="2"/>
         <v>1100</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J24" s="20">
         <f t="shared" si="1"/>
         <v>340</v>
       </c>
-      <c r="K19" s="21" t="s">
+      <c r="K24" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="L19" s="21" t="s">
+      <c r="L24" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="M19" s="21" t="s">
+      <c r="M24" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="N19" s="22" t="s">
+      <c r="N24" s="22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="23">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="23">
         <v>46266</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B25" s="24">
         <v>450</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C25" s="24">
         <v>80</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D25" s="24">
         <v>130</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E25" s="24">
         <v>45</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F25" s="24">
         <v>150</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G25" s="24">
         <v>3</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H25" s="24">
         <v>260</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I25" s="25">
         <f t="shared" si="2"/>
         <v>1115</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J25" s="25">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="K20" s="26" t="s">
+      <c r="K25" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L20" s="26" t="s">
+      <c r="L25" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="M20" s="26" t="s">
+      <c r="M25" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="N20" s="27"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+      <c r="N25" s="27"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
         <v>46267</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B26" s="9">
         <v>400</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C26" s="9">
         <v>35</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D26" s="9">
         <v>150</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E26" s="9">
         <v>100</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F26" s="9">
         <v>400</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G26" s="9">
         <v>8</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H26" s="9">
         <v>90</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I26" s="10">
         <f t="shared" si="2"/>
         <v>1175</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
         <v>265</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K26" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L26" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M21" s="11" t="s">
+      <c r="M26" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="N21" s="12" t="s">
+      <c r="N26" s="12" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
         <v>46268</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B27" s="9">
         <v>420</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C27" s="9">
         <v>150</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D27" s="9">
         <v>60</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E27" s="9">
         <v>100</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F27" s="9">
         <v>300</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G27" s="9">
         <v>6</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H27" s="9">
         <v>80</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I27" s="10">
         <f t="shared" si="2"/>
         <v>1110</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
         <v>330</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K27" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L27" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M22" s="11" t="s">
+      <c r="M27" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N22" s="12" t="s">
+      <c r="N27" s="12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
         <v>46269</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B28" s="9">
         <v>370</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C28" s="9">
         <v>180</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D28" s="9">
         <v>180</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E28" s="9">
         <v>70</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F28" s="9">
         <v>250</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G28" s="9">
         <v>5</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H28" s="9">
         <v>100</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I28" s="10">
         <f t="shared" si="2"/>
         <v>1150</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
         <v>290</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K28" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L28" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M23" s="11" t="s">
+      <c r="M28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N23" s="12" t="s">
+      <c r="N28" s="12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
         <v>46270</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B29" s="9">
         <v>500</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C29" s="9">
         <v>200</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D29" s="9">
         <v>120</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E29" s="9">
         <v>60</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F29" s="9">
         <v>0</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G29" s="9">
         <v>0</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H29" s="9">
         <v>190</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I29" s="10">
         <f t="shared" si="2"/>
         <v>1070</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
         <v>370</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K29" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L29" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N24" s="12" t="s">
+      <c r="N29" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
         <v>46271</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B30" s="9">
         <v>385</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C30" s="9">
         <v>135</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D30" s="9">
         <v>200</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E30" s="9">
         <v>120</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F30" s="9">
         <v>0</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G30" s="9">
         <v>0</v>
-      </c>
-      <c r="H25" s="9">
-        <v>150</v>
-      </c>
-      <c r="I25" s="10">
-        <f t="shared" si="2"/>
-        <v>990</v>
-      </c>
-      <c r="J25" s="10">
-        <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L25" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
-        <v>46272</v>
-      </c>
-      <c r="B26" s="9">
-        <v>400</v>
-      </c>
-      <c r="C26" s="9">
-        <v>180</v>
-      </c>
-      <c r="D26" s="9">
-        <v>150</v>
-      </c>
-      <c r="E26" s="9">
-        <v>100</v>
-      </c>
-      <c r="F26" s="9">
-        <v>300</v>
-      </c>
-      <c r="G26" s="9">
-        <v>6</v>
-      </c>
-      <c r="H26" s="9">
-        <v>215</v>
-      </c>
-      <c r="I26" s="10">
-        <f t="shared" si="2"/>
-        <v>1345</v>
-      </c>
-      <c r="J26" s="10">
-        <f t="shared" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L26" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N26" s="12"/>
-    </row>
-    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
-        <v>46273</v>
-      </c>
-      <c r="B27" s="9">
-        <v>480</v>
-      </c>
-      <c r="C27" s="9">
-        <v>120</v>
-      </c>
-      <c r="D27" s="9">
-        <v>60</v>
-      </c>
-      <c r="E27" s="9">
-        <v>20</v>
-      </c>
-      <c r="F27" s="9">
-        <v>150</v>
-      </c>
-      <c r="G27" s="9">
-        <v>3</v>
-      </c>
-      <c r="H27" s="9">
-        <v>240</v>
-      </c>
-      <c r="I27" s="10">
-        <f t="shared" si="2"/>
-        <v>1070</v>
-      </c>
-      <c r="J27" s="10">
-        <f t="shared" si="1"/>
-        <v>370</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N27" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
-        <v>46274</v>
-      </c>
-      <c r="B28" s="9">
-        <v>300</v>
-      </c>
-      <c r="C28" s="9">
-        <v>60</v>
-      </c>
-      <c r="D28" s="9">
-        <v>200</v>
-      </c>
-      <c r="E28" s="9">
-        <v>120</v>
-      </c>
-      <c r="F28" s="9">
-        <v>400</v>
-      </c>
-      <c r="G28" s="9">
-        <v>8</v>
-      </c>
-      <c r="H28" s="9">
-        <v>150</v>
-      </c>
-      <c r="I28" s="10">
-        <f t="shared" si="2"/>
-        <v>1230</v>
-      </c>
-      <c r="J28" s="10">
-        <f t="shared" si="1"/>
-        <v>210</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L28" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
-        <v>46275</v>
-      </c>
-      <c r="B29" s="9">
-        <v>420</v>
-      </c>
-      <c r="C29" s="9">
-        <v>78</v>
-      </c>
-      <c r="D29" s="9">
-        <v>200</v>
-      </c>
-      <c r="E29" s="9">
-        <v>75</v>
-      </c>
-      <c r="F29" s="9">
-        <v>250</v>
-      </c>
-      <c r="G29" s="9">
-        <v>5</v>
-      </c>
-      <c r="H29" s="9">
-        <v>300</v>
-      </c>
-      <c r="I29" s="10">
-        <f t="shared" si="2"/>
-        <v>1323</v>
-      </c>
-      <c r="J29" s="10">
-        <f t="shared" si="1"/>
-        <v>117</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
-        <v>46276</v>
-      </c>
-      <c r="B30" s="9">
-        <v>460</v>
-      </c>
-      <c r="C30" s="9">
-        <v>90</v>
-      </c>
-      <c r="D30" s="9">
-        <v>110</v>
-      </c>
-      <c r="E30" s="9">
-        <v>30</v>
-      </c>
-      <c r="F30" s="9">
-        <v>150</v>
-      </c>
-      <c r="G30" s="9">
-        <v>3</v>
       </c>
       <c r="H30" s="9">
         <v>150</v>
@@ -2269,7 +2143,7 @@
         <v>450</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L30" s="11" t="s">
         <v>50</v>
@@ -2278,362 +2152,606 @@
         <v>51</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
-        <v>46277</v>
+        <v>46272</v>
       </c>
       <c r="B31" s="9">
+        <v>400</v>
+      </c>
+      <c r="C31" s="9">
+        <v>180</v>
+      </c>
+      <c r="D31" s="9">
+        <v>150</v>
+      </c>
+      <c r="E31" s="9">
+        <v>100</v>
+      </c>
+      <c r="F31" s="9">
         <v>300</v>
       </c>
-      <c r="C31" s="9">
-        <v>30</v>
-      </c>
-      <c r="D31" s="9">
-        <v>60</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0</v>
-      </c>
-      <c r="F31" s="9">
-        <v>0</v>
-      </c>
       <c r="G31" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H31" s="9">
-        <v>120</v>
+        <v>215</v>
       </c>
       <c r="I31" s="10">
         <f t="shared" si="2"/>
-        <v>510</v>
+        <v>1345</v>
       </c>
       <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v>930</v>
+        <v>95</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="M31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N31" s="12" t="s">
+      <c r="N31" s="12"/>
+    </row>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B32" s="9">
+        <v>480</v>
+      </c>
+      <c r="C32" s="9">
+        <v>120</v>
+      </c>
+      <c r="D32" s="9">
+        <v>60</v>
+      </c>
+      <c r="E32" s="9">
+        <v>20</v>
+      </c>
+      <c r="F32" s="9">
+        <v>150</v>
+      </c>
+      <c r="G32" s="9">
+        <v>3</v>
+      </c>
+      <c r="H32" s="9">
+        <v>240</v>
+      </c>
+      <c r="I32" s="10">
+        <f t="shared" si="2"/>
+        <v>1070</v>
+      </c>
+      <c r="J32" s="10">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B33" s="9">
+        <v>300</v>
+      </c>
+      <c r="C33" s="9">
+        <v>60</v>
+      </c>
+      <c r="D33" s="9">
+        <v>200</v>
+      </c>
+      <c r="E33" s="9">
+        <v>120</v>
+      </c>
+      <c r="F33" s="9">
+        <v>400</v>
+      </c>
+      <c r="G33" s="9">
+        <v>8</v>
+      </c>
+      <c r="H33" s="9">
+        <v>150</v>
+      </c>
+      <c r="I33" s="10">
+        <f t="shared" si="2"/>
+        <v>1230</v>
+      </c>
+      <c r="J33" s="10">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B34" s="9">
+        <v>420</v>
+      </c>
+      <c r="C34" s="9">
+        <v>78</v>
+      </c>
+      <c r="D34" s="9">
+        <v>200</v>
+      </c>
+      <c r="E34" s="9">
+        <v>75</v>
+      </c>
+      <c r="F34" s="9">
+        <v>250</v>
+      </c>
+      <c r="G34" s="9">
+        <v>5</v>
+      </c>
+      <c r="H34" s="9">
+        <v>300</v>
+      </c>
+      <c r="I34" s="10">
+        <f t="shared" si="2"/>
+        <v>1323</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B35" s="9">
+        <v>460</v>
+      </c>
+      <c r="C35" s="9">
+        <v>90</v>
+      </c>
+      <c r="D35" s="9">
+        <v>110</v>
+      </c>
+      <c r="E35" s="9">
+        <v>30</v>
+      </c>
+      <c r="F35" s="9">
+        <v>150</v>
+      </c>
+      <c r="G35" s="9">
+        <v>3</v>
+      </c>
+      <c r="H35" s="9">
+        <v>150</v>
+      </c>
+      <c r="I35" s="10">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="J35" s="10">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B36" s="9">
+        <v>300</v>
+      </c>
+      <c r="C36" s="9">
+        <v>30</v>
+      </c>
+      <c r="D36" s="9">
+        <v>60</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0</v>
+      </c>
+      <c r="H36" s="9">
+        <v>120</v>
+      </c>
+      <c r="I36" s="10">
+        <f t="shared" si="2"/>
+        <v>510</v>
+      </c>
+      <c r="J36" s="10">
+        <f t="shared" si="1"/>
+        <v>930</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B37" s="9">
+        <v>460</v>
+      </c>
+      <c r="C37" s="9">
+        <v>20</v>
+      </c>
+      <c r="D37" s="9">
+        <v>190</v>
+      </c>
+      <c r="E37" s="9">
+        <v>60</v>
+      </c>
+      <c r="F37" s="9">
+        <v>0</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0</v>
+      </c>
+      <c r="H37" s="9">
+        <v>230</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
+        <v>960</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B38" s="9">
+        <v>350</v>
+      </c>
+      <c r="C38" s="9">
+        <v>65</v>
+      </c>
+      <c r="D38" s="9">
+        <v>120</v>
+      </c>
+      <c r="E38" s="9">
+        <v>45</v>
+      </c>
+      <c r="F38" s="9">
+        <v>300</v>
+      </c>
+      <c r="G38" s="9">
+        <v>6</v>
+      </c>
+      <c r="H38" s="9">
+        <v>130</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
+        <v>430</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B39" s="9">
+        <v>200</v>
+      </c>
+      <c r="C39" s="9">
+        <v>45</v>
+      </c>
+      <c r="D39" s="9">
+        <v>270</v>
+      </c>
+      <c r="E39" s="9">
+        <v>80</v>
+      </c>
+      <c r="F39" s="9">
+        <v>150</v>
+      </c>
+      <c r="G39" s="9">
+        <v>3</v>
+      </c>
+      <c r="H39" s="9">
+        <v>120</v>
+      </c>
+      <c r="I39" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
+        <v>865</v>
+      </c>
+      <c r="J39" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
+        <v>575</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B40" s="9">
+        <v>350</v>
+      </c>
+      <c r="C40" s="9">
+        <v>80</v>
+      </c>
+      <c r="D40" s="9">
+        <v>70</v>
+      </c>
+      <c r="E40" s="9">
+        <v>30</v>
+      </c>
+      <c r="F40" s="9">
+        <v>400</v>
+      </c>
+      <c r="G40" s="9">
+        <v>8</v>
+      </c>
+      <c r="H40" s="9">
+        <v>80</v>
+      </c>
+      <c r="I40" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
+        <v>430</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B41" s="9">
+        <v>400</v>
+      </c>
+      <c r="C41" s="9">
+        <v>95</v>
+      </c>
+      <c r="D41" s="9">
+        <v>150</v>
+      </c>
+      <c r="E41" s="9">
+        <v>45</v>
+      </c>
+      <c r="F41" s="9">
+        <v>250</v>
+      </c>
+      <c r="G41" s="9">
+        <v>5</v>
+      </c>
+      <c r="H41" s="9">
+        <v>70</v>
+      </c>
+      <c r="I41" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
+        <v>430</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9">
+        <v>250</v>
+      </c>
+      <c r="G42" s="9">
+        <v>5</v>
+      </c>
+      <c r="H42" s="9"/>
+      <c r="I42" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
+        <v>250</v>
+      </c>
+      <c r="J42" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="12"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
+        <v>1190</v>
+      </c>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="12"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="8"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J38" s="10" t="str">
+      <c r="J43" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="12"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J39" s="10" t="str">
+      <c r="J44" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="12"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="12"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="8"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J40" s="10" t="str">
+      <c r="J45" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="12"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
@@ -3133,7 +3251,7 @@
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" ref="J68:J131" si="3">IF(I68="","",1440-I68)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -3155,7 +3273,7 @@
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3177,7 +3295,7 @@
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3199,7 +3317,7 @@
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3221,7 +3339,7 @@
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3243,7 +3361,7 @@
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J73:J136" si="3">IF(I73="","",1440-I73)</f>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3415,7 +3533,7 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" ref="I81:I144" si="4">IF(SUM(B81:F81,H81)=0,"",SUM(B81:F81,H81))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
@@ -3437,7 +3555,7 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
@@ -3459,7 +3577,7 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
@@ -3481,7 +3599,7 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
@@ -3503,7 +3621,7 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
@@ -3525,7 +3643,7 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I86:I149" si="4">IF(SUM(B86:F86,H86)=0,"",SUM(B86:F86,H86))</f>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
@@ -4541,7 +4659,7 @@
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" ref="J132:J195" si="5">IF(I132="","",1440-I132)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4563,7 +4681,7 @@
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4585,7 +4703,7 @@
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4607,7 +4725,7 @@
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4629,7 +4747,7 @@
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4651,7 +4769,7 @@
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J137:J200" si="5">IF(I137="","",1440-I137)</f>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4823,7 +4941,7 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" ref="I145:I208" si="6">IF(SUM(B145:F145,H145)=0,"",SUM(B145:F145,H145))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
@@ -4845,7 +4963,7 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
@@ -4867,7 +4985,7 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
@@ -4889,7 +5007,7 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
@@ -4911,7 +5029,7 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
@@ -4933,7 +5051,7 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I150:I213" si="6">IF(SUM(B150:F150,H150)=0,"",SUM(B150:F150,H150))</f>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
@@ -5949,7 +6067,7 @@
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" ref="J196:J259" si="7">IF(I196="","",1440-I196)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5971,7 +6089,7 @@
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5993,7 +6111,7 @@
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6015,7 +6133,7 @@
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6037,7 +6155,7 @@
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6059,7 +6177,7 @@
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J201:J264" si="7">IF(I201="","",1440-I201)</f>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6231,7 +6349,7 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" ref="I209:I272" si="8">IF(SUM(B209:F209,H209)=0,"",SUM(B209:F209,H209))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
@@ -6253,7 +6371,7 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
@@ -6275,7 +6393,7 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
@@ -6297,7 +6415,7 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
@@ -6319,7 +6437,7 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
@@ -6341,7 +6459,7 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I214:I277" si="8">IF(SUM(B214:F214,H214)=0,"",SUM(B214:F214,H214))</f>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
@@ -7357,7 +7475,7 @@
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" ref="J260:J323" si="9">IF(I260="","",1440-I260)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7379,7 +7497,7 @@
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7401,7 +7519,7 @@
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7423,7 +7541,7 @@
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7445,7 +7563,7 @@
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7467,7 +7585,7 @@
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J265:J328" si="9">IF(I265="","",1440-I265)</f>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7639,7 +7757,7 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" ref="I273:I336" si="10">IF(SUM(B273:F273,H273)=0,"",SUM(B273:F273,H273))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
@@ -7661,7 +7779,7 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
@@ -7683,7 +7801,7 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
@@ -7705,7 +7823,7 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
@@ -7727,7 +7845,7 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
@@ -7749,7 +7867,7 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I278:I341" si="10">IF(SUM(B278:F278,H278)=0,"",SUM(B278:F278,H278))</f>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
@@ -8765,7 +8883,7 @@
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" ref="J324:J387" si="11">IF(I324="","",1440-I324)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8787,7 +8905,7 @@
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8809,7 +8927,7 @@
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8831,7 +8949,7 @@
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8853,7 +8971,7 @@
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8875,7 +8993,7 @@
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J329:J392" si="11">IF(I329="","",1440-I329)</f>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9047,7 +9165,7 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" ref="I337:I399" si="12">IF(SUM(B337:F337,H337)=0,"",SUM(B337:F337,H337))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
@@ -9069,7 +9187,7 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
@@ -9091,7 +9209,7 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
@@ -9113,7 +9231,7 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
@@ -9135,7 +9253,7 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
@@ -9157,7 +9275,7 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I342:I404" si="12">IF(SUM(B342:F342,H342)=0,"",SUM(B342:F342,H342))</f>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
@@ -10173,7 +10291,7 @@
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" ref="J388:J399" si="13">IF(I388="","",1440-I388)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10195,7 +10313,7 @@
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10217,7 +10335,7 @@
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10239,7 +10357,7 @@
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10261,7 +10379,7 @@
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10283,7 +10401,7 @@
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J393:J404" si="13">IF(I393="","",1440-I393)</f>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10423,6 +10541,116 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A400" s="13"/>
+      <c r="B400" s="14"/>
+      <c r="C400" s="14"/>
+      <c r="D400" s="14"/>
+      <c r="E400" s="14"/>
+      <c r="F400" s="14"/>
+      <c r="G400" s="14"/>
+      <c r="H400" s="14"/>
+      <c r="I400" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J400" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K400" s="16"/>
+      <c r="L400" s="16"/>
+      <c r="M400" s="16"/>
+      <c r="N400" s="17"/>
+    </row>
+    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A401" s="13"/>
+      <c r="B401" s="14"/>
+      <c r="C401" s="14"/>
+      <c r="D401" s="14"/>
+      <c r="E401" s="14"/>
+      <c r="F401" s="14"/>
+      <c r="G401" s="14"/>
+      <c r="H401" s="14"/>
+      <c r="I401" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J401" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K401" s="16"/>
+      <c r="L401" s="16"/>
+      <c r="M401" s="16"/>
+      <c r="N401" s="17"/>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A404" s="13"/>
+      <c r="B404" s="14"/>
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J404" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K404" s="16"/>
+      <c r="L404" s="16"/>
+      <c r="M404" s="16"/>
+      <c r="N404" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10432,21 +10660,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J399">
+  <conditionalFormatting sqref="J6:J404">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K399" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K11:K404" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L399" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L11:L404" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M399" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M11:M404" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1CA0FC-DBD7-498E-88C9-1FD6B1BAD60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F66CE0-EC94-4D17-9CDE-35D0C856A2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2663,32 +2663,50 @@
       <c r="A42" s="8">
         <v>46283</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
+      <c r="B42" s="9">
+        <v>340</v>
+      </c>
+      <c r="C42" s="9">
+        <v>120</v>
+      </c>
+      <c r="D42" s="9">
+        <v>240</v>
+      </c>
+      <c r="E42" s="9">
+        <v>60</v>
+      </c>
       <c r="F42" s="9">
         <v>250</v>
       </c>
       <c r="G42" s="9">
         <v>5</v>
       </c>
-      <c r="H42" s="9"/>
+      <c r="H42" s="9">
+        <v>150</v>
+      </c>
       <c r="I42" s="10">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>1160</v>
       </c>
       <c r="J42" s="10">
         <f t="shared" si="1"/>
-        <v>1190</v>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
+        <v>280</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N42" s="12"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
+      <c r="A43" s="8">
+        <v>46284</v>
+      </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F66CE0-EC94-4D17-9CDE-35D0C856A2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABDACEA-53E0-45EF-8677-6C34288A77BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2707,24 +2707,44 @@
       <c r="A43" s="8">
         <v>46284</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
+      <c r="B43" s="9">
+        <v>420</v>
+      </c>
+      <c r="C43" s="9">
+        <v>60</v>
+      </c>
+      <c r="D43" s="9">
+        <v>200</v>
+      </c>
+      <c r="E43" s="9">
+        <v>80</v>
+      </c>
+      <c r="F43" s="9">
+        <v>30</v>
+      </c>
+      <c r="G43" s="9">
+        <v>1</v>
+      </c>
+      <c r="H43" s="9">
+        <v>90</v>
+      </c>
+      <c r="I43" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
+        <v>880</v>
+      </c>
+      <c r="J43" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
+        <v>560</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N43" s="12"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABDACEA-53E0-45EF-8677-6C34288A77BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70C106E-4023-4131-A6B3-D02CF5EDA6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>Visit a nearest mela.</t>
+  </si>
+  <si>
+    <t>Lots are revision are still pending for DBMS Ca</t>
+  </si>
+  <si>
+    <t>In the evening I relaxed after the CA completed</t>
   </si>
 </sst>
 </file>
@@ -2747,49 +2753,97 @@
       </c>
       <c r="N43" s="12"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
+    <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B44" s="9">
+        <v>300</v>
+      </c>
+      <c r="C44" s="9">
+        <v>60</v>
+      </c>
+      <c r="D44" s="9">
+        <v>300</v>
+      </c>
+      <c r="E44" s="9">
+        <v>30</v>
+      </c>
+      <c r="F44" s="9">
+        <v>0</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0</v>
+      </c>
+      <c r="H44" s="9">
+        <v>240</v>
+      </c>
+      <c r="I44" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
+        <v>930</v>
+      </c>
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
+        <v>510</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B45" s="9">
+        <v>200</v>
+      </c>
+      <c r="C45" s="9">
+        <v>45</v>
+      </c>
+      <c r="D45" s="9">
+        <v>380</v>
+      </c>
+      <c r="E45" s="9">
+        <v>60</v>
+      </c>
+      <c r="F45" s="9">
+        <v>300</v>
+      </c>
+      <c r="G45" s="9">
+        <v>6</v>
+      </c>
+      <c r="H45" s="9">
+        <v>180</v>
+      </c>
+      <c r="I45" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
+        <v>1165</v>
+      </c>
+      <c r="J45" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
+        <v>275</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70C106E-4023-4131-A6B3-D02CF5EDA6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D573A7FD-FF84-477A-9F50-43D97F445452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>In the evening I relaxed after the CA completed</t>
+  </si>
+  <si>
+    <t>Excited to take tomorrow English class</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N404"/>
+  <dimension ref="A1:N400"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1155,356 +1158,494 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
+        <v>46251</v>
+      </c>
+      <c r="B6" s="9">
+        <v>420</v>
+      </c>
+      <c r="C6" s="9">
+        <v>30</v>
+      </c>
+      <c r="D6" s="9">
+        <v>165</v>
+      </c>
+      <c r="E6" s="9">
+        <v>20</v>
+      </c>
+      <c r="F6" s="9">
+        <v>300</v>
+      </c>
+      <c r="G6" s="9">
+        <v>6</v>
+      </c>
+      <c r="H6" s="9">
+        <v>60</v>
+      </c>
+      <c r="I6" s="10">
+        <f>IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <v>995</v>
+      </c>
+      <c r="J6" s="10">
+        <f>IF(I6="","",1440-I6)</f>
+        <v>445</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="N6" s="12"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
-        <v>46248</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="12"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="9">
+        <v>480</v>
+      </c>
+      <c r="C7" s="9">
+        <v>45</v>
+      </c>
+      <c r="D7" s="9">
+        <v>120</v>
+      </c>
+      <c r="E7" s="9">
+        <v>90</v>
+      </c>
+      <c r="F7" s="9">
+        <v>250</v>
+      </c>
+      <c r="G7" s="9">
+        <v>5</v>
+      </c>
+      <c r="H7" s="9">
+        <v>30</v>
+      </c>
+      <c r="I7" s="10">
+        <f t="shared" ref="I7:I18" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>1015</v>
+      </c>
+      <c r="J7" s="10">
+        <f t="shared" ref="J7:J68" si="1">IF(I7="","",1440-I7)</f>
+        <v>425</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>46249</v>
-      </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="12"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>46253</v>
+      </c>
+      <c r="B8" s="9">
+        <v>350</v>
+      </c>
+      <c r="C8" s="9">
+        <v>80</v>
+      </c>
+      <c r="D8" s="9">
+        <v>90</v>
+      </c>
+      <c r="E8" s="9">
+        <v>30</v>
+      </c>
+      <c r="F8" s="9">
+        <v>350</v>
+      </c>
+      <c r="G8" s="9">
+        <v>7</v>
+      </c>
+      <c r="H8" s="9">
+        <v>210</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="J8" s="10">
+        <f>IF(I8="","",1440-I8)</f>
+        <v>330</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>46250</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
+        <v>46254</v>
+      </c>
+      <c r="B9" s="9">
+        <v>300</v>
+      </c>
+      <c r="C9" s="9">
+        <v>50</v>
+      </c>
+      <c r="D9" s="9">
+        <v>135</v>
+      </c>
+      <c r="E9" s="9">
+        <v>60</v>
+      </c>
+      <c r="F9" s="9">
+        <v>150</v>
+      </c>
+      <c r="G9" s="9">
+        <v>3</v>
+      </c>
+      <c r="H9" s="9">
+        <v>420</v>
+      </c>
+      <c r="I9" s="10">
+        <f>IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
+        <v>1115</v>
+      </c>
+      <c r="J9" s="10">
+        <f t="shared" si="1"/>
+        <v>325</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>46251</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="12"/>
-    </row>
-    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="9">
+        <v>210</v>
+      </c>
+      <c r="C10" s="9">
+        <v>95</v>
+      </c>
+      <c r="D10" s="9">
+        <v>135</v>
+      </c>
+      <c r="E10" s="9">
+        <v>72</v>
+      </c>
+      <c r="F10" s="9">
+        <v>250</v>
+      </c>
+      <c r="G10" s="9">
+        <v>5</v>
+      </c>
+      <c r="H10" s="9">
+        <v>270</v>
+      </c>
+      <c r="I10" s="10">
+        <f t="shared" si="0"/>
+        <v>1032</v>
+      </c>
+      <c r="J10" s="10">
+        <f>IF(I10="","",1440-I10)</f>
+        <v>408</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>46252</v>
+        <v>46256</v>
       </c>
       <c r="B11" s="9">
-        <v>480</v>
+        <v>75</v>
       </c>
       <c r="C11" s="9">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="D11" s="9">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="E11" s="9">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F11" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G11" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="9">
-        <v>30</v>
+        <v>584</v>
       </c>
       <c r="I11" s="10">
-        <f t="shared" ref="I11:I22" si="0">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
-        <v>1015</v>
+        <f t="shared" si="0"/>
+        <v>994</v>
       </c>
       <c r="J11" s="10">
-        <f t="shared" ref="J11:J72" si="1">IF(I11="","",1440-I11)</f>
-        <v>425</v>
+        <f t="shared" si="1"/>
+        <v>446</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>49</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="B12" s="9">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="C12" s="9">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D12" s="9">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E12" s="9">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="F12" s="9">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G12" s="9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H12" s="9">
-        <v>210</v>
+        <v>345</v>
       </c>
       <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>863</v>
       </c>
       <c r="J12" s="10">
-        <f>IF(I12="","",1440-I12)</f>
-        <v>330</v>
+        <f t="shared" si="1"/>
+        <v>577</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B13" s="9">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="C13" s="9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" s="9">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="E13" s="9">
         <v>60</v>
       </c>
       <c r="F13" s="9">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G13" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" s="9">
-        <v>420</v>
+        <v>100</v>
       </c>
       <c r="I13" s="10">
-        <f>IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v>1115</v>
+        <f t="shared" si="0"/>
+        <v>888</v>
       </c>
       <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v>325</v>
+        <v>552</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="L13" s="11" t="s">
         <v>50</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B14" s="9">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="C14" s="9">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="D14" s="9">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="E14" s="9">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="F14" s="9">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G14" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H14" s="9">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v>1032</v>
+        <v>935</v>
       </c>
       <c r="J14" s="10">
-        <f>IF(I14="","",1440-I14)</f>
-        <v>408</v>
+        <f t="shared" si="1"/>
+        <v>505</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B15" s="9">
-        <v>75</v>
+        <v>450</v>
       </c>
       <c r="C15" s="9">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="D15" s="9">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="E15" s="9">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F15" s="9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G15" s="9">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H15" s="9">
-        <v>584</v>
+        <v>150</v>
       </c>
       <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v>994</v>
+        <v>908</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v>446</v>
+        <v>532</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="9">
         <v>320</v>
       </c>
       <c r="C16" s="9">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D16" s="9">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="E16" s="9">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F16" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G16" s="9">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" s="9">
-        <v>345</v>
+        <v>150</v>
       </c>
       <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v>863</v>
+        <v>963</v>
       </c>
       <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v>577</v>
+        <v>477</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>61</v>
@@ -1513,27 +1654,27 @@
         <v>62</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B17" s="9">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C17" s="9">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="D17" s="9">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="E17" s="9">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F17" s="9">
         <v>250</v>
@@ -1542,1308 +1683,1236 @@
         <v>5</v>
       </c>
       <c r="H17" s="9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>51</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="9">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="C18" s="9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D18" s="9">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="E18" s="9">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F18" s="9">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G18" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" s="9">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v>935</v>
+        <v>1080</v>
       </c>
       <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v>505</v>
+        <v>360</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M18" s="11" t="s">
         <v>54</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B19" s="9">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C19" s="9">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="D19" s="9">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="E19" s="9">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="F19" s="9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
         <v>400</v>
       </c>
-      <c r="H19" s="9">
-        <v>150</v>
-      </c>
       <c r="I19" s="10">
-        <f t="shared" si="0"/>
-        <v>908</v>
+        <f t="shared" ref="I19:I81" si="2">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
+        <v>1245</v>
       </c>
       <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v>532</v>
+        <v>195</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>63</v>
       </c>
       <c r="N19" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="18">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="19">
+        <v>230</v>
+      </c>
+      <c r="C20" s="19">
+        <v>90</v>
+      </c>
+      <c r="D20" s="19">
+        <v>90</v>
+      </c>
+      <c r="E20" s="19">
+        <v>120</v>
+      </c>
+      <c r="F20" s="19">
+        <v>300</v>
+      </c>
+      <c r="G20" s="19">
+        <v>6</v>
+      </c>
+      <c r="H20" s="19">
+        <v>270</v>
+      </c>
+      <c r="I20" s="20">
+        <f t="shared" si="2"/>
+        <v>1100</v>
+      </c>
+      <c r="J20" s="20">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="23">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="24">
+        <v>450</v>
+      </c>
+      <c r="C21" s="24">
+        <v>80</v>
+      </c>
+      <c r="D21" s="24">
+        <v>130</v>
+      </c>
+      <c r="E21" s="24">
+        <v>45</v>
+      </c>
+      <c r="F21" s="24">
+        <v>150</v>
+      </c>
+      <c r="G21" s="24">
+        <v>3</v>
+      </c>
+      <c r="H21" s="24">
+        <v>260</v>
+      </c>
+      <c r="I21" s="25">
+        <f t="shared" si="2"/>
+        <v>1115</v>
+      </c>
+      <c r="J21" s="25">
+        <f t="shared" si="1"/>
+        <v>325</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="M21" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="27"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="9">
+        <v>400</v>
+      </c>
+      <c r="C22" s="9">
+        <v>35</v>
+      </c>
+      <c r="D22" s="9">
+        <v>150</v>
+      </c>
+      <c r="E22" s="9">
+        <v>100</v>
+      </c>
+      <c r="F22" s="9">
+        <v>400</v>
+      </c>
+      <c r="G22" s="9">
+        <v>8</v>
+      </c>
+      <c r="H22" s="9">
+        <v>90</v>
+      </c>
+      <c r="I22" s="10">
+        <f t="shared" si="2"/>
+        <v>1175</v>
+      </c>
+      <c r="J22" s="10">
+        <f t="shared" si="1"/>
+        <v>265</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="9">
+        <v>420</v>
+      </c>
+      <c r="C23" s="9">
+        <v>150</v>
+      </c>
+      <c r="D23" s="9">
+        <v>60</v>
+      </c>
+      <c r="E23" s="9">
+        <v>100</v>
+      </c>
+      <c r="F23" s="9">
+        <v>300</v>
+      </c>
+      <c r="G23" s="9">
+        <v>6</v>
+      </c>
+      <c r="H23" s="9">
+        <v>80</v>
+      </c>
+      <c r="I23" s="10">
+        <f t="shared" si="2"/>
+        <v>1110</v>
+      </c>
+      <c r="J23" s="10">
+        <f t="shared" si="1"/>
+        <v>330</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="9">
+        <v>370</v>
+      </c>
+      <c r="C24" s="9">
+        <v>180</v>
+      </c>
+      <c r="D24" s="9">
+        <v>180</v>
+      </c>
+      <c r="E24" s="9">
+        <v>70</v>
+      </c>
+      <c r="F24" s="9">
+        <v>250</v>
+      </c>
+      <c r="G24" s="9">
+        <v>5</v>
+      </c>
+      <c r="H24" s="9">
+        <v>100</v>
+      </c>
+      <c r="I24" s="10">
+        <f t="shared" si="2"/>
+        <v>1150</v>
+      </c>
+      <c r="J24" s="10">
+        <f t="shared" si="1"/>
+        <v>290</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="9">
+        <v>500</v>
+      </c>
+      <c r="C25" s="9">
+        <v>200</v>
+      </c>
+      <c r="D25" s="9">
+        <v>120</v>
+      </c>
+      <c r="E25" s="9">
+        <v>60</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>190</v>
+      </c>
+      <c r="I25" s="10">
+        <f t="shared" si="2"/>
+        <v>1070</v>
+      </c>
+      <c r="J25" s="10">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="9">
+        <v>385</v>
+      </c>
+      <c r="C26" s="9">
+        <v>135</v>
+      </c>
+      <c r="D26" s="9">
+        <v>200</v>
+      </c>
+      <c r="E26" s="9">
+        <v>120</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>150</v>
+      </c>
+      <c r="I26" s="10">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="J26" s="10">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="9">
+        <v>400</v>
+      </c>
+      <c r="C27" s="9">
+        <v>180</v>
+      </c>
+      <c r="D27" s="9">
+        <v>150</v>
+      </c>
+      <c r="E27" s="9">
+        <v>100</v>
+      </c>
+      <c r="F27" s="9">
+        <v>300</v>
+      </c>
+      <c r="G27" s="9">
+        <v>6</v>
+      </c>
+      <c r="H27" s="9">
+        <v>215</v>
+      </c>
+      <c r="I27" s="10">
+        <f t="shared" si="2"/>
+        <v>1345</v>
+      </c>
+      <c r="J27" s="10">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="12"/>
+    </row>
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="9">
+        <v>480</v>
+      </c>
+      <c r="C28" s="9">
+        <v>120</v>
+      </c>
+      <c r="D28" s="9">
+        <v>60</v>
+      </c>
+      <c r="E28" s="9">
+        <v>20</v>
+      </c>
+      <c r="F28" s="9">
+        <v>150</v>
+      </c>
+      <c r="G28" s="9">
+        <v>3</v>
+      </c>
+      <c r="H28" s="9">
+        <v>240</v>
+      </c>
+      <c r="I28" s="10">
+        <f t="shared" si="2"/>
+        <v>1070</v>
+      </c>
+      <c r="J28" s="10">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="9">
+        <v>300</v>
+      </c>
+      <c r="C29" s="9">
+        <v>60</v>
+      </c>
+      <c r="D29" s="9">
+        <v>200</v>
+      </c>
+      <c r="E29" s="9">
+        <v>120</v>
+      </c>
+      <c r="F29" s="9">
+        <v>400</v>
+      </c>
+      <c r="G29" s="9">
+        <v>8</v>
+      </c>
+      <c r="H29" s="9">
+        <v>150</v>
+      </c>
+      <c r="I29" s="10">
+        <f t="shared" si="2"/>
+        <v>1230</v>
+      </c>
+      <c r="J29" s="10">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
-        <v>46261</v>
-      </c>
-      <c r="B20" s="9">
-        <v>320</v>
-      </c>
-      <c r="C20" s="9">
-        <v>100</v>
-      </c>
-      <c r="D20" s="9">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="9">
+        <v>420</v>
+      </c>
+      <c r="C30" s="9">
+        <v>78</v>
+      </c>
+      <c r="D30" s="9">
+        <v>200</v>
+      </c>
+      <c r="E30" s="9">
+        <v>75</v>
+      </c>
+      <c r="F30" s="9">
+        <v>250</v>
+      </c>
+      <c r="G30" s="9">
+        <v>5</v>
+      </c>
+      <c r="H30" s="9">
         <v>300</v>
       </c>
-      <c r="E20" s="9">
+      <c r="I30" s="10">
+        <f t="shared" si="2"/>
+        <v>1323</v>
+      </c>
+      <c r="J30" s="10">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="9">
+        <v>460</v>
+      </c>
+      <c r="C31" s="9">
         <v>90</v>
       </c>
-      <c r="F20" s="9">
+      <c r="D31" s="9">
+        <v>110</v>
+      </c>
+      <c r="E31" s="9">
+        <v>30</v>
+      </c>
+      <c r="F31" s="9">
+        <v>150</v>
+      </c>
+      <c r="G31" s="9">
         <v>3</v>
       </c>
-      <c r="G20" s="9">
+      <c r="H31" s="9">
         <v>150</v>
       </c>
-      <c r="H20" s="9">
+      <c r="I31" s="10">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="J31" s="10">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="9">
+        <v>300</v>
+      </c>
+      <c r="C32" s="9">
+        <v>30</v>
+      </c>
+      <c r="D32" s="9">
+        <v>60</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>120</v>
+      </c>
+      <c r="I32" s="10">
+        <f t="shared" si="2"/>
+        <v>510</v>
+      </c>
+      <c r="J32" s="10">
+        <f t="shared" si="1"/>
+        <v>930</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="9">
+        <v>460</v>
+      </c>
+      <c r="C33" s="9">
+        <v>20</v>
+      </c>
+      <c r="D33" s="9">
+        <v>190</v>
+      </c>
+      <c r="E33" s="9">
+        <v>60</v>
+      </c>
+      <c r="F33" s="9">
+        <v>0</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9">
+        <v>230</v>
+      </c>
+      <c r="I33" s="10">
+        <f t="shared" si="2"/>
+        <v>960</v>
+      </c>
+      <c r="J33" s="10">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="9">
+        <v>350</v>
+      </c>
+      <c r="C34" s="9">
+        <v>65</v>
+      </c>
+      <c r="D34" s="9">
+        <v>120</v>
+      </c>
+      <c r="E34" s="9">
+        <v>45</v>
+      </c>
+      <c r="F34" s="9">
+        <v>300</v>
+      </c>
+      <c r="G34" s="9">
+        <v>6</v>
+      </c>
+      <c r="H34" s="9">
+        <v>130</v>
+      </c>
+      <c r="I34" s="10">
+        <f t="shared" si="2"/>
+        <v>1010</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="9">
+        <v>200</v>
+      </c>
+      <c r="C35" s="9">
+        <v>45</v>
+      </c>
+      <c r="D35" s="9">
+        <v>270</v>
+      </c>
+      <c r="E35" s="9">
+        <v>80</v>
+      </c>
+      <c r="F35" s="9">
         <v>150</v>
       </c>
-      <c r="I20" s="10">
-        <f t="shared" si="0"/>
-        <v>963</v>
-      </c>
-      <c r="J20" s="10">
+      <c r="G35" s="9">
+        <v>3</v>
+      </c>
+      <c r="H35" s="9">
+        <v>120</v>
+      </c>
+      <c r="I35" s="10">
+        <f t="shared" si="2"/>
+        <v>865</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
-        <v>477</v>
-      </c>
-      <c r="K20" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="K35" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L35" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="9">
+        <v>350</v>
+      </c>
+      <c r="C36" s="9">
+        <v>80</v>
+      </c>
+      <c r="D36" s="9">
+        <v>70</v>
+      </c>
+      <c r="E36" s="9">
+        <v>30</v>
+      </c>
+      <c r="F36" s="9">
+        <v>400</v>
+      </c>
+      <c r="G36" s="9">
+        <v>8</v>
+      </c>
+      <c r="H36" s="9">
+        <v>80</v>
+      </c>
+      <c r="I36" s="10">
+        <f t="shared" si="2"/>
+        <v>1010</v>
+      </c>
+      <c r="J36" s="10">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L36" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M20" s="11" t="s">
+      <c r="M36" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="9">
+        <v>400</v>
+      </c>
+      <c r="C37" s="9">
+        <v>95</v>
+      </c>
+      <c r="D37" s="9">
+        <v>150</v>
+      </c>
+      <c r="E37" s="9">
+        <v>45</v>
+      </c>
+      <c r="F37" s="9">
+        <v>250</v>
+      </c>
+      <c r="G37" s="9">
+        <v>5</v>
+      </c>
+      <c r="H37" s="9">
+        <v>70</v>
+      </c>
+      <c r="I37" s="10">
+        <f t="shared" si="2"/>
+        <v>1010</v>
+      </c>
+      <c r="J37" s="10">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="9">
+        <v>340</v>
+      </c>
+      <c r="C38" s="9">
+        <v>120</v>
+      </c>
+      <c r="D38" s="9">
+        <v>240</v>
+      </c>
+      <c r="E38" s="9">
+        <v>60</v>
+      </c>
+      <c r="F38" s="9">
+        <v>250</v>
+      </c>
+      <c r="G38" s="9">
+        <v>5</v>
+      </c>
+      <c r="H38" s="9">
+        <v>150</v>
+      </c>
+      <c r="I38" s="10">
+        <f t="shared" si="2"/>
+        <v>1160</v>
+      </c>
+      <c r="J38" s="10">
+        <f t="shared" si="1"/>
+        <v>280</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N20" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
-        <v>46262</v>
-      </c>
-      <c r="B21" s="9">
-        <v>300</v>
-      </c>
-      <c r="C21" s="9">
-        <v>120</v>
-      </c>
-      <c r="D21" s="9">
+      <c r="N38" s="12"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="9">
+        <v>420</v>
+      </c>
+      <c r="C39" s="9">
         <v>60</v>
       </c>
-      <c r="E21" s="9">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9">
-        <v>250</v>
-      </c>
-      <c r="G21" s="9">
-        <v>5</v>
-      </c>
-      <c r="H21" s="9">
-        <v>150</v>
-      </c>
-      <c r="I21" s="10">
-        <f t="shared" si="0"/>
+      <c r="D39" s="9">
+        <v>200</v>
+      </c>
+      <c r="E39" s="9">
+        <v>80</v>
+      </c>
+      <c r="F39" s="9">
+        <v>30</v>
+      </c>
+      <c r="G39" s="9">
+        <v>1</v>
+      </c>
+      <c r="H39" s="9">
+        <v>90</v>
+      </c>
+      <c r="I39" s="10">
+        <f t="shared" si="2"/>
         <v>880</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J39" s="10">
         <f t="shared" si="1"/>
         <v>560</v>
       </c>
-      <c r="K21" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N21" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
-        <v>46263</v>
-      </c>
-      <c r="B22" s="9">
-        <v>350</v>
-      </c>
-      <c r="C22" s="9">
-        <v>60</v>
-      </c>
-      <c r="D22" s="9">
-        <v>300</v>
-      </c>
-      <c r="E22" s="9">
-        <v>120</v>
-      </c>
-      <c r="F22" s="9">
-        <v>0</v>
-      </c>
-      <c r="G22" s="9">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9">
-        <v>250</v>
-      </c>
-      <c r="I22" s="10">
-        <f t="shared" si="0"/>
-        <v>1080</v>
-      </c>
-      <c r="J22" s="10">
-        <f t="shared" si="1"/>
-        <v>360</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N22" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
-        <v>46264</v>
-      </c>
-      <c r="B23" s="9">
-        <v>440</v>
-      </c>
-      <c r="C23" s="9">
-        <v>45</v>
-      </c>
-      <c r="D23" s="9">
-        <v>270</v>
-      </c>
-      <c r="E23" s="9">
-        <v>90</v>
-      </c>
-      <c r="F23" s="9">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9">
-        <v>400</v>
-      </c>
-      <c r="I23" s="10">
-        <f t="shared" ref="I23:I85" si="2">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
-        <v>1245</v>
-      </c>
-      <c r="J23" s="10">
-        <f t="shared" si="1"/>
-        <v>195</v>
-      </c>
-      <c r="K23" s="11" t="s">
+      <c r="K39" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L39" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="18">
-        <v>46265</v>
-      </c>
-      <c r="B24" s="19">
-        <v>230</v>
-      </c>
-      <c r="C24" s="19">
-        <v>90</v>
-      </c>
-      <c r="D24" s="19">
-        <v>90</v>
-      </c>
-      <c r="E24" s="19">
-        <v>120</v>
-      </c>
-      <c r="F24" s="19">
-        <v>300</v>
-      </c>
-      <c r="G24" s="19">
-        <v>6</v>
-      </c>
-      <c r="H24" s="19">
-        <v>270</v>
-      </c>
-      <c r="I24" s="20">
-        <f t="shared" si="2"/>
-        <v>1100</v>
-      </c>
-      <c r="J24" s="20">
-        <f t="shared" si="1"/>
-        <v>340</v>
-      </c>
-      <c r="K24" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="L24" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="M24" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="N24" s="22" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="23">
-        <v>46266</v>
-      </c>
-      <c r="B25" s="24">
-        <v>450</v>
-      </c>
-      <c r="C25" s="24">
-        <v>80</v>
-      </c>
-      <c r="D25" s="24">
-        <v>130</v>
-      </c>
-      <c r="E25" s="24">
-        <v>45</v>
-      </c>
-      <c r="F25" s="24">
-        <v>150</v>
-      </c>
-      <c r="G25" s="24">
-        <v>3</v>
-      </c>
-      <c r="H25" s="24">
-        <v>260</v>
-      </c>
-      <c r="I25" s="25">
-        <f t="shared" si="2"/>
-        <v>1115</v>
-      </c>
-      <c r="J25" s="25">
-        <f t="shared" si="1"/>
-        <v>325</v>
-      </c>
-      <c r="K25" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="L25" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="M25" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="N25" s="27"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
-        <v>46267</v>
-      </c>
-      <c r="B26" s="9">
-        <v>400</v>
-      </c>
-      <c r="C26" s="9">
-        <v>35</v>
-      </c>
-      <c r="D26" s="9">
-        <v>150</v>
-      </c>
-      <c r="E26" s="9">
-        <v>100</v>
-      </c>
-      <c r="F26" s="9">
-        <v>400</v>
-      </c>
-      <c r="G26" s="9">
-        <v>8</v>
-      </c>
-      <c r="H26" s="9">
-        <v>90</v>
-      </c>
-      <c r="I26" s="10">
-        <f t="shared" si="2"/>
-        <v>1175</v>
-      </c>
-      <c r="J26" s="10">
-        <f t="shared" si="1"/>
-        <v>265</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L26" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
-        <v>46268</v>
-      </c>
-      <c r="B27" s="9">
-        <v>420</v>
-      </c>
-      <c r="C27" s="9">
-        <v>150</v>
-      </c>
-      <c r="D27" s="9">
-        <v>60</v>
-      </c>
-      <c r="E27" s="9">
-        <v>100</v>
-      </c>
-      <c r="F27" s="9">
-        <v>300</v>
-      </c>
-      <c r="G27" s="9">
-        <v>6</v>
-      </c>
-      <c r="H27" s="9">
-        <v>80</v>
-      </c>
-      <c r="I27" s="10">
-        <f t="shared" si="2"/>
-        <v>1110</v>
-      </c>
-      <c r="J27" s="10">
-        <f t="shared" si="1"/>
-        <v>330</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N27" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
-        <v>46269</v>
-      </c>
-      <c r="B28" s="9">
-        <v>370</v>
-      </c>
-      <c r="C28" s="9">
-        <v>180</v>
-      </c>
-      <c r="D28" s="9">
-        <v>180</v>
-      </c>
-      <c r="E28" s="9">
-        <v>70</v>
-      </c>
-      <c r="F28" s="9">
-        <v>250</v>
-      </c>
-      <c r="G28" s="9">
-        <v>5</v>
-      </c>
-      <c r="H28" s="9">
-        <v>100</v>
-      </c>
-      <c r="I28" s="10">
-        <f t="shared" si="2"/>
-        <v>1150</v>
-      </c>
-      <c r="J28" s="10">
-        <f t="shared" si="1"/>
-        <v>290</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L28" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
-        <v>46270</v>
-      </c>
-      <c r="B29" s="9">
-        <v>500</v>
-      </c>
-      <c r="C29" s="9">
-        <v>200</v>
-      </c>
-      <c r="D29" s="9">
-        <v>120</v>
-      </c>
-      <c r="E29" s="9">
-        <v>60</v>
-      </c>
-      <c r="F29" s="9">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9">
-        <v>0</v>
-      </c>
-      <c r="H29" s="9">
-        <v>190</v>
-      </c>
-      <c r="I29" s="10">
-        <f t="shared" si="2"/>
-        <v>1070</v>
-      </c>
-      <c r="J29" s="10">
-        <f t="shared" si="1"/>
-        <v>370</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
-        <v>46271</v>
-      </c>
-      <c r="B30" s="9">
-        <v>385</v>
-      </c>
-      <c r="C30" s="9">
-        <v>135</v>
-      </c>
-      <c r="D30" s="9">
-        <v>200</v>
-      </c>
-      <c r="E30" s="9">
-        <v>120</v>
-      </c>
-      <c r="F30" s="9">
-        <v>0</v>
-      </c>
-      <c r="G30" s="9">
-        <v>0</v>
-      </c>
-      <c r="H30" s="9">
-        <v>150</v>
-      </c>
-      <c r="I30" s="10">
-        <f t="shared" si="2"/>
-        <v>990</v>
-      </c>
-      <c r="J30" s="10">
-        <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L30" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N30" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
-        <v>46272</v>
-      </c>
-      <c r="B31" s="9">
-        <v>400</v>
-      </c>
-      <c r="C31" s="9">
-        <v>180</v>
-      </c>
-      <c r="D31" s="9">
-        <v>150</v>
-      </c>
-      <c r="E31" s="9">
-        <v>100</v>
-      </c>
-      <c r="F31" s="9">
-        <v>300</v>
-      </c>
-      <c r="G31" s="9">
-        <v>6</v>
-      </c>
-      <c r="H31" s="9">
-        <v>215</v>
-      </c>
-      <c r="I31" s="10">
-        <f t="shared" si="2"/>
-        <v>1345</v>
-      </c>
-      <c r="J31" s="10">
-        <f t="shared" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L31" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N31" s="12"/>
-    </row>
-    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
-        <v>46273</v>
-      </c>
-      <c r="B32" s="9">
-        <v>480</v>
-      </c>
-      <c r="C32" s="9">
-        <v>120</v>
-      </c>
-      <c r="D32" s="9">
-        <v>60</v>
-      </c>
-      <c r="E32" s="9">
-        <v>20</v>
-      </c>
-      <c r="F32" s="9">
-        <v>150</v>
-      </c>
-      <c r="G32" s="9">
-        <v>3</v>
-      </c>
-      <c r="H32" s="9">
-        <v>240</v>
-      </c>
-      <c r="I32" s="10">
-        <f t="shared" si="2"/>
-        <v>1070</v>
-      </c>
-      <c r="J32" s="10">
-        <f t="shared" si="1"/>
-        <v>370</v>
-      </c>
-      <c r="K32" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="L32" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="M32" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N32" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
-        <v>46274</v>
-      </c>
-      <c r="B33" s="9">
-        <v>300</v>
-      </c>
-      <c r="C33" s="9">
-        <v>60</v>
-      </c>
-      <c r="D33" s="9">
-        <v>200</v>
-      </c>
-      <c r="E33" s="9">
-        <v>120</v>
-      </c>
-      <c r="F33" s="9">
-        <v>400</v>
-      </c>
-      <c r="G33" s="9">
-        <v>8</v>
-      </c>
-      <c r="H33" s="9">
-        <v>150</v>
-      </c>
-      <c r="I33" s="10">
-        <f t="shared" si="2"/>
-        <v>1230</v>
-      </c>
-      <c r="J33" s="10">
-        <f t="shared" si="1"/>
-        <v>210</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L33" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M33" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N33" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8">
-        <v>46275</v>
-      </c>
-      <c r="B34" s="9">
-        <v>420</v>
-      </c>
-      <c r="C34" s="9">
-        <v>78</v>
-      </c>
-      <c r="D34" s="9">
-        <v>200</v>
-      </c>
-      <c r="E34" s="9">
-        <v>75</v>
-      </c>
-      <c r="F34" s="9">
-        <v>250</v>
-      </c>
-      <c r="G34" s="9">
-        <v>5</v>
-      </c>
-      <c r="H34" s="9">
-        <v>300</v>
-      </c>
-      <c r="I34" s="10">
-        <f t="shared" si="2"/>
-        <v>1323</v>
-      </c>
-      <c r="J34" s="10">
-        <f t="shared" si="1"/>
-        <v>117</v>
-      </c>
-      <c r="K34" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L34" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="M34" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N34" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
-        <v>46276</v>
-      </c>
-      <c r="B35" s="9">
-        <v>460</v>
-      </c>
-      <c r="C35" s="9">
-        <v>90</v>
-      </c>
-      <c r="D35" s="9">
-        <v>110</v>
-      </c>
-      <c r="E35" s="9">
-        <v>30</v>
-      </c>
-      <c r="F35" s="9">
-        <v>150</v>
-      </c>
-      <c r="G35" s="9">
-        <v>3</v>
-      </c>
-      <c r="H35" s="9">
-        <v>150</v>
-      </c>
-      <c r="I35" s="10">
-        <f t="shared" si="2"/>
-        <v>990</v>
-      </c>
-      <c r="J35" s="10">
-        <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L35" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M35" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N35" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="8">
-        <v>46277</v>
-      </c>
-      <c r="B36" s="9">
-        <v>300</v>
-      </c>
-      <c r="C36" s="9">
-        <v>30</v>
-      </c>
-      <c r="D36" s="9">
-        <v>60</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0</v>
-      </c>
-      <c r="F36" s="9">
-        <v>0</v>
-      </c>
-      <c r="G36" s="9">
-        <v>0</v>
-      </c>
-      <c r="H36" s="9">
-        <v>120</v>
-      </c>
-      <c r="I36" s="10">
-        <f t="shared" si="2"/>
-        <v>510</v>
-      </c>
-      <c r="J36" s="10">
-        <f t="shared" si="1"/>
-        <v>930</v>
-      </c>
-      <c r="K36" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L36" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M36" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N36" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="8">
-        <v>46278</v>
-      </c>
-      <c r="B37" s="9">
-        <v>460</v>
-      </c>
-      <c r="C37" s="9">
-        <v>20</v>
-      </c>
-      <c r="D37" s="9">
-        <v>190</v>
-      </c>
-      <c r="E37" s="9">
-        <v>60</v>
-      </c>
-      <c r="F37" s="9">
-        <v>0</v>
-      </c>
-      <c r="G37" s="9">
-        <v>0</v>
-      </c>
-      <c r="H37" s="9">
-        <v>230</v>
-      </c>
-      <c r="I37" s="10">
-        <f t="shared" si="2"/>
-        <v>960</v>
-      </c>
-      <c r="J37" s="10">
-        <f t="shared" si="1"/>
-        <v>480</v>
-      </c>
-      <c r="K37" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M37" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N37" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8">
-        <v>46279</v>
-      </c>
-      <c r="B38" s="9">
-        <v>350</v>
-      </c>
-      <c r="C38" s="9">
-        <v>65</v>
-      </c>
-      <c r="D38" s="9">
-        <v>120</v>
-      </c>
-      <c r="E38" s="9">
-        <v>45</v>
-      </c>
-      <c r="F38" s="9">
-        <v>300</v>
-      </c>
-      <c r="G38" s="9">
-        <v>6</v>
-      </c>
-      <c r="H38" s="9">
-        <v>130</v>
-      </c>
-      <c r="I38" s="10">
-        <f t="shared" si="2"/>
-        <v>1010</v>
-      </c>
-      <c r="J38" s="10">
-        <f t="shared" si="1"/>
-        <v>430</v>
-      </c>
-      <c r="K38" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="M38" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N38" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="8">
-        <v>46280</v>
-      </c>
-      <c r="B39" s="9">
-        <v>200</v>
-      </c>
-      <c r="C39" s="9">
-        <v>45</v>
-      </c>
-      <c r="D39" s="9">
-        <v>270</v>
-      </c>
-      <c r="E39" s="9">
-        <v>80</v>
-      </c>
-      <c r="F39" s="9">
-        <v>150</v>
-      </c>
-      <c r="G39" s="9">
-        <v>3</v>
-      </c>
-      <c r="H39" s="9">
-        <v>120</v>
-      </c>
-      <c r="I39" s="10">
-        <f t="shared" si="2"/>
-        <v>865</v>
-      </c>
-      <c r="J39" s="10">
-        <f t="shared" si="1"/>
-        <v>575</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L39" s="11" t="s">
-        <v>50</v>
       </c>
       <c r="M39" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N39" s="12" t="s">
-        <v>87</v>
-      </c>
+      <c r="N39" s="12"/>
     </row>
     <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
-        <v>46281</v>
+        <v>46285</v>
       </c>
       <c r="B40" s="9">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C40" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D40" s="9">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="E40" s="9">
         <v>30</v>
       </c>
       <c r="F40" s="9">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G40" s="9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H40" s="9">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="2"/>
-        <v>1010</v>
+        <v>930</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>510</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M40" s="11" t="s">
         <v>63</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B41" s="9">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="C41" s="9">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="D41" s="9">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="E41" s="9">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F41" s="9">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G41" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H41" s="9">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="I41" s="10">
         <f t="shared" si="2"/>
-        <v>1010</v>
+        <v>1165</v>
       </c>
       <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>275</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M41" s="11" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="B42" s="9">
         <v>340</v>
       </c>
       <c r="C42" s="9">
+        <v>170</v>
+      </c>
+      <c r="D42" s="9">
+        <v>180</v>
+      </c>
+      <c r="E42" s="9">
+        <v>40</v>
+      </c>
+      <c r="F42" s="9">
+        <v>150</v>
+      </c>
+      <c r="G42" s="9">
+        <v>3</v>
+      </c>
+      <c r="H42" s="9">
         <v>120</v>
-      </c>
-      <c r="D42" s="9">
-        <v>240</v>
-      </c>
-      <c r="E42" s="9">
-        <v>60</v>
-      </c>
-      <c r="F42" s="9">
-        <v>250</v>
-      </c>
-      <c r="G42" s="9">
-        <v>5</v>
-      </c>
-      <c r="H42" s="9">
-        <v>150</v>
       </c>
       <c r="I42" s="10">
         <f t="shared" si="2"/>
-        <v>1160</v>
+        <v>1000</v>
       </c>
       <c r="J42" s="10">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>440</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>49</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M42" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N42" s="12"/>
+      <c r="N42" s="12" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8">
-        <v>46284</v>
-      </c>
-      <c r="B43" s="9">
-        <v>420</v>
-      </c>
-      <c r="C43" s="9">
-        <v>60</v>
-      </c>
-      <c r="D43" s="9">
-        <v>200</v>
-      </c>
-      <c r="E43" s="9">
-        <v>80</v>
-      </c>
-      <c r="F43" s="9">
-        <v>30</v>
-      </c>
-      <c r="G43" s="9">
-        <v>1</v>
-      </c>
-      <c r="H43" s="9">
-        <v>90</v>
-      </c>
-      <c r="I43" s="10">
+      <c r="A43" s="13"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>880</v>
-      </c>
-      <c r="J43" s="10">
+        <v/>
+      </c>
+      <c r="J43" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>560</v>
-      </c>
-      <c r="K43" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L43" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="M43" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N43" s="12"/>
-    </row>
-    <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="8">
-        <v>46285</v>
-      </c>
-      <c r="B44" s="9">
-        <v>300</v>
-      </c>
-      <c r="C44" s="9">
-        <v>60</v>
-      </c>
-      <c r="D44" s="9">
-        <v>300</v>
-      </c>
-      <c r="E44" s="9">
-        <v>30</v>
-      </c>
-      <c r="F44" s="9">
-        <v>0</v>
-      </c>
-      <c r="G44" s="9">
-        <v>0</v>
-      </c>
-      <c r="H44" s="9">
-        <v>240</v>
-      </c>
-      <c r="I44" s="10">
+        <v/>
+      </c>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="17"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="13"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>930</v>
-      </c>
-      <c r="J44" s="10">
+        <v/>
+      </c>
+      <c r="J44" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>510</v>
-      </c>
-      <c r="K44" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="L44" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="M44" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N44" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="8">
-        <v>46286</v>
-      </c>
-      <c r="B45" s="9">
-        <v>200</v>
-      </c>
-      <c r="C45" s="9">
-        <v>45</v>
-      </c>
-      <c r="D45" s="9">
-        <v>380</v>
-      </c>
-      <c r="E45" s="9">
-        <v>60</v>
-      </c>
-      <c r="F45" s="9">
-        <v>300</v>
-      </c>
-      <c r="G45" s="9">
-        <v>6</v>
-      </c>
-      <c r="H45" s="9">
-        <v>180</v>
-      </c>
-      <c r="I45" s="10">
+        <v/>
+      </c>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="17"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="13"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>1165</v>
-      </c>
-      <c r="J45" s="10">
+        <v/>
+      </c>
+      <c r="J45" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>275</v>
-      </c>
-      <c r="K45" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="L45" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M45" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N45" s="12" t="s">
-        <v>90</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
@@ -3365,7 +3434,7 @@
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3387,7 +3456,7 @@
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3409,7 +3478,7 @@
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3431,7 +3500,7 @@
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3453,7 +3522,7 @@
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" ref="J73:J136" si="3">IF(I73="","",1440-I73)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3647,7 +3716,7 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I82:I145" si="4">IF(SUM(B82:F82,H82)=0,"",SUM(B82:F82,H82))</f>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
@@ -3669,7 +3738,7 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
@@ -3691,7 +3760,7 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
@@ -3713,7 +3782,7 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
@@ -3735,7 +3804,7 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" ref="I86:I149" si="4">IF(SUM(B86:F86,H86)=0,"",SUM(B86:F86,H86))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
@@ -4773,7 +4842,7 @@
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4795,7 +4864,7 @@
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4817,7 +4886,7 @@
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4839,7 +4908,7 @@
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4861,7 +4930,7 @@
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" ref="J137:J200" si="5">IF(I137="","",1440-I137)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -5055,7 +5124,7 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I146:I209" si="6">IF(SUM(B146:F146,H146)=0,"",SUM(B146:F146,H146))</f>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
@@ -5077,7 +5146,7 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
@@ -5099,7 +5168,7 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
@@ -5121,7 +5190,7 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
@@ -5143,7 +5212,7 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" ref="I150:I213" si="6">IF(SUM(B150:F150,H150)=0,"",SUM(B150:F150,H150))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
@@ -6181,7 +6250,7 @@
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6203,7 +6272,7 @@
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6225,7 +6294,7 @@
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6247,7 +6316,7 @@
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6269,7 +6338,7 @@
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" ref="J201:J264" si="7">IF(I201="","",1440-I201)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6463,7 +6532,7 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I210:I273" si="8">IF(SUM(B210:F210,H210)=0,"",SUM(B210:F210,H210))</f>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
@@ -6485,7 +6554,7 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
@@ -6507,7 +6576,7 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
@@ -6529,7 +6598,7 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
@@ -6551,7 +6620,7 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" ref="I214:I277" si="8">IF(SUM(B214:F214,H214)=0,"",SUM(B214:F214,H214))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
@@ -7589,7 +7658,7 @@
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7611,7 +7680,7 @@
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7633,7 +7702,7 @@
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7655,7 +7724,7 @@
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7677,7 +7746,7 @@
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" ref="J265:J328" si="9">IF(I265="","",1440-I265)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7871,7 +7940,7 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I274:I337" si="10">IF(SUM(B274:F274,H274)=0,"",SUM(B274:F274,H274))</f>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
@@ -7893,7 +7962,7 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
@@ -7915,7 +7984,7 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
@@ -7937,7 +8006,7 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
@@ -7959,7 +8028,7 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" ref="I278:I341" si="10">IF(SUM(B278:F278,H278)=0,"",SUM(B278:F278,H278))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
@@ -8997,7 +9066,7 @@
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9019,7 +9088,7 @@
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9041,7 +9110,7 @@
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9063,7 +9132,7 @@
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9085,7 +9154,7 @@
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" ref="J329:J392" si="11">IF(I329="","",1440-I329)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9279,7 +9348,7 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I338:I400" si="12">IF(SUM(B338:F338,H338)=0,"",SUM(B338:F338,H338))</f>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
@@ -9301,7 +9370,7 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
@@ -9323,7 +9392,7 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
@@ -9345,7 +9414,7 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
@@ -9367,7 +9436,7 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" ref="I342:I404" si="12">IF(SUM(B342:F342,H342)=0,"",SUM(B342:F342,H342))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
@@ -10405,7 +10474,7 @@
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10427,7 +10496,7 @@
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10449,7 +10518,7 @@
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10471,7 +10540,7 @@
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10493,7 +10562,7 @@
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" ref="J393:J404" si="13">IF(I393="","",1440-I393)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10655,94 +10724,6 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
-    </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A402" s="13"/>
-      <c r="B402" s="14"/>
-      <c r="C402" s="14"/>
-      <c r="D402" s="14"/>
-      <c r="E402" s="14"/>
-      <c r="F402" s="14"/>
-      <c r="G402" s="14"/>
-      <c r="H402" s="14"/>
-      <c r="I402" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J402" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K402" s="16"/>
-      <c r="L402" s="16"/>
-      <c r="M402" s="16"/>
-      <c r="N402" s="17"/>
-    </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A403" s="13"/>
-      <c r="B403" s="14"/>
-      <c r="C403" s="14"/>
-      <c r="D403" s="14"/>
-      <c r="E403" s="14"/>
-      <c r="F403" s="14"/>
-      <c r="G403" s="14"/>
-      <c r="H403" s="14"/>
-      <c r="I403" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J403" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K403" s="16"/>
-      <c r="L403" s="16"/>
-      <c r="M403" s="16"/>
-      <c r="N403" s="17"/>
-    </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A404" s="13"/>
-      <c r="B404" s="14"/>
-      <c r="C404" s="14"/>
-      <c r="D404" s="14"/>
-      <c r="E404" s="14"/>
-      <c r="F404" s="14"/>
-      <c r="G404" s="14"/>
-      <c r="H404" s="14"/>
-      <c r="I404" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J404" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K404" s="16"/>
-      <c r="L404" s="16"/>
-      <c r="M404" s="16"/>
-      <c r="N404" s="17"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10752,21 +10733,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J404">
+  <conditionalFormatting sqref="J6:J400">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K11:K404" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L11:L404" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M11:M404" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D573A7FD-FF84-477A-9F50-43D97F445452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3309DF24-E38C-41FD-99D3-633000BB7CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Excited to take tomorrow English class</t>
+  </si>
+  <si>
+    <t>Preparing for English CA</t>
   </si>
 </sst>
 </file>
@@ -2849,26 +2852,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="9">
+        <v>420</v>
+      </c>
+      <c r="C43" s="9">
+        <v>90</v>
+      </c>
+      <c r="D43" s="9">
+        <v>200</v>
+      </c>
+      <c r="E43" s="9">
+        <v>150</v>
+      </c>
+      <c r="F43" s="9">
+        <v>400</v>
+      </c>
+      <c r="G43" s="9">
+        <v>8</v>
+      </c>
+      <c r="H43" s="9">
+        <v>100</v>
+      </c>
+      <c r="I43" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J43" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3309DF24-E38C-41FD-99D3-633000BB7CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8D3513-CBE4-4A48-BD2C-7FED37AB084E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2898,26 +2898,48 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="9">
+        <v>360</v>
+      </c>
+      <c r="C44" s="9">
+        <v>140</v>
+      </c>
+      <c r="D44" s="9">
+        <v>160</v>
+      </c>
+      <c r="E44" s="9">
+        <v>90</v>
+      </c>
+      <c r="F44" s="9">
+        <v>200</v>
+      </c>
+      <c r="G44" s="9">
+        <v>4</v>
+      </c>
+      <c r="H44" s="9">
+        <v>120</v>
+      </c>
+      <c r="I44" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8D3513-CBE4-4A48-BD2C-7FED37AB084E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC087ABD-D2E6-4D6A-922A-70B42B00FAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC087ABD-D2E6-4D6A-922A-70B42B00FAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99800FE-D3D5-4E97-96DF-27C77C9939E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,15 @@
   </si>
   <si>
     <t>Preparing for English CA</t>
+  </si>
+  <si>
+    <t>Exicted for first hackathon</t>
+  </si>
+  <si>
+    <t>Very tired after the hackathon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPU Protest </t>
   </si>
 </sst>
 </file>
@@ -2942,92 +2951,166 @@
       <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B45" s="9">
+        <v>300</v>
+      </c>
+      <c r="C45" s="9">
+        <v>120</v>
+      </c>
+      <c r="D45" s="9">
+        <v>90</v>
+      </c>
+      <c r="E45" s="9">
+        <v>60</v>
+      </c>
+      <c r="F45" s="9">
+        <v>300</v>
+      </c>
+      <c r="G45" s="9">
+        <v>5</v>
+      </c>
+      <c r="H45" s="9">
+        <v>420</v>
+      </c>
+      <c r="I45" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J45" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+        <v>150</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B46" s="9">
+        <v>420</v>
+      </c>
+      <c r="C46" s="9">
+        <v>45</v>
+      </c>
+      <c r="D46" s="9">
+        <v>60</v>
+      </c>
+      <c r="E46" s="9">
+        <v>120</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>540</v>
+      </c>
+      <c r="I46" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J46" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+        <v>255</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B47" s="9">
+        <v>360</v>
+      </c>
+      <c r="C47" s="9">
+        <v>0</v>
+      </c>
+      <c r="D47" s="9">
+        <v>60</v>
+      </c>
+      <c r="E47" s="9">
+        <v>30</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>450</v>
+      </c>
+      <c r="J47" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>990</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J48" s="15" t="str">
+      <c r="J48" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99800FE-D3D5-4E97-96DF-27C77C9939E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D81344E-F10D-40A0-BF8C-CBCB175367DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t xml:space="preserve">LPU Protest </t>
+  </si>
+  <si>
+    <t>Whole day spend in travelling</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N400"/>
+  <dimension ref="A1:N392"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1242,7 +1245,7 @@
         <v>1015</v>
       </c>
       <c r="J7" s="10">
-        <f t="shared" ref="J7:J68" si="1">IF(I7="","",1440-I7)</f>
+        <f t="shared" ref="J7:J60" si="1">IF(I7="","",1440-I7)</f>
         <v>425</v>
       </c>
       <c r="K7" s="11" t="s">
@@ -1790,7 +1793,7 @@
         <v>400</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" ref="I19:I81" si="2">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
+        <f t="shared" ref="I19:I73" si="2">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
         <v>1245</v>
       </c>
       <c r="J19" s="10">
@@ -3088,51 +3091,97 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>46293</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
+      <c r="B48" s="9">
+        <v>180</v>
+      </c>
+      <c r="C48" s="9">
+        <v>0</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>0</v>
+      </c>
+      <c r="I48" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
+        <v>180</v>
+      </c>
+      <c r="J48" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B49" s="9">
+        <v>120</v>
+      </c>
+      <c r="C49" s="9">
+        <v>10</v>
+      </c>
+      <c r="D49" s="9">
+        <v>60</v>
+      </c>
+      <c r="E49" s="9">
+        <v>30</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>0</v>
+      </c>
+      <c r="I49" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>220</v>
+      </c>
+      <c r="J49" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>1220</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
@@ -3390,7 +3439,7 @@
         <v/>
       </c>
       <c r="J61" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J61:J124" si="3">IF(I61="","",1440-I61)</f>
         <v/>
       </c>
       <c r="K61" s="16"/>
@@ -3412,7 +3461,7 @@
         <v/>
       </c>
       <c r="J62" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K62" s="16"/>
@@ -3434,7 +3483,7 @@
         <v/>
       </c>
       <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K63" s="16"/>
@@ -3456,7 +3505,7 @@
         <v/>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K64" s="16"/>
@@ -3478,7 +3527,7 @@
         <v/>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -3500,7 +3549,7 @@
         <v/>
       </c>
       <c r="J66" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K66" s="16"/>
@@ -3522,7 +3571,7 @@
         <v/>
       </c>
       <c r="J67" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K67" s="16"/>
@@ -3544,7 +3593,7 @@
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -3566,7 +3615,7 @@
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3672,7 +3721,7 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I74:I137" si="4">IF(SUM(B74:F74,H74)=0,"",SUM(B74:F74,H74))</f>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
@@ -3694,7 +3743,7 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
@@ -3716,7 +3765,7 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
@@ -3738,7 +3787,7 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
@@ -3760,7 +3809,7 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
@@ -3782,7 +3831,7 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
@@ -3804,7 +3853,7 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
@@ -3826,7 +3875,7 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
@@ -3848,7 +3897,7 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" ref="I82:I145" si="4">IF(SUM(B82:F82,H82)=0,"",SUM(B82:F82,H82))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
@@ -4798,7 +4847,7 @@
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J125:J188" si="5">IF(I125="","",1440-I125)</f>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4820,7 +4869,7 @@
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4842,7 +4891,7 @@
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4864,7 +4913,7 @@
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4886,7 +4935,7 @@
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4908,7 +4957,7 @@
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4930,7 +4979,7 @@
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4952,7 +5001,7 @@
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4974,7 +5023,7 @@
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -5080,7 +5129,7 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I138:I201" si="6">IF(SUM(B138:F138,H138)=0,"",SUM(B138:F138,H138))</f>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
@@ -5102,7 +5151,7 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
@@ -5124,7 +5173,7 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
@@ -5146,7 +5195,7 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
@@ -5168,7 +5217,7 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
@@ -5190,7 +5239,7 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
@@ -5212,7 +5261,7 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
@@ -5234,7 +5283,7 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
@@ -5256,7 +5305,7 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" ref="I146:I209" si="6">IF(SUM(B146:F146,H146)=0,"",SUM(B146:F146,H146))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
@@ -6206,7 +6255,7 @@
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J189:J252" si="7">IF(I189="","",1440-I189)</f>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6228,7 +6277,7 @@
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6250,7 +6299,7 @@
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6272,7 +6321,7 @@
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6294,7 +6343,7 @@
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6316,7 +6365,7 @@
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6338,7 +6387,7 @@
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6360,7 +6409,7 @@
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6382,7 +6431,7 @@
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6488,7 +6537,7 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I202:I265" si="8">IF(SUM(B202:F202,H202)=0,"",SUM(B202:F202,H202))</f>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
@@ -6510,7 +6559,7 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
@@ -6532,7 +6581,7 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
@@ -6554,7 +6603,7 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
@@ -6576,7 +6625,7 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
@@ -6598,7 +6647,7 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
@@ -6620,7 +6669,7 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
@@ -6642,7 +6691,7 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
@@ -6664,7 +6713,7 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" ref="I210:I273" si="8">IF(SUM(B210:F210,H210)=0,"",SUM(B210:F210,H210))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
@@ -7614,7 +7663,7 @@
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J253:J316" si="9">IF(I253="","",1440-I253)</f>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7636,7 +7685,7 @@
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7658,7 +7707,7 @@
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7680,7 +7729,7 @@
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7702,7 +7751,7 @@
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7724,7 +7773,7 @@
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7746,7 +7795,7 @@
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7768,7 +7817,7 @@
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7790,7 +7839,7 @@
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7896,7 +7945,7 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I266:I329" si="10">IF(SUM(B266:F266,H266)=0,"",SUM(B266:F266,H266))</f>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
@@ -7918,7 +7967,7 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
@@ -7940,7 +7989,7 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
@@ -7962,7 +8011,7 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
@@ -7984,7 +8033,7 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
@@ -8006,7 +8055,7 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
@@ -8028,7 +8077,7 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
@@ -8050,7 +8099,7 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
@@ -8072,7 +8121,7 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" ref="I274:I337" si="10">IF(SUM(B274:F274,H274)=0,"",SUM(B274:F274,H274))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
@@ -9022,7 +9071,7 @@
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J317:J380" si="11">IF(I317="","",1440-I317)</f>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -9044,7 +9093,7 @@
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -9066,7 +9115,7 @@
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -9088,7 +9137,7 @@
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9110,7 +9159,7 @@
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9132,7 +9181,7 @@
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9154,7 +9203,7 @@
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9176,7 +9225,7 @@
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9198,7 +9247,7 @@
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9304,7 +9353,7 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I330:I392" si="12">IF(SUM(B330:F330,H330)=0,"",SUM(B330:F330,H330))</f>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
@@ -9326,7 +9375,7 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
@@ -9348,7 +9397,7 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
@@ -9370,7 +9419,7 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
@@ -9392,7 +9441,7 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
@@ -9414,7 +9463,7 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
@@ -9436,7 +9485,7 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
@@ -9458,7 +9507,7 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
@@ -9480,7 +9529,7 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" ref="I338:I400" si="12">IF(SUM(B338:F338,H338)=0,"",SUM(B338:F338,H338))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
@@ -10430,7 +10479,7 @@
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J381:J392" si="13">IF(I381="","",1440-I381)</f>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10452,7 +10501,7 @@
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10474,7 +10523,7 @@
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10496,7 +10545,7 @@
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10518,7 +10567,7 @@
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10540,7 +10589,7 @@
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10562,7 +10611,7 @@
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10584,7 +10633,7 @@
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10606,7 +10655,7 @@
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10680,182 +10729,6 @@
       <c r="M392" s="16"/>
       <c r="N392" s="17"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A393" s="13"/>
-      <c r="B393" s="14"/>
-      <c r="C393" s="14"/>
-      <c r="D393" s="14"/>
-      <c r="E393" s="14"/>
-      <c r="F393" s="14"/>
-      <c r="G393" s="14"/>
-      <c r="H393" s="14"/>
-      <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K393" s="16"/>
-      <c r="L393" s="16"/>
-      <c r="M393" s="16"/>
-      <c r="N393" s="17"/>
-    </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A394" s="13"/>
-      <c r="B394" s="14"/>
-      <c r="C394" s="14"/>
-      <c r="D394" s="14"/>
-      <c r="E394" s="14"/>
-      <c r="F394" s="14"/>
-      <c r="G394" s="14"/>
-      <c r="H394" s="14"/>
-      <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K394" s="16"/>
-      <c r="L394" s="16"/>
-      <c r="M394" s="16"/>
-      <c r="N394" s="17"/>
-    </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A395" s="13"/>
-      <c r="B395" s="14"/>
-      <c r="C395" s="14"/>
-      <c r="D395" s="14"/>
-      <c r="E395" s="14"/>
-      <c r="F395" s="14"/>
-      <c r="G395" s="14"/>
-      <c r="H395" s="14"/>
-      <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K395" s="16"/>
-      <c r="L395" s="16"/>
-      <c r="M395" s="16"/>
-      <c r="N395" s="17"/>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A396" s="13"/>
-      <c r="B396" s="14"/>
-      <c r="C396" s="14"/>
-      <c r="D396" s="14"/>
-      <c r="E396" s="14"/>
-      <c r="F396" s="14"/>
-      <c r="G396" s="14"/>
-      <c r="H396" s="14"/>
-      <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K396" s="16"/>
-      <c r="L396" s="16"/>
-      <c r="M396" s="16"/>
-      <c r="N396" s="17"/>
-    </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A397" s="13"/>
-      <c r="B397" s="14"/>
-      <c r="C397" s="14"/>
-      <c r="D397" s="14"/>
-      <c r="E397" s="14"/>
-      <c r="F397" s="14"/>
-      <c r="G397" s="14"/>
-      <c r="H397" s="14"/>
-      <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K397" s="16"/>
-      <c r="L397" s="16"/>
-      <c r="M397" s="16"/>
-      <c r="N397" s="17"/>
-    </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A398" s="13"/>
-      <c r="B398" s="14"/>
-      <c r="C398" s="14"/>
-      <c r="D398" s="14"/>
-      <c r="E398" s="14"/>
-      <c r="F398" s="14"/>
-      <c r="G398" s="14"/>
-      <c r="H398" s="14"/>
-      <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K398" s="16"/>
-      <c r="L398" s="16"/>
-      <c r="M398" s="16"/>
-      <c r="N398" s="17"/>
-    </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A399" s="13"/>
-      <c r="B399" s="14"/>
-      <c r="C399" s="14"/>
-      <c r="D399" s="14"/>
-      <c r="E399" s="14"/>
-      <c r="F399" s="14"/>
-      <c r="G399" s="14"/>
-      <c r="H399" s="14"/>
-      <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K399" s="16"/>
-      <c r="L399" s="16"/>
-      <c r="M399" s="16"/>
-      <c r="N399" s="17"/>
-    </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A400" s="13"/>
-      <c r="B400" s="14"/>
-      <c r="C400" s="14"/>
-      <c r="D400" s="14"/>
-      <c r="E400" s="14"/>
-      <c r="F400" s="14"/>
-      <c r="G400" s="14"/>
-      <c r="H400" s="14"/>
-      <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K400" s="16"/>
-      <c r="L400" s="16"/>
-      <c r="M400" s="16"/>
-      <c r="N400" s="17"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10865,21 +10738,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J400">
+  <conditionalFormatting sqref="J6:J392">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K392" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L392" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M392" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D81344E-F10D-40A0-BF8C-CBCB175367DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E271D63-A6D6-4DF7-99FA-061FA15B39BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t>Whole day spend in travelling</t>
+  </si>
+  <si>
+    <t>Rest at home and visit some places in my hometown</t>
+  </si>
+  <si>
+    <t>Visit some temples</t>
   </si>
 </sst>
 </file>
@@ -3183,49 +3189,97 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B50" s="9">
+        <v>540</v>
+      </c>
+      <c r="C50" s="9">
+        <v>45</v>
+      </c>
+      <c r="D50" s="9">
+        <v>90</v>
+      </c>
+      <c r="E50" s="9">
+        <v>45</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>30</v>
+      </c>
+      <c r="I50" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J50" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B51" s="9">
+        <v>480</v>
+      </c>
+      <c r="C51" s="9">
+        <v>60</v>
+      </c>
+      <c r="D51" s="9">
+        <v>120</v>
+      </c>
+      <c r="E51" s="9">
+        <v>60</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>60</v>
+      </c>
+      <c r="I51" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J51" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E271D63-A6D6-4DF7-99FA-061FA15B39BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7AA1D4-D1FB-4401-A4E4-F23AC03ACF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,12 @@
   </si>
   <si>
     <t>Visit some temples</t>
+  </si>
+  <si>
+    <t>Just hangning with friends</t>
+  </si>
+  <si>
+    <t>Revise some topics for Mid Term</t>
   </si>
 </sst>
 </file>
@@ -3235,7 +3241,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>46296</v>
       </c>
@@ -3282,48 +3288,96 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B52" s="9">
+        <v>320</v>
+      </c>
+      <c r="C52" s="9">
+        <v>30</v>
+      </c>
+      <c r="D52" s="9">
+        <v>180</v>
+      </c>
+      <c r="E52" s="9">
+        <v>30</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>30</v>
+      </c>
+      <c r="I52" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J52" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B53" s="9">
+        <v>420</v>
+      </c>
+      <c r="C53" s="9">
+        <v>120</v>
+      </c>
+      <c r="D53" s="9">
+        <v>150</v>
+      </c>
+      <c r="E53" s="9">
+        <v>180</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>120</v>
+      </c>
+      <c r="I53" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J53" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7AA1D4-D1FB-4401-A4E4-F23AC03ACF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE31156-4ECC-49C0-A168-8E36CA3F9F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,12 @@
   </si>
   <si>
     <t>Revise some topics for Mid Term</t>
+  </si>
+  <si>
+    <t>Online classes started</t>
+  </si>
+  <si>
+    <t>Do some activities with friends</t>
   </si>
 </sst>
 </file>
@@ -3379,49 +3385,97 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B54" s="9">
+        <v>420</v>
+      </c>
+      <c r="C54" s="9">
+        <v>120</v>
+      </c>
+      <c r="D54" s="9">
+        <v>180</v>
+      </c>
+      <c r="E54" s="9">
+        <v>45</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>200</v>
+      </c>
+      <c r="I54" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J54" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B55" s="9">
+        <v>350</v>
+      </c>
+      <c r="C55" s="9">
+        <v>60</v>
+      </c>
+      <c r="D55" s="9">
+        <v>100</v>
+      </c>
+      <c r="E55" s="9">
+        <v>30</v>
+      </c>
+      <c r="F55" s="9">
+        <v>300</v>
+      </c>
+      <c r="G55" s="9">
+        <v>6</v>
+      </c>
+      <c r="H55" s="9">
+        <v>60</v>
+      </c>
+      <c r="I55" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J55" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N55" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE31156-4ECC-49C0-A168-8E36CA3F9F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C5D9CC-7C6B-440F-BC1B-AFAAE981AF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -345,6 +345,12 @@
   <si>
     <t>Do some activities with friends</t>
   </si>
+  <si>
+    <t>While travelling meet new peoples and become good friends</t>
+  </si>
+  <si>
+    <t>Preparing for Mid Term</t>
+  </si>
 </sst>
 </file>
 
@@ -462,7 +468,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -485,37 +491,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB7B7B7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB7B7B7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB7B7B7"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB7B7B7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB7B7B7"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -554,36 +534,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1076,74 +1026,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="30">
+      <c r="F2" s="20">
         <v>12616871</v>
       </c>
-      <c r="G2" s="30"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="30"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1618,21 +1568,21 @@
         <v>150</v>
       </c>
       <c r="F15" s="9">
+        <v>400</v>
+      </c>
+      <c r="G15" s="9">
         <v>8</v>
-      </c>
-      <c r="G15" s="9">
-        <v>400</v>
       </c>
       <c r="H15" s="9">
         <v>150</v>
       </c>
       <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v>908</v>
+        <v>1300</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v>532</v>
+        <v>140</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>63</v>
@@ -1664,21 +1614,21 @@
         <v>90</v>
       </c>
       <c r="F16" s="9">
+        <v>150</v>
+      </c>
+      <c r="G16" s="9">
         <v>3</v>
-      </c>
-      <c r="G16" s="9">
-        <v>150</v>
       </c>
       <c r="H16" s="9">
         <v>150</v>
       </c>
       <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v>963</v>
+        <v>1110</v>
       </c>
       <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v>477</v>
+        <v>330</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>61</v>
@@ -1832,94 +1782,94 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="18">
+      <c r="A20" s="8">
         <v>46265</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="9">
         <v>230</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="9">
         <v>90</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="9">
         <v>90</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="9">
         <v>120</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="9">
         <v>300</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="9">
         <v>6</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="9">
         <v>270</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="10">
         <f t="shared" si="2"/>
         <v>1100</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
         <v>340</v>
       </c>
-      <c r="K20" s="21" t="s">
+      <c r="K20" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L20" s="21" t="s">
+      <c r="L20" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M20" s="21" t="s">
+      <c r="M20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N20" s="22" t="s">
+      <c r="N20" s="12" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="23">
+      <c r="A21" s="8">
         <v>46266</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="9">
         <v>450</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="9">
         <v>80</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="9">
         <v>130</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="9">
         <v>45</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="9">
         <v>150</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="9">
         <v>3</v>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="9">
         <v>260</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="10">
         <f t="shared" si="2"/>
         <v>1115</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="K21" s="26" t="s">
+      <c r="K21" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="L21" s="26" t="s">
+      <c r="L21" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M21" s="26" t="s">
+      <c r="M21" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="N21" s="27"/>
+      <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
@@ -3478,158 +3428,318 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="9">
+        <v>360</v>
+      </c>
+      <c r="C56" s="9">
+        <v>30</v>
+      </c>
+      <c r="D56" s="9">
+        <v>0</v>
+      </c>
+      <c r="E56" s="9">
+        <v>45</v>
+      </c>
+      <c r="F56" s="9">
+        <v>150</v>
+      </c>
+      <c r="G56" s="9">
+        <v>3</v>
+      </c>
+      <c r="H56" s="9">
+        <v>30</v>
+      </c>
+      <c r="I56" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>615</v>
+      </c>
+      <c r="J56" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>825</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N56" s="12"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="9">
+        <v>420</v>
+      </c>
+      <c r="C57" s="9">
+        <v>45</v>
+      </c>
+      <c r="D57" s="9">
+        <v>80</v>
+      </c>
+      <c r="E57" s="9">
+        <v>30</v>
+      </c>
+      <c r="F57" s="9">
+        <v>400</v>
+      </c>
+      <c r="G57" s="9">
+        <v>8</v>
+      </c>
+      <c r="H57" s="9">
+        <v>120</v>
+      </c>
+      <c r="I57" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J57" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>345</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N57" s="12"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="9">
+        <v>480</v>
+      </c>
+      <c r="C58" s="9">
+        <v>30</v>
+      </c>
+      <c r="D58" s="9">
+        <v>90</v>
+      </c>
+      <c r="E58" s="9">
+        <v>0</v>
+      </c>
+      <c r="F58" s="9">
+        <v>300</v>
+      </c>
+      <c r="G58" s="9">
+        <v>6</v>
+      </c>
+      <c r="H58" s="9">
+        <v>45</v>
+      </c>
+      <c r="I58" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>945</v>
+      </c>
+      <c r="J58" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>495</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N58" s="12"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="9">
+        <v>150</v>
+      </c>
+      <c r="C59" s="9">
+        <v>20</v>
+      </c>
+      <c r="D59" s="9">
+        <v>120</v>
+      </c>
+      <c r="E59" s="9">
+        <v>20</v>
+      </c>
+      <c r="F59" s="9">
+        <v>150</v>
+      </c>
+      <c r="G59" s="9">
+        <v>3</v>
+      </c>
+      <c r="H59" s="9">
+        <v>90</v>
+      </c>
+      <c r="I59" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>550</v>
+      </c>
+      <c r="J59" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="12"/>
+    </row>
+    <row r="60" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B60" s="9">
+        <v>480</v>
+      </c>
+      <c r="C60" s="9">
+        <v>0</v>
+      </c>
+      <c r="D60" s="9">
+        <v>0</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0</v>
+      </c>
+      <c r="F60" s="9">
+        <v>0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9">
+        <v>60</v>
+      </c>
+      <c r="I60" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J60" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N60" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="9">
+        <v>300</v>
+      </c>
+      <c r="C61" s="9">
+        <v>120</v>
+      </c>
+      <c r="D61" s="9">
+        <v>240</v>
+      </c>
+      <c r="E61" s="9">
+        <v>60</v>
+      </c>
+      <c r="F61" s="9">
+        <v>0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9">
+        <v>45</v>
+      </c>
+      <c r="I61" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J61" s="10">
         <f t="shared" ref="J61:J124" si="3">IF(I61="","",1440-I61)</f>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>675</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N61" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="9">
+        <v>420</v>
+      </c>
+      <c r="C62" s="9">
+        <v>150</v>
+      </c>
+      <c r="D62" s="9">
+        <v>300</v>
+      </c>
+      <c r="E62" s="9">
+        <v>120</v>
+      </c>
+      <c r="F62" s="9">
+        <v>0</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9">
+        <v>60</v>
+      </c>
+      <c r="I62" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J62" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C5D9CC-7C6B-440F-BC1B-AFAAE981AF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9976A6-C7A0-4175-BE15-B281FCA52EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>Preparing for Mid Term</t>
+  </si>
+  <si>
+    <t>Start a new journey of life, Vlogging</t>
   </si>
 </sst>
 </file>
@@ -3742,70 +3745,142 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="9">
+        <v>450</v>
+      </c>
+      <c r="C63" s="9">
+        <v>60</v>
+      </c>
+      <c r="D63" s="9">
+        <v>180</v>
+      </c>
+      <c r="E63" s="9">
+        <v>30</v>
+      </c>
+      <c r="F63" s="9">
+        <v>0</v>
+      </c>
+      <c r="G63" s="9">
+        <v>0</v>
+      </c>
+      <c r="H63" s="9">
+        <v>120</v>
+      </c>
+      <c r="I63" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J63" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N63" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B64" s="9">
+        <v>350</v>
+      </c>
+      <c r="C64" s="9">
+        <v>120</v>
+      </c>
+      <c r="D64" s="9">
+        <v>120</v>
+      </c>
+      <c r="E64" s="9">
+        <v>30</v>
+      </c>
+      <c r="F64" s="9">
+        <v>0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>45</v>
+      </c>
+      <c r="I64" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>665</v>
+      </c>
+      <c r="J64" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>775</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N64" s="12" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="9">
+        <v>480</v>
+      </c>
+      <c r="C65" s="9">
+        <v>60</v>
+      </c>
+      <c r="D65" s="9">
+        <v>300</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>200</v>
+      </c>
+      <c r="I65" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J65" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N65" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9976A6-C7A0-4175-BE15-B281FCA52EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37F4442-3EB9-42E7-B45E-586F1201479D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>Start a new journey of life, Vlogging</t>
+  </si>
+  <si>
+    <t>Preparing for Analytics Mid Term</t>
   </si>
 </sst>
 </file>
@@ -3882,49 +3885,97 @@
         <v>104</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+    <row r="66" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="9">
+        <v>250</v>
+      </c>
+      <c r="C66" s="9">
+        <v>150</v>
+      </c>
+      <c r="D66" s="9">
+        <v>360</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0</v>
+      </c>
+      <c r="F66" s="9">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>90</v>
+      </c>
+      <c r="I66" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J66" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="9">
+        <v>380</v>
+      </c>
+      <c r="C67" s="9">
+        <v>90</v>
+      </c>
+      <c r="D67" s="9">
+        <v>210</v>
+      </c>
+      <c r="E67" s="9">
+        <v>0</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0</v>
+      </c>
+      <c r="H67" s="9">
+        <v>180</v>
+      </c>
+      <c r="I67" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J67" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N67" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37F4442-3EB9-42E7-B45E-586F1201479D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62B8B2E-F531-4DB2-8AC9-D34CEDA95EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,18 @@
   </si>
   <si>
     <t>Preparing for Analytics Mid Term</t>
+  </si>
+  <si>
+    <t>Enjoy the holiday after the mid term</t>
+  </si>
+  <si>
+    <t>Feeling not well today</t>
+  </si>
+  <si>
+    <t>Visit jalandhhar for Rawan Dahan</t>
+  </si>
+  <si>
+    <t>Classes starts</t>
   </si>
 </sst>
 </file>
@@ -3977,93 +3989,189 @@
         <v>104</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+    <row r="68" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="8">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="9">
+        <v>480</v>
+      </c>
+      <c r="C68" s="9">
+        <v>60</v>
+      </c>
+      <c r="D68" s="9">
+        <v>240</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0</v>
+      </c>
+      <c r="G68" s="9">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
+        <v>30</v>
+      </c>
+      <c r="I68" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J68" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="9">
+        <v>180</v>
+      </c>
+      <c r="C69" s="9">
+        <v>10</v>
+      </c>
+      <c r="D69" s="9">
+        <v>280</v>
+      </c>
+      <c r="E69" s="9">
+        <v>45</v>
+      </c>
+      <c r="F69" s="9">
+        <v>250</v>
+      </c>
+      <c r="G69" s="9">
+        <v>5</v>
+      </c>
+      <c r="H69" s="9">
+        <v>150</v>
+      </c>
+      <c r="I69" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J69" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+        <v>525</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N69" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="9">
+        <v>400</v>
+      </c>
+      <c r="C70" s="9">
+        <v>0</v>
+      </c>
+      <c r="D70" s="9">
+        <v>150</v>
+      </c>
+      <c r="E70" s="9">
+        <v>30</v>
+      </c>
+      <c r="F70" s="9">
+        <v>0</v>
+      </c>
+      <c r="G70" s="9">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
+        <v>100</v>
+      </c>
+      <c r="I70" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J70" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N70" s="12" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="9">
+        <v>360</v>
+      </c>
+      <c r="C71" s="9">
+        <v>90</v>
+      </c>
+      <c r="D71" s="9">
+        <v>180</v>
+      </c>
+      <c r="E71" s="9">
+        <v>120</v>
+      </c>
+      <c r="F71" s="9">
+        <v>300</v>
+      </c>
+      <c r="G71" s="9">
+        <v>6</v>
+      </c>
+      <c r="H71" s="9">
+        <v>30</v>
+      </c>
+      <c r="I71" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J71" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N71" s="12" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62B8B2E-F531-4DB2-8AC9-D34CEDA95EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDCFAC8-AE98-401C-B9D4-CA5E044484C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4174,48 +4174,92 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="9">
+        <v>420</v>
+      </c>
+      <c r="C72" s="9">
+        <v>30</v>
+      </c>
+      <c r="D72" s="9">
+        <v>300</v>
+      </c>
+      <c r="E72" s="9">
+        <v>180</v>
+      </c>
+      <c r="F72" s="9">
+        <v>200</v>
+      </c>
+      <c r="G72" s="9">
+        <v>4</v>
+      </c>
+      <c r="H72" s="9">
+        <v>120</v>
+      </c>
+      <c r="I72" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J72" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N72" s="12"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="9">
+        <v>480</v>
+      </c>
+      <c r="C73" s="9">
+        <v>120</v>
+      </c>
+      <c r="D73" s="9">
+        <v>150</v>
+      </c>
+      <c r="E73" s="9">
+        <v>150</v>
+      </c>
+      <c r="F73" s="9">
+        <v>250</v>
+      </c>
+      <c r="G73" s="9">
+        <v>5</v>
+      </c>
+      <c r="H73" s="9">
+        <v>60</v>
+      </c>
+      <c r="I73" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J73" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N73" s="12"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDCFAC8-AE98-401C-B9D4-CA5E044484C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A950FCD5-D9F4-49C3-A599-6E2CAC27C1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,12 @@
   </si>
   <si>
     <t>Classes starts</t>
+  </si>
+  <si>
+    <t>Enjoy the holiday with my friends and a lots of enjoyment</t>
+  </si>
+  <si>
+    <t>Do some content creation work with new members</t>
   </si>
 </sst>
 </file>
@@ -4261,49 +4267,97 @@
       </c>
       <c r="N73" s="12"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+    <row r="74" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="8">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="9">
+        <v>500</v>
+      </c>
+      <c r="C74" s="9">
+        <v>30</v>
+      </c>
+      <c r="D74" s="9">
+        <v>300</v>
+      </c>
+      <c r="E74" s="9">
+        <v>30</v>
+      </c>
+      <c r="F74" s="9">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9">
+        <v>250</v>
+      </c>
+      <c r="I74" s="10">
         <f t="shared" ref="I74:I137" si="4">IF(SUM(B74:F74,H74)=0,"",SUM(B74:F74,H74))</f>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+        <v>330</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N74" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="8">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="9">
+        <v>450</v>
+      </c>
+      <c r="C75" s="9">
+        <v>0</v>
+      </c>
+      <c r="D75" s="9">
+        <v>90</v>
+      </c>
+      <c r="E75" s="9">
+        <v>60</v>
+      </c>
+      <c r="F75" s="9">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>300</v>
+      </c>
+      <c r="I75" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J75" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>

--- a/12616871.xlsx
+++ b/12616871.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\12616871_CAP776_D1P2632\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A950FCD5-D9F4-49C3-A599-6E2CAC27C1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374FDA45-3899-4A50-8254-84D3F20CFAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>Do some content creation work with new members</t>
+  </si>
+  <si>
+    <t>Completed the project of cpp and complete all the analytics test.</t>
   </si>
 </sst>
 </file>
@@ -4359,27 +4362,51 @@
         <v>111</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+    <row r="76" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A76" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B76" s="9">
+        <v>420</v>
+      </c>
+      <c r="C76" s="9">
+        <v>30</v>
+      </c>
+      <c r="D76" s="9">
+        <v>350</v>
+      </c>
+      <c r="E76" s="9">
+        <v>350</v>
+      </c>
+      <c r="F76" s="9">
+        <v>0</v>
+      </c>
+      <c r="G76" s="9">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>150</v>
+      </c>
+      <c r="I76" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J76" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N76" s="12" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="13"/>
